--- a/mock/input.xlsx
+++ b/mock/input.xlsx
@@ -36,14 +36,14 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgXdXUUhZ1MEm1g3tZrgg2qmgxqKA=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mghCHGfEgrBcIVnAQ48VcIUvhFP+w=="/>
     </ext>
   </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="301">
   <si>
     <t>Packages</t>
   </si>
@@ -84,26 +84,6 @@
   </si>
   <si>
     <t>Starting Price*:</t>
-  </si>
-  <si>
-    <t>$XX,XXX*
-[DE4H2TJW]</t>
-  </si>
-  <si>
-    <t>$XX,XXX*
-[DE4H3TJW]</t>
-  </si>
-  <si>
-    <t>$XX,XXX*
-[DE4H6TJW]</t>
-  </si>
-  <si>
-    <t>$XX,XXX*
-[DE4G7TJW]</t>
-  </si>
-  <si>
-    <t>$XX,XXX*
-[DE5G9TEW]</t>
   </si>
   <si>
     <r>
@@ -3057,13 +3037,13 @@
     </xf>
     <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="11" fillId="0" fontId="6" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf quotePrefix="1" borderId="11" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="11" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf quotePrefix="1" borderId="12" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf borderId="12" fillId="0" fontId="6" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -3816,20 +3796,20 @@
         <v>7</v>
       </c>
       <c r="C4" s="14"/>
-      <c r="D4" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G4" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="H4" s="17" t="s">
-        <v>12</v>
+      <c r="D4" s="15">
+        <v>33000.0</v>
+      </c>
+      <c r="E4" s="16">
+        <v>35000.0</v>
+      </c>
+      <c r="F4" s="16">
+        <v>38000.0</v>
+      </c>
+      <c r="G4" s="16">
+        <v>38000.0</v>
+      </c>
+      <c r="H4" s="17">
+        <v>52900.0</v>
       </c>
       <c r="I4" s="18"/>
       <c r="J4" s="18"/>
@@ -3853,7 +3833,7 @@
     <row r="5" ht="43.5" customHeight="1">
       <c r="A5" s="9"/>
       <c r="B5" s="10" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
@@ -3911,22 +3891,22 @@
     <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="9"/>
       <c r="B7" s="23" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G7" s="24" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
@@ -3950,7 +3930,7 @@
     <row r="8" ht="25.5" customHeight="1">
       <c r="A8" s="26"/>
       <c r="B8" s="27" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="D8" s="28">
         <v>1.5</v>
@@ -3965,7 +3945,7 @@
         <v>1.5</v>
       </c>
       <c r="H8" s="29" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9"/>
@@ -3989,7 +3969,7 @@
     <row r="9" ht="25.5" customHeight="1">
       <c r="A9" s="26"/>
       <c r="B9" s="27" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D9" s="28">
         <v>17.8</v>
@@ -4028,22 +4008,22 @@
     <row r="10" ht="45.0" customHeight="1">
       <c r="A10" s="9"/>
       <c r="B10" s="27" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D10" s="28" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F10" s="28" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G10" s="31" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H10" s="30" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9"/>
@@ -4067,22 +4047,22 @@
     <row r="11" ht="39.0" customHeight="1">
       <c r="A11" s="9"/>
       <c r="B11" s="27" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D11" s="28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F11" s="28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="G11" s="28" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H11" s="30" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9"/>
@@ -4106,22 +4086,22 @@
     <row r="12" ht="27.0" customHeight="1">
       <c r="A12" s="9"/>
       <c r="B12" s="27" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D12" s="28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F12" s="28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G12" s="28" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="H12" s="30" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I12" s="9"/>
       <c r="J12" s="9"/>
@@ -4145,22 +4125,22 @@
     <row r="13" ht="27.0" customHeight="1">
       <c r="A13" s="26"/>
       <c r="B13" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="D13" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="30" t="s">
         <v>28</v>
-      </c>
-      <c r="D13" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="28" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="30" t="s">
-        <v>33</v>
       </c>
       <c r="I13" s="9"/>
       <c r="J13" s="9"/>
@@ -4184,22 +4164,22 @@
     <row r="14" ht="27.0" customHeight="1">
       <c r="A14" s="26"/>
       <c r="B14" s="27" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D14" s="28" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="F14" s="28" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="H14" s="30" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
@@ -4223,23 +4203,23 @@
     <row r="15" ht="27.0" customHeight="1">
       <c r="A15" s="9"/>
       <c r="B15" s="32" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C15" s="14"/>
       <c r="D15" s="28" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F15" s="28" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H15" s="30" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
@@ -4263,23 +4243,23 @@
     <row r="16" ht="27.0" customHeight="1">
       <c r="A16" s="9"/>
       <c r="B16" s="33" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C16" s="34"/>
       <c r="D16" s="31" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="F16" s="31" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G16" s="31" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="H16" s="30" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="I16" s="9"/>
       <c r="J16" s="9"/>
@@ -4303,20 +4283,20 @@
     <row r="17" ht="27.0" customHeight="1">
       <c r="A17" s="9"/>
       <c r="B17" s="33" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C17" s="34"/>
       <c r="D17" s="35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E17" s="35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F17" s="35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G17" s="35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H17" s="36"/>
       <c r="I17" s="9"/>
@@ -4341,23 +4321,23 @@
     <row r="18" ht="27.0" customHeight="1">
       <c r="A18" s="9"/>
       <c r="B18" s="33" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="28" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F18" s="28" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H18" s="30" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="I18" s="9"/>
       <c r="J18" s="9"/>
@@ -4381,23 +4361,23 @@
     <row r="19" ht="45.0" customHeight="1">
       <c r="A19" s="9"/>
       <c r="B19" s="33" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C19" s="34"/>
       <c r="D19" s="31" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F19" s="31" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G19" s="31" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H19" s="30" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="I19" s="9"/>
       <c r="J19" s="9"/>
@@ -4421,23 +4401,23 @@
     <row r="20" ht="45.0" customHeight="1">
       <c r="A20" s="9"/>
       <c r="B20" s="33" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C20" s="34"/>
       <c r="D20" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F20" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G20" s="31" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="H20" s="30" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="I20" s="9"/>
       <c r="J20" s="9"/>
@@ -4461,7 +4441,7 @@
     <row r="21" ht="25.5" customHeight="1">
       <c r="A21" s="26"/>
       <c r="B21" s="19" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C21" s="20"/>
       <c r="D21" s="37"/>
@@ -4491,23 +4471,23 @@
     <row r="22" ht="25.5" customHeight="1">
       <c r="A22" s="26"/>
       <c r="B22" s="39" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C22" s="14"/>
       <c r="D22" s="35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E22" s="35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F22" s="35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G22" s="35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H22" s="40" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I22" s="9"/>
       <c r="J22" s="9"/>
@@ -4531,17 +4511,17 @@
     <row r="23" ht="25.5" customHeight="1">
       <c r="A23" s="9"/>
       <c r="B23" s="41" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C23" s="20"/>
       <c r="D23" s="42" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E23" s="42" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F23" s="42" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G23" s="42"/>
       <c r="H23" s="43"/>
@@ -4567,16 +4547,16 @@
     <row r="24" ht="25.5" customHeight="1">
       <c r="A24" s="9"/>
       <c r="B24" s="26" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E24" s="44" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F24" s="44" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G24" s="44"/>
       <c r="H24" s="45"/>
@@ -4602,16 +4582,16 @@
     <row r="25" ht="25.5" customHeight="1">
       <c r="A25" s="9"/>
       <c r="B25" s="26" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E25" s="44" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F25" s="44" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G25" s="44"/>
       <c r="H25" s="45"/>
@@ -4637,7 +4617,7 @@
     <row r="26" ht="25.5" customHeight="1">
       <c r="A26" s="9"/>
       <c r="B26" s="39" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="46">
@@ -4673,17 +4653,17 @@
     <row r="27" ht="33.75" customHeight="1">
       <c r="A27" s="9"/>
       <c r="B27" s="48" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C27" s="20"/>
       <c r="D27" s="49"/>
       <c r="E27" s="49"/>
       <c r="F27" s="49"/>
       <c r="G27" s="42" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H27" s="43" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
@@ -4707,7 +4687,7 @@
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="9"/>
       <c r="B28" s="27" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="D28" s="50"/>
       <c r="E28" s="51"/>
@@ -4736,7 +4716,7 @@
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="9"/>
       <c r="B29" s="27" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D29" s="53"/>
       <c r="E29" s="53"/>
@@ -4769,13 +4749,13 @@
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="9"/>
       <c r="B30" s="27" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D30" s="53"/>
       <c r="E30" s="53"/>
       <c r="F30" s="53"/>
       <c r="G30" s="54" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H30" s="45">
         <v>2.115</v>
@@ -4802,7 +4782,7 @@
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="9"/>
       <c r="B31" s="27" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D31" s="53"/>
       <c r="E31" s="53"/>
@@ -4835,7 +4815,7 @@
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="9"/>
       <c r="B32" s="27" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="D32" s="53"/>
       <c r="E32" s="53"/>
@@ -4868,13 +4848,13 @@
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="9"/>
       <c r="B33" s="27" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="D33" s="53"/>
       <c r="E33" s="53"/>
       <c r="F33" s="53"/>
       <c r="G33" s="54" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="H33" s="45">
         <v>0.911</v>
@@ -4901,7 +4881,7 @@
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="9"/>
       <c r="B34" s="27" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D34" s="53"/>
       <c r="E34" s="53"/>
@@ -4934,7 +4914,7 @@
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="9"/>
       <c r="B35" s="27" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="D35" s="53"/>
       <c r="E35" s="53"/>
@@ -4967,7 +4947,7 @@
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="9"/>
       <c r="B36" s="32" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C36" s="14"/>
       <c r="D36" s="55"/>
@@ -5001,17 +4981,17 @@
     <row r="37" ht="25.5" customHeight="1">
       <c r="A37" s="9"/>
       <c r="B37" s="19" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C37" s="20"/>
       <c r="D37" s="28"/>
       <c r="E37" s="28"/>
       <c r="F37" s="28"/>
       <c r="G37" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H37" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I37" s="9"/>
       <c r="J37" s="9"/>
@@ -5035,17 +5015,17 @@
     <row r="38" ht="25.5" customHeight="1">
       <c r="A38" s="9"/>
       <c r="B38" s="19" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C38" s="20"/>
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
       <c r="G38" s="35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H38" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I38" s="9"/>
       <c r="J38" s="9"/>
@@ -5069,23 +5049,23 @@
     <row r="39" ht="39.0" customHeight="1">
       <c r="A39" s="9"/>
       <c r="B39" s="19" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C39" s="20"/>
       <c r="D39" s="28" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E39" s="28" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="F39" s="28" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="G39" s="28" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H39" s="30" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="I39" s="9"/>
       <c r="J39" s="9"/>
@@ -5109,23 +5089,23 @@
     <row r="40" ht="39.0" customHeight="1">
       <c r="A40" s="9"/>
       <c r="B40" s="33" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C40" s="34"/>
       <c r="D40" s="28" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E40" s="28" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F40" s="28" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G40" s="28" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H40" s="30" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I40" s="9"/>
       <c r="J40" s="9"/>
@@ -5149,7 +5129,7 @@
     <row r="41" ht="37.5" customHeight="1">
       <c r="A41" s="26"/>
       <c r="B41" s="19" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C41" s="20"/>
       <c r="D41" s="28">
@@ -5189,7 +5169,7 @@
     <row r="42" ht="45.0" customHeight="1">
       <c r="A42" s="9"/>
       <c r="B42" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C42" s="59"/>
       <c r="D42" s="10"/>
@@ -5219,23 +5199,23 @@
     <row r="43" ht="61.5" customHeight="1">
       <c r="A43" s="9"/>
       <c r="B43" s="19" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C43" s="20"/>
       <c r="D43" s="60" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E43" s="60" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F43" s="60" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="G43" s="60" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H43" s="61" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="I43" s="9"/>
       <c r="J43" s="9"/>
@@ -5259,19 +5239,19 @@
     <row r="44" ht="25.5" customHeight="1">
       <c r="A44" s="9"/>
       <c r="B44" s="19" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C44" s="20"/>
       <c r="D44" s="60"/>
       <c r="E44" s="60"/>
       <c r="F44" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G44" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H44" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I44" s="9"/>
       <c r="J44" s="9"/>
@@ -5295,19 +5275,19 @@
     <row r="45" ht="25.5" customHeight="1">
       <c r="A45" s="9"/>
       <c r="B45" s="19" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C45" s="20"/>
       <c r="D45" s="60"/>
       <c r="E45" s="60"/>
       <c r="F45" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G45" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H45" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I45" s="9"/>
       <c r="J45" s="9"/>
@@ -5331,7 +5311,7 @@
     <row r="46" ht="25.5" customHeight="1">
       <c r="A46" s="9"/>
       <c r="B46" s="19" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C46" s="20"/>
       <c r="D46" s="60"/>
@@ -5339,7 +5319,7 @@
       <c r="F46" s="57"/>
       <c r="G46" s="57"/>
       <c r="H46" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I46" s="9"/>
       <c r="J46" s="9"/>
@@ -5363,20 +5343,20 @@
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="9"/>
       <c r="B47" s="62" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C47" s="63"/>
       <c r="D47" s="42" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E47" s="42" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F47" s="42" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G47" s="42" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H47" s="43"/>
       <c r="I47" s="9"/>
@@ -5401,7 +5381,7 @@
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="9"/>
       <c r="B48" s="64" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C48" s="65"/>
       <c r="D48" s="53"/>
@@ -5409,7 +5389,7 @@
       <c r="F48" s="53"/>
       <c r="G48" s="53"/>
       <c r="H48" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I48" s="9"/>
       <c r="J48" s="9"/>
@@ -5433,23 +5413,23 @@
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="9"/>
       <c r="B49" s="32" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C49" s="14"/>
       <c r="D49" s="35" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E49" s="50" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F49" s="50" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G49" s="50" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H49" s="67" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I49" s="9"/>
       <c r="J49" s="9"/>
@@ -5473,23 +5453,23 @@
     <row r="50" ht="24.0" customHeight="1">
       <c r="A50" s="9"/>
       <c r="B50" s="19" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C50" s="20"/>
       <c r="D50" s="60" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E50" s="60" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F50" s="60" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G50" s="60" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="H50" s="61" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="I50" s="9"/>
       <c r="J50" s="9"/>
@@ -5513,23 +5493,23 @@
     <row r="51" ht="24.0" customHeight="1">
       <c r="A51" s="9"/>
       <c r="B51" s="19" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C51" s="20"/>
       <c r="D51" s="60" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E51" s="60" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="F51" s="60" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G51" s="68" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H51" s="61" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I51" s="9"/>
       <c r="J51" s="9"/>
@@ -5553,23 +5533,23 @@
     <row r="52" ht="54.0" customHeight="1">
       <c r="A52" s="9"/>
       <c r="B52" s="69" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C52" s="34"/>
       <c r="D52" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E52" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F52" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G52" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H52" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I52" s="9"/>
       <c r="J52" s="9"/>
@@ -5593,7 +5573,7 @@
     <row r="53" ht="25.5" customHeight="1">
       <c r="A53" s="9"/>
       <c r="B53" s="19" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C53" s="20"/>
       <c r="D53" s="28">
@@ -5633,23 +5613,23 @@
     <row r="54" ht="25.5" customHeight="1">
       <c r="A54" s="9"/>
       <c r="B54" s="19" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C54" s="20"/>
       <c r="D54" s="60" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E54" s="60" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="F54" s="60" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="G54" s="60" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="H54" s="61" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="I54" s="9"/>
       <c r="J54" s="9"/>
@@ -5673,7 +5653,7 @@
     <row r="55" ht="25.5" customHeight="1">
       <c r="A55" s="9"/>
       <c r="B55" s="19" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C55" s="20"/>
       <c r="D55" s="60">
@@ -5713,23 +5693,23 @@
     <row r="56" ht="25.5" customHeight="1">
       <c r="A56" s="9"/>
       <c r="B56" s="19" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C56" s="20"/>
       <c r="D56" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E56" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F56" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G56" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H56" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I56" s="9"/>
       <c r="J56" s="9"/>
@@ -5753,7 +5733,7 @@
     <row r="57" ht="43.5" customHeight="1">
       <c r="A57" s="9"/>
       <c r="B57" s="19" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C57" s="20"/>
       <c r="D57" s="57"/>
@@ -5761,7 +5741,7 @@
       <c r="F57" s="57"/>
       <c r="G57" s="57"/>
       <c r="H57" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I57" s="9"/>
       <c r="J57" s="9"/>
@@ -5785,7 +5765,7 @@
     <row r="58" ht="25.5" customHeight="1">
       <c r="A58" s="70"/>
       <c r="B58" s="19" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C58" s="20"/>
       <c r="D58" s="21"/>
@@ -5815,7 +5795,7 @@
     <row r="59" ht="25.5" customHeight="1">
       <c r="A59" s="9"/>
       <c r="B59" s="26" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D59" s="24">
         <v>12.3</v>
@@ -5854,7 +5834,7 @@
     <row r="60" ht="25.5" customHeight="1">
       <c r="A60" s="70"/>
       <c r="B60" s="19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C60" s="20"/>
       <c r="D60" s="21"/>
@@ -5884,7 +5864,7 @@
     <row r="61" ht="25.5" customHeight="1">
       <c r="A61" s="9"/>
       <c r="B61" s="39" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C61" s="14"/>
       <c r="D61" s="71">
@@ -5900,7 +5880,7 @@
         <v>11.1</v>
       </c>
       <c r="H61" s="72" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="I61" s="9"/>
       <c r="J61" s="9"/>
@@ -5924,23 +5904,23 @@
     <row r="62" ht="25.5" customHeight="1">
       <c r="A62" s="9"/>
       <c r="B62" s="32" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C62" s="14"/>
       <c r="D62" s="31" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E62" s="31" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="F62" s="31" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G62" s="31" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="H62" s="73" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="I62" s="9"/>
       <c r="J62" s="9"/>
@@ -5964,22 +5944,22 @@
     <row r="63" ht="25.5" customHeight="1">
       <c r="A63" s="9"/>
       <c r="B63" s="27" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D63" s="24" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="E63" s="24" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="F63" s="24" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H63" s="73" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="9"/>
@@ -6003,23 +5983,23 @@
     <row r="64" ht="25.5" customHeight="1">
       <c r="A64" s="9"/>
       <c r="B64" s="33" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C64" s="34"/>
       <c r="D64" s="68" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E64" s="68" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F64" s="68" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G64" s="68" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="H64" s="61" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="I64" s="9"/>
       <c r="J64" s="9"/>
@@ -6043,23 +6023,23 @@
     <row r="65" ht="25.5" customHeight="1">
       <c r="A65" s="74"/>
       <c r="B65" s="33" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C65" s="34"/>
       <c r="D65" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E65" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F65" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G65" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H65" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I65" s="74"/>
       <c r="J65" s="74"/>
@@ -6083,7 +6063,7 @@
     <row r="66" ht="25.5" customHeight="1">
       <c r="A66" s="74"/>
       <c r="B66" s="27" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D66" s="75">
         <v>3084.0</v>
@@ -6122,23 +6102,23 @@
     <row r="67" ht="25.5" customHeight="1">
       <c r="A67" s="74"/>
       <c r="B67" s="33" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C67" s="34"/>
       <c r="D67" s="68" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E67" s="68" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="F67" s="68" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G67" s="68" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="H67" s="78" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="I67" s="74"/>
       <c r="J67" s="74"/>
@@ -6162,7 +6142,7 @@
     <row r="68" ht="43.5" customHeight="1">
       <c r="A68" s="74"/>
       <c r="B68" s="10" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C68" s="59"/>
       <c r="D68" s="10"/>
@@ -6192,7 +6172,7 @@
     <row r="69" ht="24.75" customHeight="1">
       <c r="A69" s="79"/>
       <c r="B69" s="19" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C69" s="20"/>
       <c r="D69" s="37"/>
@@ -6222,19 +6202,19 @@
     <row r="70" ht="24.75" customHeight="1">
       <c r="A70" s="79"/>
       <c r="B70" s="26" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D70" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E70" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F70" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G70" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H70" s="40"/>
       <c r="I70" s="74"/>
@@ -6259,7 +6239,7 @@
     <row r="71" ht="24.75" customHeight="1">
       <c r="A71" s="79"/>
       <c r="B71" s="19" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C71" s="20"/>
       <c r="D71" s="37"/>
@@ -6289,22 +6269,22 @@
     <row r="72" ht="24.75" customHeight="1">
       <c r="A72" s="79"/>
       <c r="B72" s="81" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D72" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E72" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F72" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G72" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H72" s="82" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I72" s="74"/>
       <c r="J72" s="74"/>
@@ -6328,22 +6308,22 @@
     <row r="73" ht="24.75" customHeight="1">
       <c r="A73" s="9"/>
       <c r="B73" s="26" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D73" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E73" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F73" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G73" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H73" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I73" s="9"/>
       <c r="J73" s="9"/>
@@ -6367,17 +6347,17 @@
     <row r="74" ht="24.75" customHeight="1">
       <c r="A74" s="26"/>
       <c r="B74" s="26" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D74" s="83"/>
       <c r="E74" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F74" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G74" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H74" s="84"/>
       <c r="I74" s="9"/>
@@ -6402,22 +6382,22 @@
     <row r="75" ht="24.75" customHeight="1">
       <c r="A75" s="9"/>
       <c r="B75" s="26" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D75" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E75" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F75" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G75" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H75" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I75" s="51"/>
       <c r="J75" s="9"/>
@@ -6441,18 +6421,18 @@
     <row r="76" ht="24.75" customHeight="1">
       <c r="A76" s="9"/>
       <c r="B76" s="26" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D76" s="85"/>
       <c r="E76" s="85"/>
       <c r="F76" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G76" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H76" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I76" s="51"/>
       <c r="J76" s="9"/>
@@ -6476,22 +6456,22 @@
     <row r="77" ht="24.75" customHeight="1">
       <c r="A77" s="26"/>
       <c r="B77" s="81" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D77" s="86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E77" s="86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F77" s="86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G77" s="86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H77" s="87" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I77" s="9"/>
       <c r="J77" s="9"/>
@@ -6515,7 +6495,7 @@
     <row r="78" ht="24.75" customHeight="1">
       <c r="A78" s="26"/>
       <c r="B78" s="19" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C78" s="20"/>
       <c r="D78" s="37"/>
@@ -6545,22 +6525,22 @@
     <row r="79" ht="24.75" customHeight="1">
       <c r="A79" s="26"/>
       <c r="B79" s="26" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D79" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E79" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F79" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G79" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H79" s="89" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="9"/>
@@ -6584,18 +6564,18 @@
     <row r="80" ht="24.75" customHeight="1">
       <c r="A80" s="26"/>
       <c r="B80" s="26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D80" s="53"/>
       <c r="E80" s="53"/>
       <c r="F80" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G80" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H80" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I80" s="9"/>
       <c r="J80" s="9"/>
@@ -6619,15 +6599,15 @@
     <row r="81" ht="24.75" customHeight="1">
       <c r="A81" s="26"/>
       <c r="B81" s="26" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D81" s="55"/>
       <c r="E81" s="55"/>
       <c r="F81" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G81" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H81" s="67"/>
       <c r="I81" s="9"/>
@@ -6652,18 +6632,18 @@
     <row r="82" ht="24.75" customHeight="1">
       <c r="A82" s="26"/>
       <c r="B82" s="90" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C82" s="34"/>
       <c r="D82" s="57"/>
       <c r="E82" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F82" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G82" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H82" s="36"/>
       <c r="I82" s="51"/>
@@ -6688,7 +6668,7 @@
     <row r="83" ht="24.75" customHeight="1">
       <c r="A83" s="26"/>
       <c r="B83" s="90" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C83" s="34"/>
       <c r="D83" s="57"/>
@@ -6696,7 +6676,7 @@
       <c r="F83" s="57"/>
       <c r="G83" s="57"/>
       <c r="H83" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I83" s="51"/>
       <c r="J83" s="9"/>
@@ -6720,21 +6700,21 @@
     <row r="84" ht="24.75" customHeight="1">
       <c r="A84" s="26"/>
       <c r="B84" s="90" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C84" s="34"/>
       <c r="D84" s="57"/>
       <c r="E84" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F84" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G84" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H84" s="89" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I84" s="51"/>
       <c r="J84" s="9"/>
@@ -6758,23 +6738,23 @@
     <row r="85" ht="24.75" customHeight="1">
       <c r="A85" s="26"/>
       <c r="B85" s="90" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C85" s="34"/>
       <c r="D85" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E85" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F85" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G85" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H85" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I85" s="51"/>
       <c r="J85" s="9"/>
@@ -6798,7 +6778,7 @@
     <row r="86" ht="21.0" customHeight="1">
       <c r="A86" s="26"/>
       <c r="B86" s="33" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C86" s="34"/>
       <c r="D86" s="31">
@@ -6838,7 +6818,7 @@
     <row r="87" ht="21.0" customHeight="1">
       <c r="A87" s="26"/>
       <c r="B87" s="33" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C87" s="34"/>
       <c r="D87" s="31">
@@ -6854,7 +6834,7 @@
         <v>185.8</v>
       </c>
       <c r="H87" s="29" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="I87" s="9"/>
       <c r="J87" s="9"/>
@@ -6878,7 +6858,7 @@
     <row r="88" ht="21.0" customHeight="1">
       <c r="A88" s="26"/>
       <c r="B88" s="33" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="C88" s="34"/>
       <c r="D88" s="68">
@@ -6918,7 +6898,7 @@
     <row r="89" ht="21.0" customHeight="1">
       <c r="A89" s="26"/>
       <c r="B89" s="33" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C89" s="34"/>
       <c r="D89" s="31">
@@ -6958,7 +6938,7 @@
     <row r="90" ht="21.0" customHeight="1">
       <c r="A90" s="26"/>
       <c r="B90" s="33" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C90" s="34"/>
       <c r="D90" s="31">
@@ -6974,7 +6954,7 @@
         <v>60.5</v>
       </c>
       <c r="H90" s="29" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="I90" s="9"/>
       <c r="J90" s="9"/>
@@ -6998,7 +6978,7 @@
     <row r="91" ht="21.0" customHeight="1">
       <c r="A91" s="26"/>
       <c r="B91" s="33" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C91" s="34"/>
       <c r="D91" s="31">
@@ -7038,7 +7018,7 @@
     <row r="92" ht="21.0" customHeight="1">
       <c r="A92" s="26"/>
       <c r="B92" s="32" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C92" s="14"/>
       <c r="D92" s="71">
@@ -7054,7 +7034,7 @@
         <v>5.1</v>
       </c>
       <c r="H92" s="91" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="I92" s="9"/>
       <c r="J92" s="9"/>
@@ -7078,23 +7058,23 @@
     <row r="93" ht="21.0" customHeight="1">
       <c r="A93" s="26"/>
       <c r="B93" s="32" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C93" s="14"/>
       <c r="D93" s="71" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="E93" s="71" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F93" s="71" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G93" s="71" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="H93" s="91" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="I93" s="9"/>
       <c r="J93" s="9"/>
@@ -7118,7 +7098,7 @@
     <row r="94" ht="43.5" customHeight="1">
       <c r="A94" s="9"/>
       <c r="B94" s="92" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C94" s="59"/>
       <c r="D94" s="10"/>
@@ -7148,7 +7128,7 @@
     <row r="95" ht="31.5" customHeight="1">
       <c r="A95" s="9"/>
       <c r="B95" s="19" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C95" s="20"/>
       <c r="D95" s="37"/>
@@ -7178,13 +7158,13 @@
     <row r="96" ht="27.0" customHeight="1">
       <c r="A96" s="9"/>
       <c r="B96" s="26" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D96" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E96" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F96" s="24"/>
       <c r="G96" s="24"/>
@@ -7211,15 +7191,15 @@
     <row r="97" ht="27.0" customHeight="1">
       <c r="A97" s="9"/>
       <c r="B97" s="26" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D97" s="53"/>
       <c r="E97" s="53"/>
       <c r="F97" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G97" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H97" s="66"/>
       <c r="I97" s="9"/>
@@ -7244,14 +7224,14 @@
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="9"/>
       <c r="B98" s="26" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D98" s="53"/>
       <c r="E98" s="53"/>
       <c r="F98" s="53"/>
       <c r="G98" s="53"/>
       <c r="H98" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I98" s="9"/>
       <c r="J98" s="9"/>
@@ -7275,14 +7255,14 @@
     <row r="99" ht="24.75" customHeight="1">
       <c r="A99" s="9"/>
       <c r="B99" s="26" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D99" s="53"/>
       <c r="E99" s="53"/>
       <c r="F99" s="53"/>
       <c r="G99" s="53"/>
       <c r="H99" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I99" s="9"/>
       <c r="J99" s="9"/>
@@ -7306,15 +7286,15 @@
     <row r="100" ht="24.75" customHeight="1">
       <c r="A100" s="9"/>
       <c r="B100" s="26" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D100" s="53"/>
       <c r="E100" s="53"/>
       <c r="F100" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G100" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H100" s="66"/>
       <c r="I100" s="9"/>
@@ -7339,13 +7319,13 @@
     <row r="101" ht="24.75" customHeight="1">
       <c r="A101" s="9"/>
       <c r="B101" s="26" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D101" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E101" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F101" s="53"/>
       <c r="G101" s="53"/>
@@ -7372,18 +7352,18 @@
     <row r="102" ht="24.75" customHeight="1">
       <c r="A102" s="9"/>
       <c r="B102" s="26" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D102" s="53"/>
       <c r="E102" s="53"/>
       <c r="F102" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G102" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H102" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I102" s="9"/>
       <c r="J102" s="9"/>
@@ -7407,15 +7387,15 @@
     <row r="103" ht="24.75" customHeight="1">
       <c r="A103" s="9"/>
       <c r="B103" s="26" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D103" s="53"/>
       <c r="E103" s="53"/>
       <c r="F103" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G103" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H103" s="66"/>
       <c r="I103" s="9"/>
@@ -7440,22 +7420,22 @@
     <row r="104" ht="24.75" customHeight="1">
       <c r="A104" s="9"/>
       <c r="B104" s="26" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D104" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E104" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F104" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G104" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H104" s="67" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I104" s="9"/>
       <c r="J104" s="9"/>
@@ -7479,7 +7459,7 @@
     <row r="105" ht="30.75" customHeight="1">
       <c r="A105" s="9"/>
       <c r="B105" s="19" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C105" s="20"/>
       <c r="D105" s="37"/>
@@ -7509,23 +7489,23 @@
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="9"/>
       <c r="B106" s="94" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C106" s="14"/>
       <c r="D106" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E106" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F106" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G106" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H106" s="67" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I106" s="9"/>
       <c r="J106" s="9"/>
@@ -7549,18 +7529,18 @@
     <row r="107" ht="31.5" customHeight="1">
       <c r="A107" s="9"/>
       <c r="B107" s="26" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D107" s="88"/>
       <c r="E107" s="88"/>
       <c r="F107" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G107" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H107" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I107" s="9"/>
       <c r="J107" s="9"/>
@@ -7584,7 +7564,7 @@
     <row r="108" ht="43.5" customHeight="1">
       <c r="A108" s="9"/>
       <c r="B108" s="19" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C108" s="20"/>
       <c r="D108" s="37"/>
@@ -7614,18 +7594,18 @@
     <row r="109" ht="24.75" customHeight="1">
       <c r="A109" s="9"/>
       <c r="B109" s="26" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D109" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E109" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F109" s="88"/>
       <c r="G109" s="88"/>
       <c r="H109" s="89" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I109" s="9"/>
       <c r="J109" s="9"/>
@@ -7649,15 +7629,15 @@
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="9"/>
       <c r="B110" s="26" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D110" s="88"/>
       <c r="E110" s="88"/>
       <c r="F110" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G110" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H110" s="66"/>
       <c r="I110" s="9"/>
@@ -7682,22 +7662,22 @@
     <row r="111" ht="24.75" customHeight="1">
       <c r="A111" s="9"/>
       <c r="B111" s="26" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D111" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E111" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F111" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G111" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H111" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I111" s="9"/>
       <c r="J111" s="9"/>
@@ -7721,22 +7701,22 @@
     <row r="112" ht="24.75" customHeight="1">
       <c r="A112" s="9"/>
       <c r="B112" s="26" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D112" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E112" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F112" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G112" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H112" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I112" s="9"/>
       <c r="J112" s="9"/>
@@ -7760,12 +7740,12 @@
     <row r="113" ht="24.75" customHeight="1">
       <c r="A113" s="9"/>
       <c r="B113" s="26" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D113" s="53"/>
       <c r="E113" s="53"/>
       <c r="F113" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G113" s="53"/>
       <c r="H113" s="67"/>
@@ -7791,7 +7771,7 @@
     <row r="114" ht="27.75" customHeight="1">
       <c r="A114" s="9"/>
       <c r="B114" s="19" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C114" s="20"/>
       <c r="D114" s="37"/>
@@ -7821,22 +7801,22 @@
     <row r="115" ht="27.0" customHeight="1">
       <c r="A115" s="9"/>
       <c r="B115" s="26" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="D115" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E115" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F115" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G115" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H115" s="89" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I115" s="9"/>
       <c r="J115" s="9"/>
@@ -7860,22 +7840,22 @@
     <row r="116" ht="27.0" customHeight="1">
       <c r="A116" s="9"/>
       <c r="B116" s="26" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D116" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E116" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F116" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G116" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H116" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I116" s="9"/>
       <c r="J116" s="9"/>
@@ -7899,23 +7879,23 @@
     <row r="117" ht="27.0" customHeight="1">
       <c r="A117" s="9"/>
       <c r="B117" s="39" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="C117" s="14"/>
       <c r="D117" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E117" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F117" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G117" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H117" s="67" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I117" s="9"/>
       <c r="J117" s="9"/>
@@ -7939,21 +7919,21 @@
     <row r="118" ht="27.0" customHeight="1">
       <c r="A118" s="9"/>
       <c r="B118" s="39" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="C118" s="14"/>
       <c r="D118" s="55"/>
       <c r="E118" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F118" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G118" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H118" s="67" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I118" s="9"/>
       <c r="J118" s="9"/>
@@ -7977,18 +7957,18 @@
     <row r="119" ht="27.0" customHeight="1">
       <c r="A119" s="9"/>
       <c r="B119" s="39" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C119" s="14"/>
       <c r="D119" s="35"/>
       <c r="E119" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F119" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G119" s="55" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H119" s="36"/>
       <c r="I119" s="9"/>
@@ -8013,7 +7993,7 @@
     <row r="120" ht="27.0" customHeight="1">
       <c r="A120" s="9"/>
       <c r="B120" s="39" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="C120" s="14"/>
       <c r="D120" s="35"/>
@@ -8021,7 +8001,7 @@
       <c r="F120" s="55"/>
       <c r="G120" s="55"/>
       <c r="H120" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I120" s="9"/>
       <c r="J120" s="9"/>
@@ -8045,23 +8025,23 @@
     <row r="121" ht="25.5" customHeight="1">
       <c r="A121" s="9"/>
       <c r="B121" s="69" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="C121" s="34"/>
       <c r="D121" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E121" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F121" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G121" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H121" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I121" s="51"/>
       <c r="J121" s="9"/>
@@ -8085,21 +8065,21 @@
     <row r="122" ht="25.5" customHeight="1">
       <c r="A122" s="9"/>
       <c r="B122" s="69" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="C122" s="34"/>
       <c r="D122" s="57"/>
       <c r="E122" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F122" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G122" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H122" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I122" s="51"/>
       <c r="J122" s="9"/>
@@ -8122,24 +8102,24 @@
     </row>
     <row r="123" ht="25.5" customHeight="1">
       <c r="A123" s="69" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B123" s="34"/>
       <c r="C123" s="34"/>
       <c r="D123" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E123" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F123" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G123" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H123" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="9"/>
@@ -8163,23 +8143,23 @@
     <row r="124" ht="25.5" customHeight="1">
       <c r="A124" s="9"/>
       <c r="B124" s="69" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C124" s="34"/>
       <c r="D124" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E124" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F124" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G124" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H124" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I124" s="9"/>
       <c r="J124" s="9"/>
@@ -8203,11 +8183,11 @@
     <row r="125" ht="25.5" customHeight="1">
       <c r="A125" s="9"/>
       <c r="B125" s="69" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C125" s="34"/>
       <c r="D125" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E125" s="57"/>
       <c r="F125" s="57"/>
@@ -8235,18 +8215,18 @@
     <row r="126" ht="25.5" customHeight="1">
       <c r="A126" s="9"/>
       <c r="B126" s="69" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C126" s="34"/>
       <c r="D126" s="57"/>
       <c r="E126" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F126" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G126" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H126" s="36"/>
       <c r="I126" s="9"/>
@@ -8271,7 +8251,7 @@
     <row r="127" ht="25.5" customHeight="1">
       <c r="A127" s="9"/>
       <c r="B127" s="69" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="C127" s="34"/>
       <c r="D127" s="57"/>
@@ -8279,7 +8259,7 @@
       <c r="F127" s="57"/>
       <c r="G127" s="57"/>
       <c r="H127" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I127" s="74"/>
       <c r="J127" s="74"/>
@@ -8302,24 +8282,24 @@
     </row>
     <row r="128" ht="43.5" customHeight="1">
       <c r="A128" s="69" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B128" s="34"/>
       <c r="C128" s="34"/>
       <c r="D128" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E128" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F128" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G128" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H128" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I128" s="74"/>
       <c r="J128" s="74"/>
@@ -8343,7 +8323,7 @@
     <row r="129" ht="21.75" customHeight="1">
       <c r="A129" s="79"/>
       <c r="B129" s="19" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="C129" s="20"/>
       <c r="D129" s="37"/>
@@ -8373,7 +8353,7 @@
     <row r="130" ht="21.75" customHeight="1">
       <c r="A130" s="26"/>
       <c r="B130" s="26" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D130" s="95">
         <v>37.6</v>
@@ -8412,7 +8392,7 @@
     <row r="131" ht="21.75" customHeight="1">
       <c r="A131" s="26"/>
       <c r="B131" s="26" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D131" s="97">
         <v>36.4</v>
@@ -8451,7 +8431,7 @@
     <row r="132" ht="21.75" customHeight="1">
       <c r="A132" s="79"/>
       <c r="B132" s="19" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="C132" s="20"/>
       <c r="D132" s="60"/>
@@ -8481,7 +8461,7 @@
     <row r="133" ht="21.75" customHeight="1">
       <c r="A133" s="26"/>
       <c r="B133" s="26" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D133" s="95">
         <v>42.3</v>
@@ -8520,7 +8500,7 @@
     <row r="134" ht="21.75" customHeight="1">
       <c r="A134" s="26"/>
       <c r="B134" s="26" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D134" s="97">
         <v>37.4</v>
@@ -8559,7 +8539,7 @@
     <row r="135" ht="21.75" customHeight="1">
       <c r="A135" s="79"/>
       <c r="B135" s="19" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="C135" s="20"/>
       <c r="D135" s="60"/>
@@ -8589,7 +8569,7 @@
     <row r="136" ht="21.75" customHeight="1">
       <c r="A136" s="26"/>
       <c r="B136" s="26" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D136" s="95">
         <v>57.0</v>
@@ -8628,7 +8608,7 @@
     <row r="137" ht="21.75" customHeight="1">
       <c r="A137" s="26"/>
       <c r="B137" s="26" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D137" s="97">
         <v>56.0</v>
@@ -8667,7 +8647,7 @@
     <row r="138" ht="21.75" customHeight="1">
       <c r="A138" s="79"/>
       <c r="B138" s="19" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C138" s="20"/>
       <c r="D138" s="60"/>
@@ -8697,7 +8677,7 @@
     <row r="139" ht="21.75" customHeight="1">
       <c r="A139" s="26"/>
       <c r="B139" s="26" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="D139" s="95">
         <v>54.3</v>
@@ -8736,7 +8716,7 @@
     <row r="140" ht="21.75" customHeight="1">
       <c r="A140" s="26"/>
       <c r="B140" s="26" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="D140" s="97">
         <v>48.9</v>
@@ -8775,7 +8755,7 @@
     <row r="141" ht="27.75" customHeight="1">
       <c r="A141" s="9"/>
       <c r="B141" s="19" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="C141" s="20"/>
       <c r="D141" s="60">
@@ -8815,7 +8795,7 @@
     <row r="142" ht="33.75" customHeight="1">
       <c r="A142" s="9"/>
       <c r="B142" s="33" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C142" s="34"/>
       <c r="D142" s="68">
@@ -8855,7 +8835,7 @@
     <row r="143" ht="31.5" customHeight="1">
       <c r="A143" s="9"/>
       <c r="B143" s="69" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C143" s="34"/>
       <c r="D143" s="31">
@@ -8895,7 +8875,7 @@
     <row r="144" ht="43.5" customHeight="1">
       <c r="A144" s="74"/>
       <c r="B144" s="100" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="C144" s="10"/>
       <c r="D144" s="10"/>
@@ -8926,7 +8906,7 @@
       <c r="A145" s="74"/>
       <c r="B145" s="101"/>
       <c r="C145" s="101" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D145" s="102"/>
       <c r="E145" s="102"/>
@@ -8956,13 +8936,13 @@
       <c r="A146" s="74"/>
       <c r="B146" s="9"/>
       <c r="C146" s="26" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="D146" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E146" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F146" s="24"/>
       <c r="G146" s="24"/>
@@ -8990,18 +8970,18 @@
       <c r="A147" s="74"/>
       <c r="B147" s="9"/>
       <c r="C147" s="81" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="D147" s="24"/>
       <c r="E147" s="44"/>
       <c r="F147" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G147" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H147" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I147" s="74"/>
       <c r="J147" s="74"/>
@@ -9026,7 +9006,7 @@
       <c r="A148" s="74"/>
       <c r="B148" s="9"/>
       <c r="C148" s="26" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D148" s="24">
         <v>8.0</v>
@@ -9066,22 +9046,22 @@
       <c r="A149" s="9"/>
       <c r="B149" s="9"/>
       <c r="C149" s="26" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="D149" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E149" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F149" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G149" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H149" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I149" s="74"/>
       <c r="J149" s="74"/>
@@ -9106,18 +9086,18 @@
       <c r="A150" s="9"/>
       <c r="B150" s="9"/>
       <c r="C150" s="26" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D150" s="53"/>
       <c r="E150" s="53"/>
       <c r="F150" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G150" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H150" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I150" s="74"/>
       <c r="J150" s="74"/>
@@ -9142,13 +9122,13 @@
       <c r="A151" s="9"/>
       <c r="B151" s="9"/>
       <c r="C151" s="26" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D151" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E151" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F151" s="53"/>
       <c r="G151" s="53"/>
@@ -9176,22 +9156,22 @@
       <c r="A152" s="9"/>
       <c r="B152" s="9"/>
       <c r="C152" s="26" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D152" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E152" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F152" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G152" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H152" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I152" s="9"/>
       <c r="J152" s="9"/>
@@ -9216,19 +9196,19 @@
       <c r="A153" s="9"/>
       <c r="B153" s="9"/>
       <c r="C153" s="26" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D153" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E153" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F153" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G153" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H153" s="66"/>
       <c r="I153" s="9"/>
@@ -9254,22 +9234,22 @@
       <c r="A154" s="9"/>
       <c r="B154" s="9"/>
       <c r="C154" s="26" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D154" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E154" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F154" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G154" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H154" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I154" s="9"/>
       <c r="J154" s="9"/>
@@ -9294,18 +9274,18 @@
       <c r="A155" s="9"/>
       <c r="B155" s="9"/>
       <c r="C155" s="26" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="D155" s="53"/>
       <c r="E155" s="53"/>
       <c r="F155" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G155" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H155" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I155" s="9"/>
       <c r="J155" s="9"/>
@@ -9330,18 +9310,18 @@
       <c r="A156" s="9"/>
       <c r="B156" s="9"/>
       <c r="C156" s="104" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D156" s="53"/>
       <c r="E156" s="53"/>
       <c r="F156" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G156" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H156" s="67" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I156" s="9"/>
       <c r="J156" s="9"/>
@@ -9365,23 +9345,23 @@
     <row r="157" ht="24.0" customHeight="1">
       <c r="A157" s="9"/>
       <c r="B157" s="69" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="C157" s="34"/>
       <c r="D157" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E157" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F157" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G157" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H157" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I157" s="9"/>
       <c r="J157" s="9"/>
@@ -9405,23 +9385,23 @@
     <row r="158" ht="24.0" customHeight="1">
       <c r="A158" s="9"/>
       <c r="B158" s="105" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="C158" s="63"/>
       <c r="D158" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E158" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F158" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G158" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H158" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I158" s="9"/>
       <c r="J158" s="9"/>
@@ -9445,19 +9425,19 @@
     <row r="159" ht="24.0" customHeight="1">
       <c r="A159" s="9"/>
       <c r="B159" s="69" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="C159" s="34"/>
       <c r="D159" s="57"/>
       <c r="E159" s="57"/>
       <c r="F159" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G159" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H159" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I159" s="9"/>
       <c r="J159" s="9"/>
@@ -9481,7 +9461,7 @@
     <row r="160" ht="24.0" customHeight="1">
       <c r="A160" s="9"/>
       <c r="B160" s="27" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D160" s="37"/>
       <c r="E160" s="37"/>
@@ -9511,22 +9491,22 @@
       <c r="A161" s="9"/>
       <c r="B161" s="106"/>
       <c r="C161" s="81" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="D161" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E161" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F161" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G161" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H161" s="89" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I161" s="50"/>
       <c r="J161" s="9"/>
@@ -9551,22 +9531,22 @@
       <c r="A162" s="9"/>
       <c r="B162" s="106"/>
       <c r="C162" s="81" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="D162" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E162" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F162" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G162" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H162" s="89" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I162" s="50"/>
       <c r="J162" s="9"/>
@@ -9591,22 +9571,22 @@
       <c r="A163" s="9"/>
       <c r="B163" s="106"/>
       <c r="C163" s="26" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D163" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E163" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F163" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G163" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H163" s="67" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I163" s="50"/>
       <c r="J163" s="9"/>
@@ -9630,16 +9610,16 @@
     <row r="164" ht="34.5" customHeight="1">
       <c r="A164" s="9"/>
       <c r="B164" s="69" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C164" s="34"/>
       <c r="D164" s="57"/>
       <c r="E164" s="57"/>
       <c r="F164" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G164" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H164" s="36"/>
       <c r="I164" s="9"/>
@@ -9664,16 +9644,16 @@
     <row r="165" ht="36.0" customHeight="1">
       <c r="A165" s="9"/>
       <c r="B165" s="69" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C165" s="34"/>
       <c r="D165" s="57"/>
       <c r="E165" s="31"/>
       <c r="F165" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G165" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H165" s="36"/>
       <c r="I165" s="9"/>
@@ -9698,16 +9678,16 @@
     <row r="166" ht="34.5" customHeight="1">
       <c r="A166" s="9"/>
       <c r="B166" s="69" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C166" s="34"/>
       <c r="D166" s="57"/>
       <c r="E166" s="31"/>
       <c r="F166" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G166" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H166" s="107"/>
       <c r="I166" s="9"/>
@@ -9732,7 +9712,7 @@
     <row r="167" ht="43.5" customHeight="1">
       <c r="A167" s="9"/>
       <c r="B167" s="10" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C167" s="10"/>
       <c r="D167" s="10"/>
@@ -9763,7 +9743,7 @@
       <c r="A168" s="9"/>
       <c r="B168" s="41"/>
       <c r="C168" s="19" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="D168" s="37"/>
       <c r="E168" s="37"/>
@@ -9793,22 +9773,22 @@
       <c r="A169" s="9"/>
       <c r="B169" s="108"/>
       <c r="C169" s="81" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D169" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E169" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F169" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G169" s="88" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H169" s="89" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I169" s="9"/>
       <c r="J169" s="9"/>
@@ -9832,22 +9812,22 @@
     <row r="170" ht="37.5" customHeight="1">
       <c r="A170" s="9"/>
       <c r="B170" s="81" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D170" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E170" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F170" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G170" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H170" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I170" s="51"/>
       <c r="J170" s="9"/>
@@ -9871,16 +9851,16 @@
     <row r="171" ht="40.5" customHeight="1">
       <c r="A171" s="9"/>
       <c r="B171" s="26" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D171" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E171" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F171" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G171" s="53"/>
       <c r="H171" s="66"/>
@@ -9906,22 +9886,22 @@
     <row r="172" ht="40.5" customHeight="1">
       <c r="A172" s="9"/>
       <c r="B172" s="81" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D172" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E172" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F172" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G172" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H172" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I172" s="51"/>
       <c r="J172" s="9"/>
@@ -9945,22 +9925,22 @@
     <row r="173" ht="36.0" customHeight="1">
       <c r="A173" s="9"/>
       <c r="B173" s="81" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D173" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E173" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F173" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G173" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H173" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I173" s="51"/>
       <c r="J173" s="9"/>
@@ -9985,16 +9965,16 @@
       <c r="A174" s="9"/>
       <c r="B174" s="81"/>
       <c r="C174" s="81" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D174" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E174" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F174" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G174" s="53"/>
       <c r="H174" s="66"/>
@@ -10021,22 +10001,22 @@
       <c r="A175" s="9"/>
       <c r="B175" s="81"/>
       <c r="C175" s="81" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D175" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E175" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F175" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G175" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H175" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I175" s="51"/>
       <c r="J175" s="9"/>
@@ -10061,22 +10041,22 @@
       <c r="A176" s="9"/>
       <c r="B176" s="26"/>
       <c r="C176" s="26" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D176" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E176" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F176" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G176" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H176" s="66" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I176" s="51"/>
       <c r="J176" s="9"/>
@@ -10101,22 +10081,22 @@
       <c r="A177" s="9"/>
       <c r="B177" s="26"/>
       <c r="C177" s="26" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D177" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E177" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F177" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G177" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H177" s="109" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I177" s="51"/>
       <c r="J177" s="9"/>
@@ -10141,22 +10121,22 @@
       <c r="A178" s="9"/>
       <c r="B178" s="26"/>
       <c r="C178" s="26" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D178" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E178" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F178" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G178" s="53" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H178" s="109" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I178" s="51"/>
       <c r="J178" s="9"/>
@@ -10180,22 +10160,22 @@
     <row r="179" ht="31.5" customHeight="1">
       <c r="A179" s="9"/>
       <c r="B179" s="81" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D179" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E179" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F179" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G179" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H179" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I179" s="51"/>
       <c r="J179" s="9"/>
@@ -10219,22 +10199,22 @@
     <row r="180" ht="36.0" customHeight="1">
       <c r="A180" s="9"/>
       <c r="B180" s="81" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D180" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E180" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F180" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G180" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H180" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I180" s="51"/>
       <c r="J180" s="9"/>
@@ -10259,16 +10239,16 @@
       <c r="A181" s="9"/>
       <c r="B181" s="81"/>
       <c r="C181" s="110" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D181" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E181" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F181" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G181" s="83"/>
       <c r="H181" s="84"/>
@@ -10294,22 +10274,22 @@
     <row r="182" ht="25.5" customHeight="1">
       <c r="A182" s="9"/>
       <c r="B182" s="26" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="D182" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E182" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F182" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G182" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H182" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I182" s="51"/>
       <c r="J182" s="9"/>
@@ -10333,19 +10313,19 @@
     <row r="183" ht="25.5" customHeight="1">
       <c r="A183" s="9"/>
       <c r="B183" s="39" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="C183" s="14"/>
       <c r="D183" s="80"/>
       <c r="E183" s="80"/>
       <c r="F183" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G183" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H183" s="87" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I183" s="51"/>
       <c r="J183" s="9"/>
@@ -10370,7 +10350,7 @@
       <c r="A184" s="9"/>
       <c r="B184" s="26"/>
       <c r="C184" s="27" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="D184" s="37"/>
       <c r="E184" s="37"/>
@@ -10399,22 +10379,22 @@
     <row r="185" ht="33.0" customHeight="1">
       <c r="A185" s="9"/>
       <c r="B185" s="26" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D185" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E185" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F185" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G185" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H185" s="82" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I185" s="9"/>
       <c r="J185" s="9"/>
@@ -10438,19 +10418,19 @@
     <row r="186" ht="25.5" customHeight="1">
       <c r="A186" s="9"/>
       <c r="B186" s="39" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C186" s="14"/>
       <c r="D186" s="35"/>
       <c r="E186" s="86"/>
       <c r="F186" s="86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G186" s="86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H186" s="87" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I186" s="51"/>
       <c r="J186" s="9"/>
@@ -10475,7 +10455,7 @@
       <c r="A187" s="9"/>
       <c r="B187" s="111"/>
       <c r="C187" s="19" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D187" s="37"/>
       <c r="E187" s="37"/>
@@ -10505,18 +10485,18 @@
       <c r="A188" s="9"/>
       <c r="B188" s="26"/>
       <c r="C188" s="113" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D188" s="83"/>
       <c r="E188" s="83"/>
       <c r="F188" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G188" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H188" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I188" s="9"/>
       <c r="J188" s="9"/>
@@ -10540,22 +10520,22 @@
     <row r="189" ht="25.5" customHeight="1">
       <c r="A189" s="9"/>
       <c r="B189" s="26" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D189" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E189" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F189" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G189" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H189" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I189" s="51"/>
       <c r="J189" s="9"/>
@@ -10580,22 +10560,22 @@
       <c r="A190" s="9"/>
       <c r="B190" s="26"/>
       <c r="C190" s="113" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D190" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E190" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F190" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G190" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H190" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I190" s="9"/>
       <c r="J190" s="9"/>
@@ -10619,23 +10599,23 @@
     <row r="191" ht="25.5" customHeight="1">
       <c r="A191" s="9"/>
       <c r="B191" s="39" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C191" s="14"/>
       <c r="D191" s="86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E191" s="86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F191" s="86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G191" s="86" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H191" s="87" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I191" s="9"/>
       <c r="J191" s="9"/>
@@ -10659,7 +10639,7 @@
     <row r="192" ht="25.5" customHeight="1">
       <c r="A192" s="9"/>
       <c r="B192" s="19" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C192" s="20"/>
       <c r="D192" s="37"/>
@@ -10689,22 +10669,22 @@
     <row r="193" ht="34.5" customHeight="1">
       <c r="A193" s="9"/>
       <c r="B193" s="26" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D193" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E193" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F193" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G193" s="80" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H193" s="82" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I193" s="9"/>
       <c r="J193" s="9"/>
@@ -10729,22 +10709,22 @@
       <c r="A194" s="9"/>
       <c r="B194" s="108"/>
       <c r="C194" s="113" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D194" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E194" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F194" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G194" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H194" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I194" s="51"/>
       <c r="J194" s="9"/>
@@ -10769,22 +10749,22 @@
       <c r="A195" s="9"/>
       <c r="B195" s="108"/>
       <c r="C195" s="26" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D195" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E195" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F195" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G195" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H195" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I195" s="51"/>
       <c r="J195" s="9"/>
@@ -10809,22 +10789,22 @@
       <c r="A196" s="9"/>
       <c r="B196" s="108"/>
       <c r="C196" s="26" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D196" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E196" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F196" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G196" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H196" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I196" s="51"/>
       <c r="J196" s="9"/>
@@ -10849,22 +10829,22 @@
       <c r="A197" s="9"/>
       <c r="B197" s="108"/>
       <c r="C197" s="26" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D197" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E197" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F197" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G197" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H197" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I197" s="51"/>
       <c r="J197" s="9"/>
@@ -10889,22 +10869,22 @@
       <c r="A198" s="9"/>
       <c r="B198" s="108"/>
       <c r="C198" s="26" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D198" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E198" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F198" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G198" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H198" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I198" s="51"/>
       <c r="J198" s="9"/>
@@ -10929,22 +10909,22 @@
       <c r="A199" s="9"/>
       <c r="B199" s="108"/>
       <c r="C199" s="26" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D199" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E199" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F199" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G199" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H199" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I199" s="51"/>
       <c r="J199" s="9"/>
@@ -10968,22 +10948,22 @@
     <row r="200" ht="39.0" customHeight="1">
       <c r="A200" s="9"/>
       <c r="B200" s="26" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D200" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E200" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F200" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G200" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H200" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I200" s="9"/>
       <c r="J200" s="9"/>
@@ -11008,22 +10988,22 @@
       <c r="A201" s="9"/>
       <c r="B201" s="27"/>
       <c r="C201" s="26" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D201" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E201" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F201" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G201" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H201" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I201" s="9"/>
       <c r="J201" s="9"/>
@@ -11048,22 +11028,22 @@
       <c r="A202" s="9"/>
       <c r="B202" s="27"/>
       <c r="C202" s="26" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D202" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E202" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F202" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G202" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H202" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I202" s="9"/>
       <c r="J202" s="9"/>
@@ -11088,22 +11068,22 @@
       <c r="A203" s="9"/>
       <c r="B203" s="27"/>
       <c r="C203" s="26" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D203" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E203" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F203" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G203" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H203" s="84" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I203" s="9"/>
       <c r="J203" s="9"/>
@@ -11127,22 +11107,22 @@
     <row r="204" ht="43.5" customHeight="1">
       <c r="A204" s="9"/>
       <c r="B204" s="26" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D204" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E204" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F204" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G204" s="83" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H204" s="114" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I204" s="9"/>
       <c r="J204" s="9"/>
@@ -11166,7 +11146,7 @@
     <row r="205" ht="43.5" customHeight="1">
       <c r="A205" s="9"/>
       <c r="B205" s="115" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="C205" s="59"/>
       <c r="D205" s="59"/>
@@ -11196,23 +11176,23 @@
     <row r="206" ht="51.75" customHeight="1">
       <c r="A206" s="116"/>
       <c r="B206" s="69" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C206" s="34"/>
       <c r="D206" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E206" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F206" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G206" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H206" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I206" s="116"/>
       <c r="J206" s="116"/>
@@ -11236,23 +11216,23 @@
     <row r="207" ht="54.0" customHeight="1">
       <c r="A207" s="116"/>
       <c r="B207" s="69" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="C207" s="34"/>
       <c r="D207" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E207" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F207" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G207" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H207" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I207" s="116"/>
       <c r="J207" s="116"/>
@@ -11276,23 +11256,23 @@
     <row r="208" ht="43.5" customHeight="1">
       <c r="A208" s="116"/>
       <c r="B208" s="69" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="C208" s="34"/>
       <c r="D208" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E208" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F208" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G208" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H208" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I208" s="116"/>
       <c r="J208" s="116"/>
@@ -11316,23 +11296,23 @@
     <row r="209" ht="58.5" customHeight="1">
       <c r="A209" s="116"/>
       <c r="B209" s="69" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="C209" s="34"/>
       <c r="D209" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E209" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F209" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G209" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H209" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I209" s="116"/>
       <c r="J209" s="116"/>
@@ -11356,23 +11336,23 @@
     <row r="210" ht="55.5" customHeight="1">
       <c r="A210" s="116"/>
       <c r="B210" s="69" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C210" s="34"/>
       <c r="D210" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E210" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F210" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G210" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H210" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I210" s="116"/>
       <c r="J210" s="116"/>
@@ -11396,23 +11376,23 @@
     <row r="211" ht="43.5" customHeight="1">
       <c r="A211" s="116"/>
       <c r="B211" s="69" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="C211" s="34"/>
       <c r="D211" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E211" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="F211" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="G211" s="57" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="H211" s="36" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="I211" s="116"/>
       <c r="J211" s="116"/>
@@ -11436,7 +11416,7 @@
     <row r="212" ht="90.75" customHeight="1">
       <c r="A212" s="116"/>
       <c r="B212" s="117" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="C212" s="118"/>
       <c r="D212" s="57"/>
@@ -33529,25 +33509,104 @@
     </row>
   </sheetData>
   <mergeCells count="203">
-    <mergeCell ref="B112:C112"/>
-    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B38:C38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="B47:C47"/>
+    <mergeCell ref="B48:C48"/>
+    <mergeCell ref="B49:C49"/>
+    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="B57:C57"/>
+    <mergeCell ref="B58:C58"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="B63:C63"/>
+    <mergeCell ref="B64:C64"/>
+    <mergeCell ref="B65:C65"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="B68:C68"/>
+    <mergeCell ref="B69:C69"/>
+    <mergeCell ref="B70:C70"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="B73:C73"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="B75:C75"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="B77:C77"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B88:C88"/>
+    <mergeCell ref="B89:C89"/>
     <mergeCell ref="B90:C90"/>
     <mergeCell ref="B91:C91"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="B93:C93"/>
     <mergeCell ref="B94:C94"/>
     <mergeCell ref="B95:C95"/>
-    <mergeCell ref="B114:C114"/>
-    <mergeCell ref="B104:C104"/>
-    <mergeCell ref="B107:C107"/>
-    <mergeCell ref="B137:C137"/>
-    <mergeCell ref="B139:C139"/>
-    <mergeCell ref="B126:C126"/>
-    <mergeCell ref="B127:C127"/>
-    <mergeCell ref="B130:C130"/>
-    <mergeCell ref="B131:C131"/>
-    <mergeCell ref="B133:C133"/>
-    <mergeCell ref="B134:C134"/>
-    <mergeCell ref="B136:C136"/>
-    <mergeCell ref="B166:C166"/>
+    <mergeCell ref="B96:C96"/>
+    <mergeCell ref="B97:C97"/>
+    <mergeCell ref="B98:C98"/>
+    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="B100:C100"/>
+    <mergeCell ref="B101:C101"/>
     <mergeCell ref="B170:C170"/>
     <mergeCell ref="B171:C171"/>
     <mergeCell ref="B172:C172"/>
@@ -33568,26 +33627,6 @@
     <mergeCell ref="B206:C206"/>
     <mergeCell ref="B207:C207"/>
     <mergeCell ref="B208:C208"/>
-    <mergeCell ref="B73:C73"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="B115:C115"/>
-    <mergeCell ref="B116:C116"/>
-    <mergeCell ref="B117:C117"/>
-    <mergeCell ref="B118:C118"/>
-    <mergeCell ref="B119:C119"/>
-    <mergeCell ref="B120:C120"/>
-    <mergeCell ref="B121:C121"/>
-    <mergeCell ref="B143:C143"/>
-    <mergeCell ref="B142:C142"/>
-    <mergeCell ref="B157:C157"/>
-    <mergeCell ref="B158:C158"/>
-    <mergeCell ref="B159:C159"/>
-    <mergeCell ref="B160:C160"/>
-    <mergeCell ref="B164:C164"/>
-    <mergeCell ref="B165:C165"/>
-    <mergeCell ref="B140:C140"/>
     <mergeCell ref="B209:C209"/>
     <mergeCell ref="B210:C210"/>
     <mergeCell ref="B211:C211"/>
@@ -33609,7 +33648,7 @@
     <mergeCell ref="A227:C227"/>
     <mergeCell ref="A228:C228"/>
     <mergeCell ref="A229:C229"/>
-    <mergeCell ref="A237:C237"/>
+    <mergeCell ref="A230:C230"/>
     <mergeCell ref="A238:C238"/>
     <mergeCell ref="A239:C239"/>
     <mergeCell ref="A240:C240"/>
@@ -33617,121 +33656,62 @@
     <mergeCell ref="A242:C242"/>
     <mergeCell ref="A243:C243"/>
     <mergeCell ref="A244:C244"/>
-    <mergeCell ref="A230:C230"/>
     <mergeCell ref="A231:C231"/>
     <mergeCell ref="A232:C232"/>
     <mergeCell ref="A233:C233"/>
     <mergeCell ref="A234:C234"/>
     <mergeCell ref="A235:C235"/>
     <mergeCell ref="A236:C236"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B38:C38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="B69:C69"/>
-    <mergeCell ref="B68:C68"/>
-    <mergeCell ref="B70:C70"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="B63:C63"/>
-    <mergeCell ref="B64:C64"/>
-    <mergeCell ref="B65:C65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B67:C67"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="B25:C25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="B57:C57"/>
-    <mergeCell ref="B58:C58"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="B48:C48"/>
-    <mergeCell ref="B49:C49"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="B47:C47"/>
-    <mergeCell ref="B50:C50"/>
-    <mergeCell ref="B51:C51"/>
-    <mergeCell ref="B52:C52"/>
-    <mergeCell ref="B75:C75"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="B82:C82"/>
-    <mergeCell ref="B83:C83"/>
-    <mergeCell ref="B84:C84"/>
-    <mergeCell ref="B85:C85"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B86:C86"/>
-    <mergeCell ref="B87:C87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="B77:C77"/>
-    <mergeCell ref="B96:C96"/>
-    <mergeCell ref="B97:C97"/>
-    <mergeCell ref="B98:C98"/>
-    <mergeCell ref="B99:C99"/>
-    <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B101:C101"/>
+    <mergeCell ref="A237:C237"/>
     <mergeCell ref="B102:C102"/>
     <mergeCell ref="B103:C103"/>
+    <mergeCell ref="B104:C104"/>
     <mergeCell ref="B105:C105"/>
     <mergeCell ref="B106:C106"/>
+    <mergeCell ref="B107:C107"/>
     <mergeCell ref="B108:C108"/>
     <mergeCell ref="B109:C109"/>
     <mergeCell ref="B110:C110"/>
     <mergeCell ref="B111:C111"/>
+    <mergeCell ref="B112:C112"/>
+    <mergeCell ref="B113:C113"/>
+    <mergeCell ref="B114:C114"/>
+    <mergeCell ref="B115:C115"/>
+    <mergeCell ref="B116:C116"/>
+    <mergeCell ref="B117:C117"/>
+    <mergeCell ref="B118:C118"/>
+    <mergeCell ref="B119:C119"/>
+    <mergeCell ref="B120:C120"/>
+    <mergeCell ref="B121:C121"/>
+    <mergeCell ref="B122:C122"/>
     <mergeCell ref="A123:C123"/>
-    <mergeCell ref="A128:C128"/>
     <mergeCell ref="B124:C124"/>
     <mergeCell ref="B125:C125"/>
+    <mergeCell ref="B126:C126"/>
+    <mergeCell ref="B127:C127"/>
+    <mergeCell ref="A128:C128"/>
     <mergeCell ref="B129:C129"/>
+    <mergeCell ref="B130:C130"/>
+    <mergeCell ref="B131:C131"/>
     <mergeCell ref="B132:C132"/>
+    <mergeCell ref="B133:C133"/>
+    <mergeCell ref="B134:C134"/>
     <mergeCell ref="B135:C135"/>
+    <mergeCell ref="B136:C136"/>
+    <mergeCell ref="B137:C137"/>
     <mergeCell ref="B138:C138"/>
+    <mergeCell ref="B139:C139"/>
+    <mergeCell ref="B140:C140"/>
     <mergeCell ref="B141:C141"/>
-    <mergeCell ref="B122:C122"/>
+    <mergeCell ref="B142:C142"/>
+    <mergeCell ref="B143:C143"/>
+    <mergeCell ref="B157:C157"/>
+    <mergeCell ref="B158:C158"/>
+    <mergeCell ref="B159:C159"/>
+    <mergeCell ref="B160:C160"/>
+    <mergeCell ref="B164:C164"/>
+    <mergeCell ref="B165:C165"/>
+    <mergeCell ref="B166:C166"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -33761,121 +33741,121 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="125" t="s">
+        <v>266</v>
+      </c>
+      <c r="B1" s="126" t="s">
+        <v>267</v>
+      </c>
+      <c r="C1" s="126" t="s">
+        <v>268</v>
+      </c>
+      <c r="D1" s="126" t="s">
+        <v>269</v>
+      </c>
+      <c r="E1" s="126" t="s">
+        <v>270</v>
+      </c>
+      <c r="F1" s="126" t="s">
         <v>271</v>
       </c>
-      <c r="B1" s="126" t="s">
+      <c r="G1" s="126" t="s">
         <v>272</v>
       </c>
-      <c r="C1" s="126" t="s">
+      <c r="H1" s="126" t="s">
         <v>273</v>
-      </c>
-      <c r="D1" s="126" t="s">
-        <v>274</v>
-      </c>
-      <c r="E1" s="126" t="s">
-        <v>275</v>
-      </c>
-      <c r="F1" s="126" t="s">
-        <v>276</v>
-      </c>
-      <c r="G1" s="126" t="s">
-        <v>277</v>
-      </c>
-      <c r="H1" s="126" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="2" ht="94.5" customHeight="1">
       <c r="A2" s="127" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B2" s="128">
         <v>168.0</v>
       </c>
       <c r="C2" s="129" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D2" s="128" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E2" s="128" t="s">
         <v>5</v>
       </c>
       <c r="F2" s="130" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="G2" s="131" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="H2" s="132" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="133" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B3" s="134" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C3" s="135" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D3" s="134" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E3" s="134" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F3" s="135" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G3" s="134" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="H3" s="136" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="137" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B4" s="137">
         <v>39.0</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D4" s="137" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E4" s="139" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="F4" s="137" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="G4" s="140" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H4" s="137" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="141"/>
       <c r="B5" s="141"/>
       <c r="C5" s="142" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D5" s="141"/>
       <c r="E5" s="143" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="F5" s="141"/>
       <c r="G5" s="132" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H5" s="141"/>
     </row>
@@ -33889,31 +33869,31 @@
       </c>
       <c r="F6" s="144"/>
       <c r="G6" s="132" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="H6" s="144"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="145" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B7" s="146">
         <v>44.0</v>
       </c>
       <c r="C7" s="146" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="D7" s="146" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E7" s="146" t="s">
         <v>5</v>
       </c>
       <c r="F7" s="146" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="G7" s="147" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="H7" s="148"/>
     </row>
@@ -33923,19 +33903,19 @@
         <v>23.0</v>
       </c>
       <c r="C8" s="151" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D8" s="145" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E8" s="145" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F8" s="151" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="G8" s="151" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" ht="30.75" customHeight="1">
@@ -33947,13 +33927,13 @@
         <v>0</v>
       </c>
       <c r="D9" s="145" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="E9" s="152" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="F9" s="153" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="G9" s="151" t="s">
         <v>2</v>
@@ -33966,7 +33946,7 @@
       <c r="D10" s="149"/>
       <c r="E10" s="149"/>
       <c r="F10" s="153" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G10" s="151" t="s">
         <v>3</v>
@@ -33979,7 +33959,7 @@
       <c r="D11" s="155"/>
       <c r="E11" s="155"/>
       <c r="F11" s="157" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G11" s="158" t="s">
         <v>4</v>
@@ -33987,48 +33967,48 @@
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="133" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B12" s="134" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C12" s="135" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D12" s="134" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E12" s="134" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F12" s="135" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G12" s="134" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="H12" s="136" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
     </row>
     <row r="13" ht="54.0" customHeight="1">
       <c r="A13" s="159" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B13" s="159">
         <v>181.0</v>
       </c>
       <c r="C13" s="160" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D13" s="159" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="E13" s="159" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="F13" s="161" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="G13" s="162"/>
       <c r="H13" s="163"/>

--- a/mock/input.xlsx
+++ b/mock/input.xlsx
@@ -36,7 +36,7 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhJgE5NxpnQ5BkLh1vsKOKy4LLNuw=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgQZsmnraVQ+gxlIEFzNjN9aisgUQ=="/>
     </ext>
   </extLst>
 </comments>
@@ -447,7 +447,7 @@
     <t>6th</t>
   </si>
   <si>
-    <t xml:space="preserve"> Light Weight Single-Mass Flywheel &gt;</t>
+    <t xml:space="preserve"> Light Weight Single-Mass Flywheel </t>
   </si>
   <si>
     <t>Helical Limited-Slip Differential</t>

--- a/mock/input.xlsx
+++ b/mock/input.xlsx
@@ -5,12 +5,15 @@
   <sheets>
     <sheet state="visible" name="specs" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="updates" sheetId="2" r:id="rId5"/>
+    <sheet state="visible" name="oneToMany" sheetId="3" r:id="rId6"/>
+    <sheet state="visible" name="explode" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="schema" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId6" roundtripDataChecksum="DSNHEJ4MnbttL070UEEwYlKSVaeH6Je3huQwIcDXGn4="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="Kgj4/vzLRQjenZlbhETpKJgQqdmdb4hXiaUalNDO9JQ="/>
     </ext>
   </extLst>
 </workbook>
@@ -36,14 +39,14 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgQZsmnraVQ+gxlIEFzNjN9aisgUQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7miv/0lytWTAkL1f4y65tH/v8Oh4VQ=="/>
     </ext>
   </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="346">
   <si>
     <t>Packages</t>
   </si>
@@ -2304,6 +2307,105 @@
   <si>
     <t>ADDED DISCLAIMER #237</t>
   </si>
+  <si>
+    <t>Componente</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Versión</t>
+  </si>
+  <si>
+    <t>Servicio Asociado</t>
+  </si>
+  <si>
+    <t>Base de Datos</t>
+  </si>
+  <si>
+    <t>Frontend</t>
+  </si>
+  <si>
+    <t>AuthService</t>
+  </si>
+  <si>
+    <t>Backend</t>
+  </si>
+  <si>
+    <t>v1.2</t>
+  </si>
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>UserService</t>
+  </si>
+  <si>
+    <t>v1.4</t>
+  </si>
+  <si>
+    <t>OrderService</t>
+  </si>
+  <si>
+    <t>v2.0</t>
+  </si>
+  <si>
+    <t>PaymentService</t>
+  </si>
+  <si>
+    <t>v1.8</t>
+  </si>
+  <si>
+    <t>NotificationService</t>
+  </si>
+  <si>
+    <t>v1.1</t>
+  </si>
+  <si>
+    <t>Keys</t>
+  </si>
+  <si>
+    <t>a|b|c</t>
+  </si>
+  <si>
+    <t>d|e|f</t>
+  </si>
+  <si>
+    <t>h|i</t>
+  </si>
+  <si>
+    <t>z</t>
+  </si>
+  <si>
+    <t>x|y</t>
+  </si>
+  <si>
+    <t>Component</t>
+  </si>
+  <si>
+    <t>Attribute Name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Database</t>
+  </si>
+  <si>
+    <t>UsersDB</t>
+  </si>
+  <si>
+    <t>Gateway</t>
+  </si>
+  <si>
+    <t>Stripe</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
 </sst>
 </file>
 
@@ -2314,7 +2416,7 @@
     <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -2449,6 +2551,12 @@
       <sz val="12.0"/>
       <color rgb="FFFFFF00"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -3002,7 +3110,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="178">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3513,6 +3621,12 @@
     <xf borderId="54" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -3526,6 +3640,18 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -38002,4 +38128,355 @@
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="4" max="4" width="19.38"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="176" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" s="176" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="176" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1" s="176" t="s">
+        <v>316</v>
+      </c>
+      <c r="E1" s="176" t="s">
+        <v>317</v>
+      </c>
+      <c r="F1" s="176" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="59" t="s">
+        <v>319</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>321</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="F2" s="59" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>324</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="s">
+        <v>325</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>326</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="E4" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>328</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="F5" s="59" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>330</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>322</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="176" t="s">
+        <v>313</v>
+      </c>
+      <c r="B1" s="176" t="s">
+        <v>314</v>
+      </c>
+      <c r="C1" s="176" t="s">
+        <v>315</v>
+      </c>
+      <c r="D1" s="177" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="59" t="s">
+        <v>319</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>321</v>
+      </c>
+      <c r="D2" s="59" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>324</v>
+      </c>
+      <c r="D3" s="59" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59" t="s">
+        <v>325</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>326</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>328</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>330</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>336</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="21.75"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="176" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="176" t="s">
+        <v>338</v>
+      </c>
+      <c r="C1" s="176" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="59" t="s">
+        <v>319</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>314</v>
+      </c>
+      <c r="C2" s="59" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="59" t="s">
+        <v>319</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>315</v>
+      </c>
+      <c r="C3" s="59" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="59"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>314</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>315</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="59"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="59"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>314</v>
+      </c>
+      <c r="C9" s="59" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>315</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="B11" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="C11" s="59" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>344</v>
+      </c>
+      <c r="C12" s="59" t="s">
+        <v>345</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/mock/input.xlsx
+++ b/mock/input.xlsx
@@ -13,7 +13,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="Kgj4/vzLRQjenZlbhETpKJgQqdmdb4hXiaUalNDO9JQ="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="VLhpHpUl6wV/vEJuQyDn6vzR2GPvwL9vP5SefqxZX7A="/>
     </ext>
   </extLst>
 </workbook>
@@ -39,14 +39,14 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7miv/0lytWTAkL1f4y65tH/v8Oh4VQ=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhpc4WtxcSRdbC3e/bbFWo6xvMa2A=="/>
     </ext>
   </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="957" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="345">
   <si>
     <t>Packages</t>
   </si>
@@ -2398,9 +2398,6 @@
     <t>Gateway</t>
   </si>
   <si>
-    <t>Stripe</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
@@ -38306,9 +38303,6 @@
       <c r="B4" s="59" t="s">
         <v>320</v>
       </c>
-      <c r="C4" s="59" t="s">
-        <v>326</v>
-      </c>
       <c r="D4" s="59" t="s">
         <v>334</v>
       </c>
@@ -38461,19 +38455,16 @@
       <c r="B11" s="59" t="s">
         <v>342</v>
       </c>
-      <c r="C11" s="59" t="s">
-        <v>343</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" s="59" t="s">
         <v>327</v>
       </c>
       <c r="B12" s="59" t="s">
+        <v>343</v>
+      </c>
+      <c r="C12" s="59" t="s">
         <v>344</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>345</v>
       </c>
     </row>
   </sheetData>

--- a/mock/input.xlsx
+++ b/mock/input.xlsx
@@ -70,7 +70,7 @@
         <t xml:space="preserve">======
 ID#AAAB1_VdfyU
 Alexander Wong    (2026-03-17 15:29:52)
-Title: Engine Type: 1.5L VTEC® Turbo Inline-4
+Headline: Engine Type: 1.5L VTEC® Turbo Inline-4
 Description: The turbocharged Integra is engineered for true driving enthusiasts. With a 1.5L VTEC® Turbo engine that pumps out 200-HP* and an early and flat torque curve that offers smooth power delivery, the Integra is a powerful and agile tour de force.
 Image:  /-/media/Acura-Platform/Vehicle-Pages/INTEGRA/2025/pricing-and-specs/Specs-Cards-Powertrain/In-Line-4-Cylinder/Acura-Integra-Pricing-and-Specs-powertrain-s.jpg</t>
       </text>
@@ -89,7 +89,7 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgQcyu16xD1mmvLjK41Jg3neVlDiA=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhubDM2u3HqRvardiPDUmGzgGpoUg=="/>
     </ext>
   </extLst>
 </comments>

--- a/mock/input.xlsx
+++ b/mock/input.xlsx
@@ -13,7 +13,7 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="rBp+/sCSO7jeLkVjpc2X0U4iZJ3/aaYljlYTIie8NpY="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId9" roundtripDataChecksum="mGQrv0ioN9o55NGTH3hB1O9WzfqgD5k1UVEkjiNT3J8="/>
     </ext>
   </extLst>
 </workbook>
@@ -75,7 +75,7 @@
 Image:  /-/media/Acura-Platform/Vehicle-Pages/INTEGRA/2025/pricing-and-specs/Specs-Cards-Powertrain/In-Line-4-Cylinder/Acura-Integra-Pricing-and-Specs-powertrain-s.jpg</t>
       </text>
     </comment>
-    <comment authorId="0" ref="I170">
+    <comment authorId="0" ref="I172">
       <text>
         <t xml:space="preserve">======
 ID#AAAB1awAxr0
@@ -89,14 +89,14 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mhubDM2u3HqRvardiPDUmGzgGpoUg=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mju7bC8eOSTi6jQ5Uj7Tx+K1EC6sw=="/>
     </ext>
   </extLst>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="950" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="952" uniqueCount="342">
   <si>
     <t>Packages</t>
   </si>
@@ -435,6 +435,9 @@
     <t>Continuously Variable Transmission (CVT) with Paddle Shifters</t>
   </si>
   <si>
+    <t>(CVT) with Paddle Shifters</t>
+  </si>
+  <si>
     <t>Ratio Range</t>
   </si>
   <si>
@@ -451,6 +454,9 @@
   </si>
   <si>
     <t>6-Speed Manual Transmission with Rev-Match Control</t>
+  </si>
+  <si>
+    <t>(6MT) with Rev-Match Control</t>
   </si>
   <si>
     <t>Gear Ratios (:1)</t>
@@ -4717,15 +4723,9 @@
         <v>52</v>
       </c>
       <c r="D23" s="32"/>
-      <c r="E23" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="F23" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="G23" s="45" t="s">
-        <v>42</v>
-      </c>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
       <c r="H23" s="45"/>
       <c r="I23" s="46"/>
       <c r="J23" s="7"/>
@@ -4749,20 +4749,20 @@
     <row r="24" ht="39.0" customHeight="1">
       <c r="A24" s="7"/>
       <c r="C24" s="43"/>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="E24" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24" s="47" t="s">
-        <v>54</v>
-      </c>
-      <c r="H24" s="47"/>
-      <c r="I24" s="48"/>
+      <c r="E24" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="F24" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="G24" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="45"/>
+      <c r="I24" s="46"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -4781,20 +4781,20 @@
       <c r="Y24" s="7"/>
       <c r="Z24" s="7"/>
     </row>
-    <row r="25" ht="25.5" customHeight="1">
+    <row r="25" ht="39.0" customHeight="1">
       <c r="A25" s="7"/>
       <c r="C25" s="43"/>
       <c r="D25" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="E25" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="47" t="s">
-        <v>56</v>
-      </c>
       <c r="F25" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G25" s="47" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H25" s="47"/>
       <c r="I25" s="48"/>
@@ -4820,19 +4820,19 @@
       <c r="A26" s="7"/>
       <c r="C26" s="43"/>
       <c r="D26" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="E26" s="47" t="s">
         <v>57</v>
       </c>
-      <c r="E26" s="49">
-        <v>5.048</v>
-      </c>
-      <c r="F26" s="49">
-        <v>5.048</v>
-      </c>
-      <c r="G26" s="49">
-        <v>5.048</v>
-      </c>
-      <c r="H26" s="49"/>
-      <c r="I26" s="50"/>
+      <c r="F26" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>57</v>
+      </c>
+      <c r="H26" s="47"/>
+      <c r="I26" s="48"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
@@ -4851,21 +4851,23 @@
       <c r="Y26" s="7"/>
       <c r="Z26" s="7"/>
     </row>
-    <row r="27" ht="33.75" customHeight="1">
+    <row r="27" ht="25.5" customHeight="1">
       <c r="A27" s="7"/>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="43"/>
+      <c r="D27" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="24"/>
-      <c r="E27" s="51"/>
-      <c r="F27" s="51"/>
-      <c r="G27" s="51"/>
-      <c r="H27" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="I27" s="46" t="s">
-        <v>42</v>
-      </c>
+      <c r="E27" s="49">
+        <v>5.048</v>
+      </c>
+      <c r="F27" s="49">
+        <v>5.048</v>
+      </c>
+      <c r="G27" s="49">
+        <v>5.048</v>
+      </c>
+      <c r="H27" s="49"/>
+      <c r="I27" s="50"/>
       <c r="J27" s="7"/>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
@@ -4884,18 +4886,15 @@
       <c r="Y27" s="7"/>
       <c r="Z27" s="7"/>
     </row>
-    <row r="28" ht="22.5" customHeight="1">
+    <row r="28" ht="33.75" customHeight="1">
       <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="32" t="s">
+      <c r="C28" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="E28" s="52"/>
-      <c r="F28" s="53"/>
-      <c r="G28" s="53"/>
-      <c r="H28" s="54"/>
-      <c r="I28" s="48"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="51"/>
+      <c r="F28" s="51"/>
+      <c r="G28" s="51"/>
       <c r="J28" s="7"/>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -4916,19 +4915,19 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="7"/>
-      <c r="B29" s="27"/>
+      <c r="B29" s="7"/>
       <c r="C29" s="33"/>
-      <c r="D29" s="32" t="s">
+      <c r="D29" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="E29" s="55"/>
-      <c r="F29" s="55"/>
-      <c r="G29" s="55"/>
-      <c r="H29" s="47">
-        <v>3.643</v>
-      </c>
-      <c r="I29" s="48">
-        <v>3.625</v>
+      <c r="E29" s="52"/>
+      <c r="F29" s="53"/>
+      <c r="G29" s="53"/>
+      <c r="H29" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="I29" s="46" t="s">
+        <v>42</v>
       </c>
       <c r="J29" s="7"/>
       <c r="K29" s="7"/>
@@ -4950,20 +4949,16 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="7"/>
-      <c r="B30" s="27"/>
+      <c r="B30" s="7"/>
       <c r="C30" s="33"/>
       <c r="D30" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="E30" s="55"/>
-      <c r="F30" s="55"/>
-      <c r="G30" s="55"/>
-      <c r="H30" s="56" t="s">
-        <v>62</v>
-      </c>
-      <c r="I30" s="48">
-        <v>2.115</v>
-      </c>
+      <c r="E30" s="52"/>
+      <c r="F30" s="53"/>
+      <c r="G30" s="53"/>
+      <c r="H30" s="54"/>
+      <c r="I30" s="48"/>
       <c r="J30" s="7"/>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -4987,16 +4982,16 @@
       <c r="B31" s="27"/>
       <c r="C31" s="33"/>
       <c r="D31" s="32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E31" s="55"/>
       <c r="F31" s="55"/>
       <c r="G31" s="55"/>
       <c r="H31" s="47">
-        <v>1.361</v>
+        <v>3.643</v>
       </c>
       <c r="I31" s="48">
-        <v>1.529</v>
+        <v>3.625</v>
       </c>
       <c r="J31" s="7"/>
       <c r="K31" s="7"/>
@@ -5021,16 +5016,16 @@
       <c r="B32" s="27"/>
       <c r="C32" s="33"/>
       <c r="D32" s="32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E32" s="55"/>
       <c r="F32" s="55"/>
       <c r="G32" s="55"/>
-      <c r="H32" s="47">
-        <v>1.024</v>
+      <c r="H32" s="56" t="s">
+        <v>64</v>
       </c>
       <c r="I32" s="48">
-        <v>1.125</v>
+        <v>2.115</v>
       </c>
       <c r="J32" s="7"/>
       <c r="K32" s="7"/>
@@ -5060,11 +5055,11 @@
       <c r="E33" s="55"/>
       <c r="F33" s="55"/>
       <c r="G33" s="55"/>
-      <c r="H33" s="56" t="s">
-        <v>66</v>
+      <c r="H33" s="47">
+        <v>1.361</v>
       </c>
       <c r="I33" s="48">
-        <v>0.911</v>
+        <v>1.529</v>
       </c>
       <c r="J33" s="7"/>
       <c r="K33" s="7"/>
@@ -5089,16 +5084,16 @@
       <c r="B34" s="27"/>
       <c r="C34" s="33"/>
       <c r="D34" s="32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E34" s="55"/>
       <c r="F34" s="55"/>
       <c r="G34" s="55"/>
       <c r="H34" s="47">
-        <v>0.686</v>
+        <v>1.024</v>
       </c>
       <c r="I34" s="48">
-        <v>0.734</v>
+        <v>1.125</v>
       </c>
       <c r="J34" s="7"/>
       <c r="K34" s="7"/>
@@ -5123,16 +5118,16 @@
       <c r="B35" s="27"/>
       <c r="C35" s="33"/>
       <c r="D35" s="32" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E35" s="55"/>
       <c r="F35" s="55"/>
       <c r="G35" s="55"/>
-      <c r="H35" s="47">
-        <v>3.673</v>
+      <c r="H35" s="56" t="s">
+        <v>68</v>
       </c>
       <c r="I35" s="48">
-        <v>3.757</v>
+        <v>0.911</v>
       </c>
       <c r="J35" s="7"/>
       <c r="K35" s="7"/>
@@ -5157,16 +5152,16 @@
       <c r="B36" s="27"/>
       <c r="C36" s="33"/>
       <c r="D36" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="E36" s="57"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="49">
-        <v>4.353</v>
-      </c>
-      <c r="I36" s="50">
-        <v>3.842</v>
+        <v>69</v>
+      </c>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="47">
+        <v>0.686</v>
+      </c>
+      <c r="I36" s="48">
+        <v>0.734</v>
       </c>
       <c r="J36" s="7"/>
       <c r="K36" s="7"/>
@@ -5186,18 +5181,22 @@
       <c r="Y36" s="7"/>
       <c r="Z36" s="7"/>
     </row>
-    <row r="37" ht="25.5" customHeight="1">
+    <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="7"/>
-      <c r="B37" s="59"/>
-      <c r="C37" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="61"/>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="44"/>
+      <c r="B37" s="27"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="E37" s="55"/>
+      <c r="F37" s="55"/>
+      <c r="G37" s="55"/>
+      <c r="H37" s="47">
+        <v>3.673</v>
+      </c>
+      <c r="I37" s="48">
+        <v>3.757</v>
+      </c>
       <c r="J37" s="7"/>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -5216,20 +5215,21 @@
       <c r="Y37" s="7"/>
       <c r="Z37" s="7"/>
     </row>
-    <row r="38" ht="25.5" customHeight="1">
+    <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="7"/>
+      <c r="B38" s="27"/>
       <c r="C38" s="33"/>
-      <c r="D38" s="61" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I38" s="39" t="s">
-        <v>42</v>
+      <c r="D38" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="E38" s="57"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="49">
+        <v>4.353</v>
+      </c>
+      <c r="I38" s="50">
+        <v>3.842</v>
       </c>
       <c r="J38" s="7"/>
       <c r="K38" s="7"/>
@@ -5250,19 +5250,17 @@
       <c r="Z38" s="7"/>
     </row>
     <row r="39" ht="25.5" customHeight="1">
-      <c r="C39" s="33"/>
-      <c r="D39" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="I39" s="39" t="s">
-        <v>42</v>
-      </c>
+      <c r="A39" s="7"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D39" s="61"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="53"/>
+      <c r="H39" s="38"/>
+      <c r="I39" s="44"/>
       <c r="J39" s="7"/>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -5281,26 +5279,20 @@
       <c r="Y39" s="7"/>
       <c r="Z39" s="7"/>
     </row>
-    <row r="40" ht="39.0" customHeight="1">
+    <row r="40" ht="25.5" customHeight="1">
       <c r="A40" s="7"/>
       <c r="C40" s="33"/>
-      <c r="D40" s="40" t="s">
+      <c r="D40" s="61" t="s">
         <v>70</v>
       </c>
-      <c r="E40" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="F40" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="G40" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="H40" s="34" t="s">
-        <v>72</v>
-      </c>
-      <c r="I40" s="36" t="s">
-        <v>73</v>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+      <c r="G40" s="34"/>
+      <c r="H40" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I40" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="J40" s="7"/>
       <c r="K40" s="7"/>
@@ -5320,26 +5312,19 @@
       <c r="Y40" s="7"/>
       <c r="Z40" s="7"/>
     </row>
-    <row r="41" ht="39.0" customHeight="1">
-      <c r="A41" s="7"/>
+    <row r="41" ht="25.5" customHeight="1">
       <c r="C41" s="33"/>
       <c r="D41" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="F41" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="G41" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="H41" s="34" t="s">
-        <v>75</v>
-      </c>
-      <c r="I41" s="36" t="s">
-        <v>76</v>
+        <v>71</v>
+      </c>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="I41" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="J41" s="7"/>
       <c r="K41" s="7"/>
@@ -5359,26 +5344,26 @@
       <c r="Y41" s="7"/>
       <c r="Z41" s="7"/>
     </row>
-    <row r="42" ht="37.5" customHeight="1">
-      <c r="A42" s="32"/>
+    <row r="42" ht="39.0" customHeight="1">
+      <c r="A42" s="7"/>
       <c r="C42" s="33"/>
       <c r="D42" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="E42" s="34">
-        <v>12.4</v>
-      </c>
-      <c r="F42" s="34">
-        <v>12.4</v>
-      </c>
-      <c r="G42" s="34">
-        <v>12.4</v>
-      </c>
-      <c r="H42" s="34">
-        <v>12.4</v>
-      </c>
-      <c r="I42" s="63">
-        <v>12.4</v>
+        <v>72</v>
+      </c>
+      <c r="E42" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F42" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="G42" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="H42" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="I42" s="36" t="s">
+        <v>75</v>
       </c>
       <c r="J42" s="7"/>
       <c r="K42" s="7"/>
@@ -5398,18 +5383,27 @@
       <c r="Y42" s="7"/>
       <c r="Z42" s="7"/>
     </row>
-    <row r="43" ht="45.0" customHeight="1">
+    <row r="43" ht="39.0" customHeight="1">
       <c r="A43" s="7"/>
-      <c r="B43" s="8" t="s">
+      <c r="C43" s="33"/>
+      <c r="D43" s="40" t="s">
+        <v>76</v>
+      </c>
+      <c r="E43" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="G43" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="H43" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="I43" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="C43" s="9"/>
-      <c r="D43" s="8"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="10"/>
-      <c r="G43" s="10"/>
-      <c r="H43" s="10"/>
-      <c r="I43" s="11"/>
       <c r="J43" s="7"/>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -5428,17 +5422,27 @@
       <c r="Y43" s="7"/>
       <c r="Z43" s="7"/>
     </row>
-    <row r="44" ht="61.5" customHeight="1">
-      <c r="A44" s="7"/>
-      <c r="C44" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="D44" s="32"/>
-      <c r="E44" s="64"/>
-      <c r="F44" s="64"/>
-      <c r="G44" s="64"/>
-      <c r="H44" s="64"/>
-      <c r="I44" s="65"/>
+    <row r="44" ht="37.5" customHeight="1">
+      <c r="A44" s="32"/>
+      <c r="C44" s="33"/>
+      <c r="D44" s="40" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="34">
+        <v>12.4</v>
+      </c>
+      <c r="F44" s="34">
+        <v>12.4</v>
+      </c>
+      <c r="G44" s="34">
+        <v>12.4</v>
+      </c>
+      <c r="H44" s="34">
+        <v>12.4</v>
+      </c>
+      <c r="I44" s="63">
+        <v>12.4</v>
+      </c>
       <c r="J44" s="7"/>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -5457,27 +5461,18 @@
       <c r="Y44" s="7"/>
       <c r="Z44" s="7"/>
     </row>
-    <row r="45" ht="61.5" customHeight="1">
+    <row r="45" ht="45.0" customHeight="1">
       <c r="A45" s="7"/>
-      <c r="C45" s="33"/>
-      <c r="D45" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="E45" s="66" t="s">
+      <c r="B45" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F45" s="66" t="s">
-        <v>80</v>
-      </c>
-      <c r="G45" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="H45" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="I45" s="67" t="s">
-        <v>82</v>
-      </c>
+      <c r="C45" s="9"/>
+      <c r="D45" s="8"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="10"/>
+      <c r="G45" s="10"/>
+      <c r="H45" s="10"/>
+      <c r="I45" s="11"/>
       <c r="J45" s="7"/>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -5496,23 +5491,17 @@
       <c r="Y45" s="7"/>
       <c r="Z45" s="7"/>
     </row>
-    <row r="46" ht="25.5" customHeight="1">
+    <row r="46" ht="61.5" customHeight="1">
       <c r="A46" s="7"/>
-      <c r="C46" s="33"/>
-      <c r="D46" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="E46" s="66"/>
-      <c r="F46" s="66"/>
-      <c r="G46" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H46" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I46" s="39" t="s">
-        <v>42</v>
-      </c>
+      <c r="C46" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D46" s="32"/>
+      <c r="E46" s="64"/>
+      <c r="F46" s="64"/>
+      <c r="G46" s="64"/>
+      <c r="H46" s="64"/>
+      <c r="I46" s="65"/>
       <c r="J46" s="7"/>
       <c r="K46" s="7"/>
       <c r="L46" s="7"/>
@@ -5531,22 +5520,26 @@
       <c r="Y46" s="7"/>
       <c r="Z46" s="7"/>
     </row>
-    <row r="47" ht="25.5" customHeight="1">
+    <row r="47" ht="61.5" customHeight="1">
       <c r="A47" s="7"/>
       <c r="C47" s="33"/>
       <c r="D47" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="E47" s="66" t="s">
+        <v>82</v>
+      </c>
+      <c r="F47" s="66" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="H47" s="66" t="s">
+        <v>83</v>
+      </c>
+      <c r="I47" s="67" t="s">
         <v>84</v>
-      </c>
-      <c r="E47" s="66"/>
-      <c r="F47" s="66"/>
-      <c r="G47" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H47" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I47" s="39" t="s">
-        <v>42</v>
       </c>
       <c r="J47" s="7"/>
       <c r="K47" s="7"/>
@@ -5574,8 +5567,12 @@
       </c>
       <c r="E48" s="66"/>
       <c r="F48" s="66"/>
-      <c r="G48" s="62"/>
-      <c r="H48" s="62"/>
+      <c r="G48" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H48" s="62" t="s">
+        <v>42</v>
+      </c>
       <c r="I48" s="39" t="s">
         <v>42</v>
       </c>
@@ -5597,25 +5594,23 @@
       <c r="Y48" s="7"/>
       <c r="Z48" s="7"/>
     </row>
-    <row r="49" ht="22.5" customHeight="1">
+    <row r="49" ht="25.5" customHeight="1">
       <c r="A49" s="7"/>
       <c r="C49" s="33"/>
       <c r="D49" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="E49" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="F49" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="G49" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="H49" s="45" t="s">
-        <v>42</v>
-      </c>
-      <c r="I49" s="46"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
+      <c r="G49" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H49" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I49" s="39" t="s">
+        <v>42</v>
+      </c>
       <c r="J49" s="7"/>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -5634,18 +5629,17 @@
       <c r="Y49" s="7"/>
       <c r="Z49" s="7"/>
     </row>
-    <row r="50" ht="22.5" customHeight="1">
+    <row r="50" ht="25.5" customHeight="1">
       <c r="A50" s="7"/>
-      <c r="B50" s="27"/>
       <c r="C50" s="33"/>
       <c r="D50" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="E50" s="55"/>
-      <c r="F50" s="55"/>
-      <c r="G50" s="55"/>
-      <c r="H50" s="55"/>
-      <c r="I50" s="68" t="s">
+      <c r="E50" s="66"/>
+      <c r="F50" s="66"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="39" t="s">
         <v>42</v>
       </c>
       <c r="J50" s="7"/>
@@ -5668,26 +5662,23 @@
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="7"/>
-      <c r="B51" s="27"/>
       <c r="C51" s="33"/>
       <c r="D51" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="E51" s="38" t="s">
-        <v>42</v>
-      </c>
-      <c r="F51" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="G51" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="H51" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="I51" s="69" t="s">
-        <v>42</v>
-      </c>
+      <c r="E51" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="F51" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="G51" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="H51" s="45" t="s">
+        <v>42</v>
+      </c>
+      <c r="I51" s="46"/>
       <c r="J51" s="7"/>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -5706,26 +5697,19 @@
       <c r="Y51" s="7"/>
       <c r="Z51" s="7"/>
     </row>
-    <row r="52" ht="24.0" customHeight="1">
+    <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="7"/>
+      <c r="B52" s="27"/>
       <c r="C52" s="33"/>
       <c r="D52" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="E52" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="F52" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="G52" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="H52" s="66" t="s">
-        <v>90</v>
-      </c>
-      <c r="I52" s="67" t="s">
-        <v>91</v>
+      <c r="E52" s="55"/>
+      <c r="F52" s="55"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="68" t="s">
+        <v>42</v>
       </c>
       <c r="J52" s="7"/>
       <c r="K52" s="7"/>
@@ -5745,26 +5729,27 @@
       <c r="Y52" s="7"/>
       <c r="Z52" s="7"/>
     </row>
-    <row r="53" ht="24.0" customHeight="1">
+    <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="7"/>
+      <c r="B53" s="27"/>
       <c r="C53" s="33"/>
       <c r="D53" s="32" t="s">
-        <v>92</v>
-      </c>
-      <c r="E53" s="66" t="s">
-        <v>93</v>
-      </c>
-      <c r="F53" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="G53" s="66" t="s">
-        <v>94</v>
-      </c>
-      <c r="H53" s="70" t="s">
-        <v>94</v>
-      </c>
-      <c r="I53" s="67" t="s">
-        <v>95</v>
+        <v>90</v>
+      </c>
+      <c r="E53" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="F53" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="G53" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="H53" s="52" t="s">
+        <v>42</v>
+      </c>
+      <c r="I53" s="69" t="s">
+        <v>42</v>
       </c>
       <c r="J53" s="7"/>
       <c r="K53" s="7"/>
@@ -5784,26 +5769,26 @@
       <c r="Y53" s="7"/>
       <c r="Z53" s="7"/>
     </row>
-    <row r="54" ht="54.0" customHeight="1">
+    <row r="54" ht="24.0" customHeight="1">
       <c r="A54" s="7"/>
-      <c r="C54" s="43"/>
+      <c r="C54" s="33"/>
       <c r="D54" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="E54" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F54" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G54" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H54" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I54" s="39" t="s">
-        <v>42</v>
+        <v>91</v>
+      </c>
+      <c r="E54" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="F54" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="G54" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="H54" s="66" t="s">
+        <v>92</v>
+      </c>
+      <c r="I54" s="67" t="s">
+        <v>93</v>
       </c>
       <c r="J54" s="7"/>
       <c r="K54" s="7"/>
@@ -5823,26 +5808,26 @@
       <c r="Y54" s="7"/>
       <c r="Z54" s="7"/>
     </row>
-    <row r="55" ht="25.5" customHeight="1">
+    <row r="55" ht="24.0" customHeight="1">
       <c r="A55" s="7"/>
       <c r="C55" s="33"/>
       <c r="D55" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="E55" s="66" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="G55" s="66" t="s">
+        <v>96</v>
+      </c>
+      <c r="H55" s="70" t="s">
+        <v>96</v>
+      </c>
+      <c r="I55" s="67" t="s">
         <v>97</v>
-      </c>
-      <c r="E55" s="34">
-        <v>2.29</v>
-      </c>
-      <c r="F55" s="34">
-        <v>2.17</v>
-      </c>
-      <c r="G55" s="34">
-        <v>2.17</v>
-      </c>
-      <c r="H55" s="34">
-        <v>2.17</v>
-      </c>
-      <c r="I55" s="36">
-        <v>2.11</v>
       </c>
       <c r="J55" s="7"/>
       <c r="K55" s="7"/>
@@ -5862,26 +5847,26 @@
       <c r="Y55" s="7"/>
       <c r="Z55" s="7"/>
     </row>
-    <row r="56" ht="25.5" customHeight="1">
+    <row r="56" ht="54.0" customHeight="1">
       <c r="A56" s="7"/>
-      <c r="C56" s="33"/>
+      <c r="C56" s="43"/>
       <c r="D56" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="E56" s="66" t="s">
-        <v>99</v>
-      </c>
-      <c r="F56" s="66" t="s">
-        <v>100</v>
-      </c>
-      <c r="G56" s="66" t="s">
-        <v>100</v>
-      </c>
-      <c r="H56" s="66" t="s">
-        <v>100</v>
-      </c>
-      <c r="I56" s="67" t="s">
-        <v>101</v>
+      <c r="E56" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F56" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G56" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H56" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I56" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="J56" s="7"/>
       <c r="K56" s="7"/>
@@ -5905,22 +5890,22 @@
       <c r="A57" s="7"/>
       <c r="C57" s="33"/>
       <c r="D57" s="32" t="s">
-        <v>102</v>
-      </c>
-      <c r="E57" s="66">
-        <v>38.1</v>
-      </c>
-      <c r="F57" s="66">
-        <v>38.1</v>
-      </c>
-      <c r="G57" s="66">
-        <v>38.1</v>
-      </c>
-      <c r="H57" s="66">
-        <v>38.1</v>
-      </c>
-      <c r="I57" s="67">
-        <v>39.7</v>
+        <v>99</v>
+      </c>
+      <c r="E57" s="34">
+        <v>2.29</v>
+      </c>
+      <c r="F57" s="34">
+        <v>2.17</v>
+      </c>
+      <c r="G57" s="34">
+        <v>2.17</v>
+      </c>
+      <c r="H57" s="34">
+        <v>2.17</v>
+      </c>
+      <c r="I57" s="36">
+        <v>2.11</v>
       </c>
       <c r="J57" s="7"/>
       <c r="K57" s="7"/>
@@ -5944,22 +5929,22 @@
       <c r="A58" s="7"/>
       <c r="C58" s="33"/>
       <c r="D58" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="E58" s="66" t="s">
+        <v>101</v>
+      </c>
+      <c r="F58" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="G58" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="H58" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="I58" s="67" t="s">
         <v>103</v>
-      </c>
-      <c r="E58" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F58" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G58" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H58" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I58" s="39" t="s">
-        <v>42</v>
       </c>
       <c r="J58" s="7"/>
       <c r="K58" s="7"/>
@@ -5979,18 +5964,26 @@
       <c r="Y58" s="7"/>
       <c r="Z58" s="7"/>
     </row>
-    <row r="59" ht="43.5" customHeight="1">
+    <row r="59" ht="25.5" customHeight="1">
       <c r="A59" s="7"/>
       <c r="C59" s="33"/>
       <c r="D59" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="E59" s="62"/>
-      <c r="F59" s="62"/>
-      <c r="G59" s="62"/>
-      <c r="H59" s="62"/>
-      <c r="I59" s="39" t="s">
-        <v>42</v>
+      <c r="E59" s="66">
+        <v>38.1</v>
+      </c>
+      <c r="F59" s="66">
+        <v>38.1</v>
+      </c>
+      <c r="G59" s="66">
+        <v>38.1</v>
+      </c>
+      <c r="H59" s="66">
+        <v>38.1</v>
+      </c>
+      <c r="I59" s="67">
+        <v>39.7</v>
       </c>
       <c r="J59" s="7"/>
       <c r="K59" s="7"/>
@@ -6011,55 +6004,56 @@
       <c r="Z59" s="7"/>
     </row>
     <row r="60" ht="25.5" customHeight="1">
-      <c r="A60" s="71"/>
+      <c r="A60" s="7"/>
       <c r="C60" s="33"/>
       <c r="D60" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="E60" s="25"/>
-      <c r="F60" s="25"/>
-      <c r="G60" s="25"/>
-      <c r="H60" s="25"/>
-      <c r="I60" s="26"/>
-      <c r="J60" s="71"/>
-      <c r="K60" s="71"/>
-      <c r="L60" s="71"/>
-      <c r="M60" s="71"/>
-      <c r="N60" s="71"/>
-      <c r="O60" s="71"/>
-      <c r="P60" s="71"/>
-      <c r="Q60" s="71"/>
-      <c r="R60" s="71"/>
-      <c r="S60" s="71"/>
-      <c r="T60" s="71"/>
-      <c r="U60" s="71"/>
-      <c r="V60" s="71"/>
-      <c r="W60" s="71"/>
-      <c r="X60" s="71"/>
-      <c r="Y60" s="71"/>
-      <c r="Z60" s="71"/>
-    </row>
-    <row r="61" ht="25.5" customHeight="1">
+      <c r="E60" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F60" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G60" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H60" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I60" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
+      <c r="M60" s="7"/>
+      <c r="N60" s="7"/>
+      <c r="O60" s="7"/>
+      <c r="P60" s="7"/>
+      <c r="Q60" s="7"/>
+      <c r="R60" s="7"/>
+      <c r="S60" s="7"/>
+      <c r="T60" s="7"/>
+      <c r="U60" s="7"/>
+      <c r="V60" s="7"/>
+      <c r="W60" s="7"/>
+      <c r="X60" s="7"/>
+      <c r="Y60" s="7"/>
+      <c r="Z60" s="7"/>
+    </row>
+    <row r="61" ht="43.5" customHeight="1">
       <c r="A61" s="7"/>
-      <c r="B61" s="40"/>
-      <c r="C61" s="43"/>
+      <c r="C61" s="33"/>
       <c r="D61" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="E61" s="30">
-        <v>12.3</v>
-      </c>
-      <c r="F61" s="30">
-        <v>12.3</v>
-      </c>
-      <c r="G61" s="30">
-        <v>12.3</v>
-      </c>
-      <c r="H61" s="30">
-        <v>12.3</v>
-      </c>
-      <c r="I61" s="31">
-        <v>13.8</v>
+      <c r="E61" s="62"/>
+      <c r="F61" s="62"/>
+      <c r="G61" s="62"/>
+      <c r="H61" s="62"/>
+      <c r="I61" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="J61" s="7"/>
       <c r="K61" s="7"/>
@@ -6115,20 +6109,20 @@
       <c r="D63" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="E63" s="72">
-        <v>11.1</v>
-      </c>
-      <c r="F63" s="72">
-        <v>11.1</v>
-      </c>
-      <c r="G63" s="72">
-        <v>11.1</v>
-      </c>
-      <c r="H63" s="72">
-        <v>11.1</v>
-      </c>
-      <c r="I63" s="73" t="s">
-        <v>109</v>
+      <c r="E63" s="30">
+        <v>12.3</v>
+      </c>
+      <c r="F63" s="30">
+        <v>12.3</v>
+      </c>
+      <c r="G63" s="30">
+        <v>12.3</v>
+      </c>
+      <c r="H63" s="30">
+        <v>12.3</v>
+      </c>
+      <c r="I63" s="31">
+        <v>13.8</v>
       </c>
       <c r="J63" s="7"/>
       <c r="K63" s="7"/>
@@ -6149,64 +6143,55 @@
       <c r="Z63" s="7"/>
     </row>
     <row r="64" ht="25.5" customHeight="1">
-      <c r="A64" s="7"/>
+      <c r="A64" s="71"/>
       <c r="C64" s="33"/>
       <c r="D64" s="32" t="s">
-        <v>110</v>
-      </c>
-      <c r="E64" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="G64" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="H64" s="37" t="s">
-        <v>111</v>
-      </c>
-      <c r="I64" s="74" t="s">
-        <v>112</v>
-      </c>
-      <c r="J64" s="7"/>
-      <c r="K64" s="7"/>
-      <c r="L64" s="7"/>
-      <c r="M64" s="7"/>
-      <c r="N64" s="7"/>
-      <c r="O64" s="7"/>
-      <c r="P64" s="7"/>
-      <c r="Q64" s="7"/>
-      <c r="R64" s="7"/>
-      <c r="S64" s="7"/>
-      <c r="T64" s="7"/>
-      <c r="U64" s="7"/>
-      <c r="V64" s="7"/>
-      <c r="W64" s="7"/>
-      <c r="X64" s="7"/>
-      <c r="Y64" s="7"/>
-      <c r="Z64" s="7"/>
+        <v>109</v>
+      </c>
+      <c r="E64" s="25"/>
+      <c r="F64" s="25"/>
+      <c r="G64" s="25"/>
+      <c r="H64" s="25"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="71"/>
+      <c r="K64" s="71"/>
+      <c r="L64" s="71"/>
+      <c r="M64" s="71"/>
+      <c r="N64" s="71"/>
+      <c r="O64" s="71"/>
+      <c r="P64" s="71"/>
+      <c r="Q64" s="71"/>
+      <c r="R64" s="71"/>
+      <c r="S64" s="71"/>
+      <c r="T64" s="71"/>
+      <c r="U64" s="71"/>
+      <c r="V64" s="71"/>
+      <c r="W64" s="71"/>
+      <c r="X64" s="71"/>
+      <c r="Y64" s="71"/>
+      <c r="Z64" s="71"/>
     </row>
     <row r="65" ht="25.5" customHeight="1">
       <c r="A65" s="7"/>
-      <c r="C65" s="33"/>
+      <c r="B65" s="40"/>
+      <c r="C65" s="43"/>
       <c r="D65" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="E65" s="30" t="s">
-        <v>114</v>
-      </c>
-      <c r="F65" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="G65" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="H65" s="30" t="s">
-        <v>115</v>
-      </c>
-      <c r="I65" s="74" t="s">
-        <v>116</v>
+        <v>110</v>
+      </c>
+      <c r="E65" s="72">
+        <v>11.1</v>
+      </c>
+      <c r="F65" s="72">
+        <v>11.1</v>
+      </c>
+      <c r="G65" s="72">
+        <v>11.1</v>
+      </c>
+      <c r="H65" s="72">
+        <v>11.1</v>
+      </c>
+      <c r="I65" s="73" t="s">
+        <v>111</v>
       </c>
       <c r="J65" s="7"/>
       <c r="K65" s="7"/>
@@ -6230,22 +6215,22 @@
       <c r="A66" s="7"/>
       <c r="C66" s="33"/>
       <c r="D66" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="E66" s="70" t="s">
-        <v>118</v>
-      </c>
-      <c r="F66" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="G66" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="H66" s="70" t="s">
-        <v>119</v>
-      </c>
-      <c r="I66" s="67" t="s">
-        <v>120</v>
+        <v>112</v>
+      </c>
+      <c r="E66" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="F66" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="G66" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="H66" s="37" t="s">
+        <v>113</v>
+      </c>
+      <c r="I66" s="74" t="s">
+        <v>114</v>
       </c>
       <c r="J66" s="7"/>
       <c r="K66" s="7"/>
@@ -6266,82 +6251,82 @@
       <c r="Z66" s="7"/>
     </row>
     <row r="67" ht="25.5" customHeight="1">
-      <c r="A67" s="75"/>
+      <c r="A67" s="7"/>
       <c r="C67" s="33"/>
       <c r="D67" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="E67" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F67" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G67" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H67" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I67" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="J67" s="76"/>
-      <c r="K67" s="76"/>
-      <c r="L67" s="76"/>
-      <c r="M67" s="76"/>
-      <c r="N67" s="76"/>
-      <c r="O67" s="76"/>
-      <c r="P67" s="76"/>
-      <c r="Q67" s="76"/>
-      <c r="R67" s="76"/>
-      <c r="S67" s="76"/>
-      <c r="T67" s="76"/>
-      <c r="U67" s="76"/>
-      <c r="V67" s="76"/>
-      <c r="W67" s="76"/>
-      <c r="X67" s="76"/>
-      <c r="Y67" s="76"/>
-      <c r="Z67" s="76"/>
+        <v>115</v>
+      </c>
+      <c r="E67" s="30" t="s">
+        <v>116</v>
+      </c>
+      <c r="F67" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="G67" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="H67" s="30" t="s">
+        <v>117</v>
+      </c>
+      <c r="I67" s="74" t="s">
+        <v>118</v>
+      </c>
+      <c r="J67" s="7"/>
+      <c r="K67" s="7"/>
+      <c r="L67" s="7"/>
+      <c r="M67" s="7"/>
+      <c r="N67" s="7"/>
+      <c r="O67" s="7"/>
+      <c r="P67" s="7"/>
+      <c r="Q67" s="7"/>
+      <c r="R67" s="7"/>
+      <c r="S67" s="7"/>
+      <c r="T67" s="7"/>
+      <c r="U67" s="7"/>
+      <c r="V67" s="7"/>
+      <c r="W67" s="7"/>
+      <c r="X67" s="7"/>
+      <c r="Y67" s="7"/>
+      <c r="Z67" s="7"/>
     </row>
     <row r="68" ht="25.5" customHeight="1">
-      <c r="A68" s="75"/>
+      <c r="A68" s="7"/>
       <c r="C68" s="33"/>
       <c r="D68" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="E68" s="70" t="s">
+        <v>120</v>
+      </c>
+      <c r="F68" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="G68" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="H68" s="70" t="s">
+        <v>121</v>
+      </c>
+      <c r="I68" s="67" t="s">
         <v>122</v>
       </c>
-      <c r="E68" s="77">
-        <v>3084.0</v>
-      </c>
-      <c r="F68" s="78">
-        <v>3109.0</v>
-      </c>
-      <c r="G68" s="78">
-        <v>3150.0</v>
-      </c>
-      <c r="H68" s="78">
-        <v>3073.0</v>
-      </c>
-      <c r="I68" s="79">
-        <v>3219.0</v>
-      </c>
-      <c r="J68" s="76"/>
-      <c r="K68" s="76"/>
-      <c r="L68" s="76"/>
-      <c r="M68" s="76"/>
-      <c r="N68" s="76"/>
-      <c r="O68" s="76"/>
-      <c r="P68" s="76"/>
-      <c r="Q68" s="76"/>
-      <c r="R68" s="76"/>
-      <c r="S68" s="76"/>
-      <c r="T68" s="76"/>
-      <c r="U68" s="76"/>
-      <c r="V68" s="76"/>
-      <c r="W68" s="76"/>
-      <c r="X68" s="76"/>
-      <c r="Y68" s="76"/>
-      <c r="Z68" s="76"/>
+      <c r="J68" s="7"/>
+      <c r="K68" s="7"/>
+      <c r="L68" s="7"/>
+      <c r="M68" s="7"/>
+      <c r="N68" s="7"/>
+      <c r="O68" s="7"/>
+      <c r="P68" s="7"/>
+      <c r="Q68" s="7"/>
+      <c r="R68" s="7"/>
+      <c r="S68" s="7"/>
+      <c r="T68" s="7"/>
+      <c r="U68" s="7"/>
+      <c r="V68" s="7"/>
+      <c r="W68" s="7"/>
+      <c r="X68" s="7"/>
+      <c r="Y68" s="7"/>
+      <c r="Z68" s="7"/>
     </row>
     <row r="69" ht="25.5" customHeight="1">
       <c r="A69" s="75"/>
@@ -6349,20 +6334,20 @@
       <c r="D69" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="E69" s="70" t="s">
-        <v>124</v>
-      </c>
-      <c r="F69" s="70" t="s">
-        <v>124</v>
-      </c>
-      <c r="G69" s="70" t="s">
-        <v>124</v>
-      </c>
-      <c r="H69" s="70" t="s">
-        <v>125</v>
-      </c>
-      <c r="I69" s="80" t="s">
-        <v>126</v>
+      <c r="E69" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G69" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H69" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I69" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="J69" s="76"/>
       <c r="K69" s="76"/>
@@ -6382,18 +6367,27 @@
       <c r="Y69" s="76"/>
       <c r="Z69" s="76"/>
     </row>
-    <row r="70" ht="43.5" customHeight="1">
+    <row r="70" ht="25.5" customHeight="1">
       <c r="A70" s="75"/>
-      <c r="B70" s="81" t="s">
-        <v>127</v>
-      </c>
-      <c r="C70" s="9"/>
-      <c r="D70" s="8"/>
-      <c r="E70" s="10"/>
-      <c r="F70" s="10"/>
-      <c r="G70" s="10"/>
-      <c r="H70" s="10"/>
-      <c r="I70" s="11"/>
+      <c r="C70" s="33"/>
+      <c r="D70" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E70" s="77">
+        <v>3084.0</v>
+      </c>
+      <c r="F70" s="78">
+        <v>3109.0</v>
+      </c>
+      <c r="G70" s="78">
+        <v>3150.0</v>
+      </c>
+      <c r="H70" s="78">
+        <v>3073.0</v>
+      </c>
+      <c r="I70" s="79">
+        <v>3219.0</v>
+      </c>
       <c r="J70" s="76"/>
       <c r="K70" s="76"/>
       <c r="L70" s="76"/>
@@ -6412,17 +6406,27 @@
       <c r="Y70" s="76"/>
       <c r="Z70" s="76"/>
     </row>
-    <row r="71" ht="24.75" customHeight="1">
-      <c r="A71" s="82"/>
-      <c r="C71" s="33" t="s">
+    <row r="71" ht="25.5" customHeight="1">
+      <c r="A71" s="75"/>
+      <c r="C71" s="33"/>
+      <c r="D71" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="E71" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="F71" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="G71" s="70" t="s">
+        <v>126</v>
+      </c>
+      <c r="H71" s="70" t="s">
+        <v>127</v>
+      </c>
+      <c r="I71" s="80" t="s">
         <v>128</v>
       </c>
-      <c r="D71" s="40"/>
-      <c r="E71" s="41"/>
-      <c r="F71" s="41"/>
-      <c r="G71" s="41"/>
-      <c r="H71" s="41"/>
-      <c r="I71" s="42"/>
       <c r="J71" s="76"/>
       <c r="K71" s="76"/>
       <c r="L71" s="76"/>
@@ -6441,26 +6445,18 @@
       <c r="Y71" s="76"/>
       <c r="Z71" s="76"/>
     </row>
-    <row r="72" ht="24.75" customHeight="1">
-      <c r="A72" s="82"/>
-      <c r="B72" s="40"/>
-      <c r="C72" s="43"/>
-      <c r="D72" s="32" t="s">
+    <row r="72" ht="43.5" customHeight="1">
+      <c r="A72" s="75"/>
+      <c r="B72" s="81" t="s">
         <v>129</v>
       </c>
-      <c r="E72" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="F72" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="G72" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="H72" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="I72" s="44"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="8"/>
+      <c r="E72" s="10"/>
+      <c r="F72" s="10"/>
+      <c r="G72" s="10"/>
+      <c r="H72" s="10"/>
+      <c r="I72" s="11"/>
       <c r="J72" s="76"/>
       <c r="K72" s="76"/>
       <c r="L72" s="76"/>
@@ -6485,7 +6481,7 @@
         <v>130</v>
       </c>
       <c r="D73" s="40"/>
-      <c r="E73" s="84"/>
+      <c r="E73" s="41"/>
       <c r="F73" s="41"/>
       <c r="G73" s="41"/>
       <c r="H73" s="41"/>
@@ -6511,8 +6507,8 @@
     <row r="74" ht="24.75" customHeight="1">
       <c r="A74" s="82"/>
       <c r="B74" s="40"/>
-      <c r="C74" s="85"/>
-      <c r="D74" s="86" t="s">
+      <c r="C74" s="43"/>
+      <c r="D74" s="32" t="s">
         <v>131</v>
       </c>
       <c r="E74" s="83" t="s">
@@ -6527,9 +6523,7 @@
       <c r="H74" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="I74" s="87" t="s">
-        <v>42</v>
-      </c>
+      <c r="I74" s="44"/>
       <c r="J74" s="76"/>
       <c r="K74" s="76"/>
       <c r="L74" s="76"/>
@@ -6549,84 +6543,77 @@
       <c r="Z74" s="76"/>
     </row>
     <row r="75" ht="24.75" customHeight="1">
-      <c r="A75" s="7"/>
-      <c r="C75" s="32"/>
-      <c r="D75" s="32" t="s">
+      <c r="A75" s="82"/>
+      <c r="C75" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="E75" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="F75" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="G75" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="H75" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I75" s="89" t="s">
-        <v>42</v>
-      </c>
-      <c r="J75" s="7"/>
-      <c r="K75" s="7"/>
-      <c r="L75" s="7"/>
-      <c r="M75" s="7"/>
-      <c r="N75" s="7"/>
-      <c r="O75" s="7"/>
-      <c r="P75" s="7"/>
-      <c r="Q75" s="7"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="7"/>
-      <c r="T75" s="7"/>
-      <c r="U75" s="7"/>
-      <c r="V75" s="7"/>
-      <c r="W75" s="7"/>
-      <c r="X75" s="7"/>
-      <c r="Y75" s="7"/>
-      <c r="Z75" s="7"/>
+      <c r="D75" s="40"/>
+      <c r="E75" s="84"/>
+      <c r="F75" s="41"/>
+      <c r="G75" s="41"/>
+      <c r="H75" s="41"/>
+      <c r="I75" s="42"/>
+      <c r="J75" s="76"/>
+      <c r="K75" s="76"/>
+      <c r="L75" s="76"/>
+      <c r="M75" s="76"/>
+      <c r="N75" s="76"/>
+      <c r="O75" s="76"/>
+      <c r="P75" s="76"/>
+      <c r="Q75" s="76"/>
+      <c r="R75" s="76"/>
+      <c r="S75" s="76"/>
+      <c r="T75" s="76"/>
+      <c r="U75" s="76"/>
+      <c r="V75" s="76"/>
+      <c r="W75" s="76"/>
+      <c r="X75" s="76"/>
+      <c r="Y75" s="76"/>
+      <c r="Z75" s="76"/>
     </row>
     <row r="76" ht="24.75" customHeight="1">
-      <c r="A76" s="32"/>
+      <c r="A76" s="82"/>
       <c r="B76" s="40"/>
-      <c r="C76" s="43"/>
-      <c r="D76" s="32" t="s">
+      <c r="C76" s="85"/>
+      <c r="D76" s="86" t="s">
         <v>133</v>
       </c>
-      <c r="E76" s="88"/>
-      <c r="F76" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="G76" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="H76" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I76" s="89"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
-      <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
-      <c r="N76" s="7"/>
-      <c r="O76" s="7"/>
-      <c r="P76" s="7"/>
-      <c r="Q76" s="7"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="7"/>
-      <c r="T76" s="7"/>
-      <c r="U76" s="7"/>
-      <c r="V76" s="7"/>
-      <c r="W76" s="7"/>
-      <c r="X76" s="7"/>
-      <c r="Y76" s="7"/>
-      <c r="Z76" s="7"/>
+      <c r="E76" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="F76" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="G76" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="H76" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="I76" s="87" t="s">
+        <v>42</v>
+      </c>
+      <c r="J76" s="76"/>
+      <c r="K76" s="76"/>
+      <c r="L76" s="76"/>
+      <c r="M76" s="76"/>
+      <c r="N76" s="76"/>
+      <c r="O76" s="76"/>
+      <c r="P76" s="76"/>
+      <c r="Q76" s="76"/>
+      <c r="R76" s="76"/>
+      <c r="S76" s="76"/>
+      <c r="T76" s="76"/>
+      <c r="U76" s="76"/>
+      <c r="V76" s="76"/>
+      <c r="W76" s="76"/>
+      <c r="X76" s="76"/>
+      <c r="Y76" s="76"/>
+      <c r="Z76" s="76"/>
     </row>
     <row r="77" ht="24.75" customHeight="1">
       <c r="A77" s="7"/>
-      <c r="B77" s="7"/>
-      <c r="C77" s="43"/>
+      <c r="C77" s="32"/>
       <c r="D77" s="32" t="s">
         <v>134</v>
       </c>
@@ -6664,23 +6651,23 @@
       <c r="Z77" s="7"/>
     </row>
     <row r="78" ht="24.75" customHeight="1">
-      <c r="A78" s="7"/>
-      <c r="B78" s="32"/>
+      <c r="A78" s="32"/>
+      <c r="B78" s="40"/>
       <c r="C78" s="43"/>
       <c r="D78" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="E78" s="90"/>
-      <c r="F78" s="90"/>
+      <c r="E78" s="88"/>
+      <c r="F78" s="88" t="s">
+        <v>42</v>
+      </c>
       <c r="G78" s="88" t="s">
         <v>42</v>
       </c>
       <c r="H78" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="I78" s="89" t="s">
-        <v>42</v>
-      </c>
+      <c r="I78" s="89"/>
       <c r="J78" s="7"/>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -6700,25 +6687,25 @@
       <c r="Z78" s="7"/>
     </row>
     <row r="79" ht="24.75" customHeight="1">
-      <c r="A79" s="32"/>
-      <c r="B79" s="40"/>
-      <c r="C79" s="85"/>
-      <c r="D79" s="86" t="s">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="43"/>
+      <c r="D79" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="E79" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="F79" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="G79" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="H79" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="I79" s="92" t="s">
+      <c r="E79" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="F79" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="G79" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="H79" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I79" s="89" t="s">
         <v>42</v>
       </c>
       <c r="J79" s="7"/>
@@ -6740,16 +6727,23 @@
       <c r="Z79" s="7"/>
     </row>
     <row r="80" ht="24.75" customHeight="1">
-      <c r="A80" s="32"/>
-      <c r="C80" s="33" t="s">
+      <c r="A80" s="7"/>
+      <c r="B80" s="32"/>
+      <c r="C80" s="43"/>
+      <c r="D80" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="D80" s="40"/>
-      <c r="E80" s="41"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="41"/>
-      <c r="H80" s="41"/>
-      <c r="I80" s="42"/>
+      <c r="E80" s="90"/>
+      <c r="F80" s="90"/>
+      <c r="G80" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="H80" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I80" s="89" t="s">
+        <v>42</v>
+      </c>
       <c r="J80" s="7"/>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -6771,23 +6765,23 @@
     <row r="81" ht="24.75" customHeight="1">
       <c r="A81" s="32"/>
       <c r="B81" s="40"/>
-      <c r="C81" s="43"/>
-      <c r="D81" s="32" t="s">
+      <c r="C81" s="85"/>
+      <c r="D81" s="86" t="s">
         <v>138</v>
       </c>
-      <c r="E81" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="F81" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G81" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H81" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="I81" s="94" t="s">
+      <c r="E81" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="F81" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="G81" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="H81" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="I81" s="92" t="s">
         <v>42</v>
       </c>
       <c r="J81" s="7"/>
@@ -6810,22 +6804,15 @@
     </row>
     <row r="82" ht="24.75" customHeight="1">
       <c r="A82" s="32"/>
-      <c r="B82" s="40"/>
-      <c r="C82" s="43"/>
-      <c r="D82" s="32" t="s">
+      <c r="C82" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="E82" s="55"/>
-      <c r="F82" s="55"/>
-      <c r="G82" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H82" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="I82" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="D82" s="40"/>
+      <c r="E82" s="41"/>
+      <c r="F82" s="41"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="41"/>
+      <c r="I82" s="42"/>
       <c r="J82" s="7"/>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
@@ -6851,15 +6838,21 @@
       <c r="D83" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="E83" s="57"/>
-      <c r="F83" s="57"/>
-      <c r="G83" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="H83" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="I83" s="69"/>
+      <c r="E83" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F83" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G83" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="H83" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I83" s="94" t="s">
+        <v>42</v>
+      </c>
       <c r="J83" s="7"/>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -6880,22 +6873,22 @@
     </row>
     <row r="84" ht="24.75" customHeight="1">
       <c r="A84" s="32"/>
-      <c r="B84" s="95"/>
-      <c r="C84" s="96"/>
-      <c r="D84" s="97" t="s">
+      <c r="B84" s="40"/>
+      <c r="C84" s="43"/>
+      <c r="D84" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="E84" s="62"/>
-      <c r="F84" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G84" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H84" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I84" s="39"/>
+      <c r="E84" s="55"/>
+      <c r="F84" s="55"/>
+      <c r="G84" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H84" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I84" s="68" t="s">
+        <v>42</v>
+      </c>
       <c r="J84" s="7"/>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -6916,18 +6909,20 @@
     </row>
     <row r="85" ht="24.75" customHeight="1">
       <c r="A85" s="32"/>
-      <c r="B85" s="95"/>
-      <c r="C85" s="96"/>
-      <c r="D85" s="97" t="s">
+      <c r="B85" s="40"/>
+      <c r="C85" s="43"/>
+      <c r="D85" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="E85" s="62"/>
-      <c r="F85" s="62"/>
-      <c r="G85" s="62"/>
-      <c r="H85" s="62"/>
-      <c r="I85" s="39" t="s">
-        <v>42</v>
-      </c>
+      <c r="E85" s="57"/>
+      <c r="F85" s="57"/>
+      <c r="G85" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="H85" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="I85" s="69"/>
       <c r="J85" s="7"/>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -6954,18 +6949,16 @@
         <v>143</v>
       </c>
       <c r="E86" s="62"/>
-      <c r="F86" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G86" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H86" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="I86" s="94" t="s">
-        <v>42</v>
-      </c>
+      <c r="F86" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G86" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H86" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I86" s="39"/>
       <c r="J86" s="7"/>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -6991,18 +6984,10 @@
       <c r="D87" s="97" t="s">
         <v>144</v>
       </c>
-      <c r="E87" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F87" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G87" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H87" s="62" t="s">
-        <v>42</v>
-      </c>
+      <c r="E87" s="62"/>
+      <c r="F87" s="62"/>
+      <c r="G87" s="62"/>
+      <c r="H87" s="62"/>
       <c r="I87" s="39" t="s">
         <v>42</v>
       </c>
@@ -7024,18 +7009,26 @@
       <c r="Y87" s="7"/>
       <c r="Z87" s="7"/>
     </row>
-    <row r="88" ht="21.0" customHeight="1">
+    <row r="88" ht="24.75" customHeight="1">
       <c r="A88" s="32"/>
-      <c r="B88" s="59"/>
-      <c r="C88" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="D88" s="40"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="37"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="36"/>
+      <c r="B88" s="95"/>
+      <c r="C88" s="96"/>
+      <c r="D88" s="97" t="s">
+        <v>145</v>
+      </c>
+      <c r="E88" s="62"/>
+      <c r="F88" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G88" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="H88" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I88" s="94" t="s">
+        <v>42</v>
+      </c>
       <c r="J88" s="7"/>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -7054,26 +7047,27 @@
       <c r="Y88" s="7"/>
       <c r="Z88" s="7"/>
     </row>
-    <row r="89" ht="21.0" customHeight="1">
+    <row r="89" ht="24.75" customHeight="1">
       <c r="A89" s="32"/>
-      <c r="C89" s="40"/>
-      <c r="D89" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="E89" s="37">
-        <v>107.7</v>
-      </c>
-      <c r="F89" s="37">
-        <v>107.7</v>
-      </c>
-      <c r="G89" s="37">
-        <v>107.7</v>
-      </c>
-      <c r="H89" s="37">
-        <v>107.7</v>
-      </c>
-      <c r="I89" s="36">
-        <v>107.7</v>
+      <c r="B89" s="95"/>
+      <c r="C89" s="96"/>
+      <c r="D89" s="97" t="s">
+        <v>146</v>
+      </c>
+      <c r="E89" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F89" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G89" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H89" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I89" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="J89" s="7"/>
       <c r="K89" s="7"/>
@@ -7095,25 +7089,16 @@
     </row>
     <row r="90" ht="21.0" customHeight="1">
       <c r="A90" s="32"/>
-      <c r="C90" s="40"/>
-      <c r="D90" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="E90" s="37">
-        <v>185.8</v>
-      </c>
-      <c r="F90" s="37">
-        <v>185.8</v>
-      </c>
-      <c r="G90" s="37">
-        <v>185.8</v>
-      </c>
-      <c r="H90" s="37">
-        <v>185.8</v>
-      </c>
-      <c r="I90" s="35" t="s">
-        <v>147</v>
-      </c>
+      <c r="B90" s="59"/>
+      <c r="C90" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D90" s="40"/>
+      <c r="E90" s="37"/>
+      <c r="F90" s="37"/>
+      <c r="G90" s="37"/>
+      <c r="H90" s="37"/>
+      <c r="I90" s="36"/>
       <c r="J90" s="7"/>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -7136,22 +7121,22 @@
       <c r="A91" s="32"/>
       <c r="C91" s="40"/>
       <c r="D91" s="40" t="s">
-        <v>148</v>
-      </c>
-      <c r="E91" s="70">
-        <v>72.0</v>
-      </c>
-      <c r="F91" s="70">
-        <v>72.0</v>
-      </c>
-      <c r="G91" s="70">
-        <v>72.0</v>
-      </c>
-      <c r="H91" s="70">
-        <v>72.0</v>
-      </c>
-      <c r="I91" s="67">
-        <v>74.8</v>
+        <v>147</v>
+      </c>
+      <c r="E91" s="37">
+        <v>107.7</v>
+      </c>
+      <c r="F91" s="37">
+        <v>107.7</v>
+      </c>
+      <c r="G91" s="37">
+        <v>107.7</v>
+      </c>
+      <c r="H91" s="37">
+        <v>107.7</v>
+      </c>
+      <c r="I91" s="36">
+        <v>107.7</v>
       </c>
       <c r="J91" s="7"/>
       <c r="K91" s="7"/>
@@ -7175,22 +7160,22 @@
       <c r="A92" s="32"/>
       <c r="C92" s="40"/>
       <c r="D92" s="40" t="s">
+        <v>148</v>
+      </c>
+      <c r="E92" s="37">
+        <v>185.8</v>
+      </c>
+      <c r="F92" s="37">
+        <v>185.8</v>
+      </c>
+      <c r="G92" s="37">
+        <v>185.8</v>
+      </c>
+      <c r="H92" s="37">
+        <v>185.8</v>
+      </c>
+      <c r="I92" s="35" t="s">
         <v>149</v>
-      </c>
-      <c r="E92" s="37">
-        <v>55.5</v>
-      </c>
-      <c r="F92" s="37">
-        <v>55.5</v>
-      </c>
-      <c r="G92" s="37">
-        <v>55.5</v>
-      </c>
-      <c r="H92" s="37">
-        <v>55.5</v>
-      </c>
-      <c r="I92" s="36">
-        <v>55.4</v>
       </c>
       <c r="J92" s="7"/>
       <c r="K92" s="7"/>
@@ -7216,20 +7201,20 @@
       <c r="D93" s="40" t="s">
         <v>150</v>
       </c>
-      <c r="E93" s="37">
-        <v>60.5</v>
-      </c>
-      <c r="F93" s="37">
-        <v>60.5</v>
-      </c>
-      <c r="G93" s="37">
-        <v>60.5</v>
-      </c>
-      <c r="H93" s="37">
-        <v>60.5</v>
-      </c>
-      <c r="I93" s="35" t="s">
-        <v>151</v>
+      <c r="E93" s="70">
+        <v>72.0</v>
+      </c>
+      <c r="F93" s="70">
+        <v>72.0</v>
+      </c>
+      <c r="G93" s="70">
+        <v>72.0</v>
+      </c>
+      <c r="H93" s="70">
+        <v>72.0</v>
+      </c>
+      <c r="I93" s="67">
+        <v>74.8</v>
       </c>
       <c r="J93" s="7"/>
       <c r="K93" s="7"/>
@@ -7253,22 +7238,22 @@
       <c r="A94" s="32"/>
       <c r="C94" s="40"/>
       <c r="D94" s="40" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E94" s="37">
-        <v>61.6</v>
+        <v>55.5</v>
       </c>
       <c r="F94" s="37">
-        <v>61.6</v>
+        <v>55.5</v>
       </c>
       <c r="G94" s="37">
-        <v>61.6</v>
+        <v>55.5</v>
       </c>
       <c r="H94" s="37">
-        <v>61.6</v>
+        <v>55.5</v>
       </c>
       <c r="I94" s="36">
-        <v>63.5</v>
+        <v>55.4</v>
       </c>
       <c r="J94" s="7"/>
       <c r="K94" s="7"/>
@@ -7288,26 +7273,26 @@
       <c r="Y94" s="7"/>
       <c r="Z94" s="7"/>
     </row>
-    <row r="95" ht="28.5" customHeight="1">
+    <row r="95" ht="21.0" customHeight="1">
       <c r="A95" s="32"/>
-      <c r="C95" s="33"/>
+      <c r="C95" s="40"/>
       <c r="D95" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="E95" s="37">
+        <v>60.5</v>
+      </c>
+      <c r="F95" s="37">
+        <v>60.5</v>
+      </c>
+      <c r="G95" s="37">
+        <v>60.5</v>
+      </c>
+      <c r="H95" s="37">
+        <v>60.5</v>
+      </c>
+      <c r="I95" s="35" t="s">
         <v>153</v>
-      </c>
-      <c r="E95" s="72">
-        <v>5.1</v>
-      </c>
-      <c r="F95" s="72">
-        <v>5.1</v>
-      </c>
-      <c r="G95" s="72">
-        <v>5.1</v>
-      </c>
-      <c r="H95" s="72">
-        <v>5.1</v>
-      </c>
-      <c r="I95" s="98" t="s">
-        <v>154</v>
       </c>
       <c r="J95" s="7"/>
       <c r="K95" s="7"/>
@@ -7327,26 +7312,26 @@
       <c r="Y95" s="7"/>
       <c r="Z95" s="7"/>
     </row>
-    <row r="96" ht="30.75" customHeight="1">
+    <row r="96" ht="21.0" customHeight="1">
       <c r="A96" s="32"/>
-      <c r="C96" s="33"/>
+      <c r="C96" s="40"/>
       <c r="D96" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="E96" s="72" t="s">
-        <v>156</v>
-      </c>
-      <c r="F96" s="72" t="s">
-        <v>156</v>
-      </c>
-      <c r="G96" s="72" t="s">
-        <v>156</v>
-      </c>
-      <c r="H96" s="72" t="s">
-        <v>156</v>
-      </c>
-      <c r="I96" s="98" t="s">
-        <v>157</v>
+        <v>154</v>
+      </c>
+      <c r="E96" s="37">
+        <v>61.6</v>
+      </c>
+      <c r="F96" s="37">
+        <v>61.6</v>
+      </c>
+      <c r="G96" s="37">
+        <v>61.6</v>
+      </c>
+      <c r="H96" s="37">
+        <v>61.6</v>
+      </c>
+      <c r="I96" s="36">
+        <v>63.5</v>
       </c>
       <c r="J96" s="7"/>
       <c r="K96" s="7"/>
@@ -7366,18 +7351,27 @@
       <c r="Y96" s="7"/>
       <c r="Z96" s="7"/>
     </row>
-    <row r="97" ht="43.5" customHeight="1">
-      <c r="A97" s="7"/>
-      <c r="B97" s="99" t="s">
-        <v>158</v>
-      </c>
-      <c r="C97" s="100"/>
-      <c r="D97" s="9"/>
-      <c r="E97" s="10"/>
-      <c r="F97" s="10"/>
-      <c r="G97" s="10"/>
-      <c r="H97" s="10"/>
-      <c r="I97" s="11"/>
+    <row r="97" ht="28.5" customHeight="1">
+      <c r="A97" s="32"/>
+      <c r="C97" s="33"/>
+      <c r="D97" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="E97" s="72">
+        <v>5.1</v>
+      </c>
+      <c r="F97" s="72">
+        <v>5.1</v>
+      </c>
+      <c r="G97" s="72">
+        <v>5.1</v>
+      </c>
+      <c r="H97" s="72">
+        <v>5.1</v>
+      </c>
+      <c r="I97" s="98" t="s">
+        <v>156</v>
+      </c>
       <c r="J97" s="7"/>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
@@ -7396,17 +7390,27 @@
       <c r="Y97" s="7"/>
       <c r="Z97" s="7"/>
     </row>
-    <row r="98" ht="31.5" customHeight="1">
-      <c r="A98" s="7"/>
-      <c r="C98" s="101" t="s">
+    <row r="98" ht="30.75" customHeight="1">
+      <c r="A98" s="32"/>
+      <c r="C98" s="33"/>
+      <c r="D98" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="E98" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="F98" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="G98" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="H98" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="I98" s="98" t="s">
         <v>159</v>
       </c>
-      <c r="D98" s="40"/>
-      <c r="E98" s="41"/>
-      <c r="F98" s="41"/>
-      <c r="G98" s="41"/>
-      <c r="H98" s="41"/>
-      <c r="I98" s="42"/>
       <c r="J98" s="7"/>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -7425,22 +7429,18 @@
       <c r="Y98" s="7"/>
       <c r="Z98" s="7"/>
     </row>
-    <row r="99" ht="27.0" customHeight="1">
+    <row r="99" ht="43.5" customHeight="1">
       <c r="A99" s="7"/>
-      <c r="B99" s="32"/>
-      <c r="C99" s="43"/>
-      <c r="D99" s="32" t="s">
+      <c r="B99" s="99" t="s">
         <v>160</v>
       </c>
-      <c r="E99" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="F99" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G99" s="30"/>
-      <c r="H99" s="30"/>
-      <c r="I99" s="102"/>
+      <c r="C99" s="100"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="10"/>
+      <c r="F99" s="10"/>
+      <c r="G99" s="10"/>
+      <c r="H99" s="10"/>
+      <c r="I99" s="11"/>
       <c r="J99" s="7"/>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -7459,22 +7459,17 @@
       <c r="Y99" s="7"/>
       <c r="Z99" s="7"/>
     </row>
-    <row r="100" ht="27.0" customHeight="1">
+    <row r="100" ht="31.5" customHeight="1">
       <c r="A100" s="7"/>
-      <c r="B100" s="32"/>
-      <c r="C100" s="43"/>
-      <c r="D100" s="32" t="s">
+      <c r="C100" s="101" t="s">
         <v>161</v>
       </c>
-      <c r="E100" s="55"/>
-      <c r="F100" s="55"/>
-      <c r="G100" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H100" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="I100" s="68"/>
+      <c r="D100" s="40"/>
+      <c r="E100" s="41"/>
+      <c r="F100" s="41"/>
+      <c r="G100" s="41"/>
+      <c r="H100" s="41"/>
+      <c r="I100" s="42"/>
       <c r="J100" s="7"/>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -7493,20 +7488,22 @@
       <c r="Y100" s="7"/>
       <c r="Z100" s="7"/>
     </row>
-    <row r="101" ht="15.75" customHeight="1">
+    <row r="101" ht="27.0" customHeight="1">
       <c r="A101" s="7"/>
       <c r="B101" s="32"/>
       <c r="C101" s="43"/>
       <c r="D101" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="E101" s="55"/>
-      <c r="F101" s="55"/>
-      <c r="G101" s="55"/>
-      <c r="H101" s="55"/>
-      <c r="I101" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="E101" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F101" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G101" s="30"/>
+      <c r="H101" s="30"/>
+      <c r="I101" s="102"/>
       <c r="J101" s="7"/>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
@@ -7525,7 +7522,7 @@
       <c r="Y101" s="7"/>
       <c r="Z101" s="7"/>
     </row>
-    <row r="102" ht="24.75" customHeight="1">
+    <row r="102" ht="27.0" customHeight="1">
       <c r="A102" s="7"/>
       <c r="B102" s="32"/>
       <c r="C102" s="43"/>
@@ -7534,11 +7531,13 @@
       </c>
       <c r="E102" s="55"/>
       <c r="F102" s="55"/>
-      <c r="G102" s="55"/>
-      <c r="H102" s="55"/>
-      <c r="I102" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="G102" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H102" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I102" s="68"/>
       <c r="J102" s="7"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
@@ -7557,7 +7556,7 @@
       <c r="Y102" s="7"/>
       <c r="Z102" s="7"/>
     </row>
-    <row r="103" ht="24.75" customHeight="1">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="7"/>
       <c r="B103" s="32"/>
       <c r="C103" s="43"/>
@@ -7566,13 +7565,11 @@
       </c>
       <c r="E103" s="55"/>
       <c r="F103" s="55"/>
-      <c r="G103" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H103" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="I103" s="68"/>
+      <c r="G103" s="55"/>
+      <c r="H103" s="55"/>
+      <c r="I103" s="68" t="s">
+        <v>42</v>
+      </c>
       <c r="J103" s="7"/>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -7598,15 +7595,13 @@
       <c r="D104" s="32" t="s">
         <v>165</v>
       </c>
-      <c r="E104" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="F104" s="55" t="s">
-        <v>42</v>
-      </c>
+      <c r="E104" s="55"/>
+      <c r="F104" s="55"/>
       <c r="G104" s="55"/>
       <c r="H104" s="55"/>
-      <c r="I104" s="68"/>
+      <c r="I104" s="68" t="s">
+        <v>42</v>
+      </c>
       <c r="J104" s="7"/>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -7640,9 +7635,7 @@
       <c r="H105" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="I105" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="I105" s="68"/>
       <c r="J105" s="7"/>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -7668,14 +7661,14 @@
       <c r="D106" s="32" t="s">
         <v>167</v>
       </c>
-      <c r="E106" s="55"/>
-      <c r="F106" s="55"/>
-      <c r="G106" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H106" s="55" t="s">
-        <v>42</v>
-      </c>
+      <c r="E106" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F106" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="G106" s="55"/>
+      <c r="H106" s="55"/>
       <c r="I106" s="68"/>
       <c r="J106" s="7"/>
       <c r="K106" s="7"/>
@@ -7702,19 +7695,15 @@
       <c r="D107" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="E107" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="F107" s="55" t="s">
-        <v>42</v>
-      </c>
+      <c r="E107" s="55"/>
+      <c r="F107" s="55"/>
       <c r="G107" s="55" t="s">
         <v>42</v>
       </c>
       <c r="H107" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="I107" s="69" t="s">
+      <c r="I107" s="68" t="s">
         <v>42</v>
       </c>
       <c r="J107" s="7"/>
@@ -7735,17 +7724,22 @@
       <c r="Y107" s="7"/>
       <c r="Z107" s="7"/>
     </row>
-    <row r="108" ht="30.75" customHeight="1">
+    <row r="108" ht="24.75" customHeight="1">
       <c r="A108" s="7"/>
-      <c r="C108" s="33" t="s">
+      <c r="B108" s="32"/>
+      <c r="C108" s="43"/>
+      <c r="D108" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="D108" s="40"/>
-      <c r="E108" s="41"/>
-      <c r="F108" s="41"/>
-      <c r="G108" s="41"/>
-      <c r="H108" s="41"/>
-      <c r="I108" s="46"/>
+      <c r="E108" s="55"/>
+      <c r="F108" s="55"/>
+      <c r="G108" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H108" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I108" s="68"/>
       <c r="J108" s="7"/>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -7764,23 +7758,23 @@
       <c r="Y108" s="7"/>
       <c r="Z108" s="7"/>
     </row>
-    <row r="109" ht="22.5" customHeight="1">
+    <row r="109" ht="24.75" customHeight="1">
       <c r="A109" s="7"/>
       <c r="B109" s="32"/>
-      <c r="C109" s="85"/>
-      <c r="D109" s="86" t="s">
+      <c r="C109" s="43"/>
+      <c r="D109" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="E109" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="F109" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="G109" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="H109" s="57" t="s">
+      <c r="E109" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F109" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="G109" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H109" s="55" t="s">
         <v>42</v>
       </c>
       <c r="I109" s="69" t="s">
@@ -7804,24 +7798,17 @@
       <c r="Y109" s="7"/>
       <c r="Z109" s="7"/>
     </row>
-    <row r="110" ht="31.5" customHeight="1">
+    <row r="110" ht="30.75" customHeight="1">
       <c r="A110" s="7"/>
-      <c r="B110" s="32"/>
-      <c r="C110" s="43"/>
-      <c r="D110" s="32" t="s">
+      <c r="C110" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="E110" s="93"/>
-      <c r="F110" s="93"/>
-      <c r="G110" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H110" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="I110" s="39" t="s">
-        <v>42</v>
-      </c>
+      <c r="D110" s="40"/>
+      <c r="E110" s="41"/>
+      <c r="F110" s="41"/>
+      <c r="G110" s="41"/>
+      <c r="H110" s="41"/>
+      <c r="I110" s="46"/>
       <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -7840,17 +7827,28 @@
       <c r="Y110" s="7"/>
       <c r="Z110" s="7"/>
     </row>
-    <row r="111" ht="43.5" customHeight="1">
+    <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="7"/>
-      <c r="C111" s="33" t="s">
+      <c r="B111" s="32"/>
+      <c r="C111" s="85"/>
+      <c r="D111" s="86" t="s">
         <v>172</v>
       </c>
-      <c r="D111" s="40"/>
-      <c r="E111" s="41"/>
-      <c r="F111" s="41"/>
-      <c r="G111" s="41"/>
-      <c r="H111" s="41"/>
-      <c r="I111" s="42"/>
+      <c r="E111" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="F111" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="G111" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="H111" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="I111" s="69" t="s">
+        <v>42</v>
+      </c>
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -7869,22 +7867,22 @@
       <c r="Y111" s="7"/>
       <c r="Z111" s="7"/>
     </row>
-    <row r="112" ht="24.75" customHeight="1">
+    <row r="112" ht="31.5" customHeight="1">
       <c r="A112" s="7"/>
       <c r="B112" s="32"/>
       <c r="C112" s="43"/>
       <c r="D112" s="32" t="s">
         <v>173</v>
       </c>
-      <c r="E112" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="F112" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G112" s="93"/>
-      <c r="H112" s="93"/>
-      <c r="I112" s="94" t="s">
+      <c r="E112" s="93"/>
+      <c r="F112" s="93"/>
+      <c r="G112" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="H112" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I112" s="39" t="s">
         <v>42</v>
       </c>
       <c r="J112" s="7"/>
@@ -7905,22 +7903,17 @@
       <c r="Y112" s="7"/>
       <c r="Z112" s="7"/>
     </row>
-    <row r="113" ht="15.75" customHeight="1">
+    <row r="113" ht="43.5" customHeight="1">
       <c r="A113" s="7"/>
-      <c r="B113" s="32"/>
-      <c r="C113" s="43"/>
-      <c r="D113" s="32" t="s">
+      <c r="C113" s="33" t="s">
         <v>174</v>
       </c>
-      <c r="E113" s="93"/>
-      <c r="F113" s="93"/>
-      <c r="G113" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H113" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="I113" s="68"/>
+      <c r="D113" s="40"/>
+      <c r="E113" s="41"/>
+      <c r="F113" s="41"/>
+      <c r="G113" s="41"/>
+      <c r="H113" s="41"/>
+      <c r="I113" s="42"/>
       <c r="J113" s="7"/>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -7952,13 +7945,9 @@
       <c r="F114" s="93" t="s">
         <v>42</v>
       </c>
-      <c r="G114" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H114" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="I114" s="68" t="s">
+      <c r="G114" s="93"/>
+      <c r="H114" s="93"/>
+      <c r="I114" s="94" t="s">
         <v>42</v>
       </c>
       <c r="J114" s="7"/>
@@ -7979,28 +7968,22 @@
       <c r="Y114" s="7"/>
       <c r="Z114" s="7"/>
     </row>
-    <row r="115" ht="24.75" customHeight="1">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="7"/>
       <c r="B115" s="32"/>
       <c r="C115" s="43"/>
       <c r="D115" s="32" t="s">
         <v>176</v>
       </c>
-      <c r="E115" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="F115" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="G115" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H115" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="I115" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="E115" s="93"/>
+      <c r="F115" s="93"/>
+      <c r="G115" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="H115" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I115" s="68"/>
       <c r="J115" s="7"/>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
@@ -8026,13 +8009,21 @@
       <c r="D116" s="32" t="s">
         <v>177</v>
       </c>
-      <c r="E116" s="55"/>
-      <c r="F116" s="55"/>
-      <c r="G116" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H116" s="55"/>
-      <c r="I116" s="69"/>
+      <c r="E116" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F116" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G116" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="H116" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I116" s="68" t="s">
+        <v>42</v>
+      </c>
       <c r="J116" s="7"/>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -8051,17 +8042,28 @@
       <c r="Y116" s="7"/>
       <c r="Z116" s="7"/>
     </row>
-    <row r="117" ht="27.75" customHeight="1">
+    <row r="117" ht="24.75" customHeight="1">
       <c r="A117" s="7"/>
-      <c r="C117" s="33" t="s">
+      <c r="B117" s="32"/>
+      <c r="C117" s="43"/>
+      <c r="D117" s="32" t="s">
         <v>178</v>
       </c>
-      <c r="D117" s="33"/>
-      <c r="E117" s="41"/>
-      <c r="F117" s="41"/>
-      <c r="G117" s="41"/>
-      <c r="H117" s="41"/>
-      <c r="I117" s="42"/>
+      <c r="E117" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F117" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="G117" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H117" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I117" s="68" t="s">
+        <v>42</v>
+      </c>
       <c r="J117" s="7"/>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -8080,28 +8082,20 @@
       <c r="Y117" s="7"/>
       <c r="Z117" s="7"/>
     </row>
-    <row r="118" ht="27.0" customHeight="1">
+    <row r="118" ht="24.75" customHeight="1">
       <c r="A118" s="7"/>
       <c r="B118" s="32"/>
       <c r="C118" s="43"/>
       <c r="D118" s="32" t="s">
         <v>179</v>
       </c>
-      <c r="E118" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="F118" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G118" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H118" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="I118" s="94" t="s">
-        <v>42</v>
-      </c>
+      <c r="E118" s="55"/>
+      <c r="F118" s="55"/>
+      <c r="G118" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H118" s="55"/>
+      <c r="I118" s="69"/>
       <c r="J118" s="7"/>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -8120,28 +8114,17 @@
       <c r="Y118" s="7"/>
       <c r="Z118" s="7"/>
     </row>
-    <row r="119" ht="27.0" customHeight="1">
+    <row r="119" ht="27.75" customHeight="1">
       <c r="A119" s="7"/>
-      <c r="B119" s="32"/>
-      <c r="C119" s="43"/>
-      <c r="D119" s="32" t="s">
+      <c r="C119" s="33" t="s">
         <v>180</v>
       </c>
-      <c r="E119" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="F119" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G119" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H119" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="I119" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="D119" s="33"/>
+      <c r="E119" s="41"/>
+      <c r="F119" s="41"/>
+      <c r="G119" s="41"/>
+      <c r="H119" s="41"/>
+      <c r="I119" s="42"/>
       <c r="J119" s="7"/>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -8167,19 +8150,19 @@
       <c r="D120" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="E120" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="F120" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="G120" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="H120" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="I120" s="69" t="s">
+      <c r="E120" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F120" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G120" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="H120" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I120" s="94" t="s">
         <v>42</v>
       </c>
       <c r="J120" s="7"/>
@@ -8202,22 +8185,24 @@
     </row>
     <row r="121" ht="27.0" customHeight="1">
       <c r="A121" s="7"/>
-      <c r="B121" s="103"/>
+      <c r="B121" s="32"/>
       <c r="C121" s="43"/>
       <c r="D121" s="32" t="s">
         <v>182</v>
       </c>
-      <c r="E121" s="57"/>
-      <c r="F121" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="G121" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="H121" s="57" t="s">
-        <v>42</v>
-      </c>
-      <c r="I121" s="69" t="s">
+      <c r="E121" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F121" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G121" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="H121" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I121" s="68" t="s">
         <v>42</v>
       </c>
       <c r="J121" s="7"/>
@@ -8245,7 +8230,9 @@
       <c r="D122" s="32" t="s">
         <v>183</v>
       </c>
-      <c r="E122" s="38"/>
+      <c r="E122" s="57" t="s">
+        <v>42</v>
+      </c>
       <c r="F122" s="57" t="s">
         <v>42</v>
       </c>
@@ -8255,7 +8242,9 @@
       <c r="H122" s="57" t="s">
         <v>42</v>
       </c>
-      <c r="I122" s="39"/>
+      <c r="I122" s="69" t="s">
+        <v>42</v>
+      </c>
       <c r="J122" s="7"/>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -8276,16 +8265,22 @@
     </row>
     <row r="123" ht="27.0" customHeight="1">
       <c r="A123" s="7"/>
-      <c r="B123" s="32"/>
+      <c r="B123" s="103"/>
       <c r="C123" s="43"/>
       <c r="D123" s="32" t="s">
         <v>184</v>
       </c>
-      <c r="E123" s="38"/>
-      <c r="F123" s="57"/>
-      <c r="G123" s="57"/>
-      <c r="H123" s="57"/>
-      <c r="I123" s="39" t="s">
+      <c r="E123" s="57"/>
+      <c r="F123" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="G123" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="H123" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="I123" s="69" t="s">
         <v>42</v>
       </c>
       <c r="J123" s="7"/>
@@ -8306,28 +8301,24 @@
       <c r="Y123" s="7"/>
       <c r="Z123" s="7"/>
     </row>
-    <row r="124" ht="25.5" customHeight="1">
+    <row r="124" ht="27.0" customHeight="1">
       <c r="A124" s="7"/>
       <c r="B124" s="32"/>
       <c r="C124" s="43"/>
       <c r="D124" s="32" t="s">
         <v>185</v>
       </c>
-      <c r="E124" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F124" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G124" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H124" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I124" s="39" t="s">
-        <v>42</v>
-      </c>
+      <c r="E124" s="38"/>
+      <c r="F124" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="G124" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="H124" s="57" t="s">
+        <v>42</v>
+      </c>
+      <c r="I124" s="39"/>
       <c r="J124" s="7"/>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
@@ -8346,23 +8337,17 @@
       <c r="Y124" s="7"/>
       <c r="Z124" s="7"/>
     </row>
-    <row r="125" ht="25.5" customHeight="1">
+    <row r="125" ht="27.0" customHeight="1">
       <c r="A125" s="7"/>
       <c r="B125" s="32"/>
       <c r="C125" s="43"/>
       <c r="D125" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="E125" s="62"/>
-      <c r="F125" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G125" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H125" s="62" t="s">
-        <v>42</v>
-      </c>
+      <c r="E125" s="38"/>
+      <c r="F125" s="57"/>
+      <c r="G125" s="57"/>
+      <c r="H125" s="57"/>
       <c r="I125" s="39" t="s">
         <v>42</v>
       </c>
@@ -8386,7 +8371,8 @@
     </row>
     <row r="126" ht="25.5" customHeight="1">
       <c r="A126" s="7"/>
-      <c r="C126" s="32"/>
+      <c r="B126" s="32"/>
+      <c r="C126" s="43"/>
       <c r="D126" s="32" t="s">
         <v>187</v>
       </c>
@@ -8430,9 +8416,7 @@
       <c r="D127" s="32" t="s">
         <v>188</v>
       </c>
-      <c r="E127" s="62" t="s">
-        <v>42</v>
-      </c>
+      <c r="E127" s="62"/>
       <c r="F127" s="62" t="s">
         <v>42</v>
       </c>
@@ -8465,18 +8449,25 @@
     </row>
     <row r="128" ht="25.5" customHeight="1">
       <c r="A128" s="7"/>
-      <c r="B128" s="32"/>
-      <c r="C128" s="43"/>
+      <c r="C128" s="32"/>
       <c r="D128" s="32" t="s">
         <v>189</v>
       </c>
       <c r="E128" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="F128" s="62"/>
-      <c r="G128" s="62"/>
-      <c r="H128" s="62"/>
-      <c r="I128" s="39"/>
+      <c r="F128" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G128" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H128" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I128" s="39" t="s">
+        <v>42</v>
+      </c>
       <c r="J128" s="7"/>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
@@ -8502,7 +8493,9 @@
       <c r="D129" s="32" t="s">
         <v>190</v>
       </c>
-      <c r="E129" s="62"/>
+      <c r="E129" s="62" t="s">
+        <v>42</v>
+      </c>
       <c r="F129" s="62" t="s">
         <v>42</v>
       </c>
@@ -8512,7 +8505,9 @@
       <c r="H129" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="I129" s="39"/>
+      <c r="I129" s="39" t="s">
+        <v>42</v>
+      </c>
       <c r="J129" s="7"/>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -8538,40 +8533,39 @@
       <c r="D130" s="32" t="s">
         <v>191</v>
       </c>
-      <c r="E130" s="62"/>
+      <c r="E130" s="62" t="s">
+        <v>42</v>
+      </c>
       <c r="F130" s="62"/>
       <c r="G130" s="62"/>
       <c r="H130" s="62"/>
-      <c r="I130" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="J130" s="76"/>
-      <c r="K130" s="76"/>
-      <c r="L130" s="76"/>
-      <c r="M130" s="76"/>
-      <c r="N130" s="76"/>
-      <c r="O130" s="76"/>
-      <c r="P130" s="76"/>
-      <c r="Q130" s="76"/>
-      <c r="R130" s="76"/>
-      <c r="S130" s="76"/>
-      <c r="T130" s="76"/>
-      <c r="U130" s="76"/>
-      <c r="V130" s="76"/>
-      <c r="W130" s="76"/>
-      <c r="X130" s="76"/>
-      <c r="Y130" s="76"/>
-      <c r="Z130" s="76"/>
-    </row>
-    <row r="131" ht="43.5" customHeight="1">
+      <c r="I130" s="39"/>
+      <c r="J130" s="7"/>
+      <c r="K130" s="7"/>
+      <c r="L130" s="7"/>
+      <c r="M130" s="7"/>
+      <c r="N130" s="7"/>
+      <c r="O130" s="7"/>
+      <c r="P130" s="7"/>
+      <c r="Q130" s="7"/>
+      <c r="R130" s="7"/>
+      <c r="S130" s="7"/>
+      <c r="T130" s="7"/>
+      <c r="U130" s="7"/>
+      <c r="V130" s="7"/>
+      <c r="W130" s="7"/>
+      <c r="X130" s="7"/>
+      <c r="Y130" s="7"/>
+      <c r="Z130" s="7"/>
+    </row>
+    <row r="131" ht="25.5" customHeight="1">
       <c r="A131" s="7"/>
-      <c r="C131" s="32"/>
+      <c r="B131" s="32"/>
+      <c r="C131" s="43"/>
       <c r="D131" s="32" t="s">
         <v>192</v>
       </c>
-      <c r="E131" s="62" t="s">
-        <v>42</v>
-      </c>
+      <c r="E131" s="62"/>
       <c r="F131" s="62" t="s">
         <v>42</v>
       </c>
@@ -8581,38 +8575,39 @@
       <c r="H131" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="I131" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="J131" s="76"/>
-      <c r="K131" s="76"/>
-      <c r="L131" s="76"/>
-      <c r="M131" s="76"/>
-      <c r="N131" s="76"/>
-      <c r="O131" s="76"/>
-      <c r="P131" s="76"/>
-      <c r="Q131" s="76"/>
-      <c r="R131" s="76"/>
-      <c r="S131" s="76"/>
-      <c r="T131" s="76"/>
-      <c r="U131" s="76"/>
-      <c r="V131" s="76"/>
-      <c r="W131" s="76"/>
-      <c r="X131" s="76"/>
-      <c r="Y131" s="76"/>
-      <c r="Z131" s="76"/>
-    </row>
-    <row r="132" ht="21.75" customHeight="1">
-      <c r="A132" s="82"/>
-      <c r="C132" s="33" t="s">
+      <c r="I131" s="39"/>
+      <c r="J131" s="7"/>
+      <c r="K131" s="7"/>
+      <c r="L131" s="7"/>
+      <c r="M131" s="7"/>
+      <c r="N131" s="7"/>
+      <c r="O131" s="7"/>
+      <c r="P131" s="7"/>
+      <c r="Q131" s="7"/>
+      <c r="R131" s="7"/>
+      <c r="S131" s="7"/>
+      <c r="T131" s="7"/>
+      <c r="U131" s="7"/>
+      <c r="V131" s="7"/>
+      <c r="W131" s="7"/>
+      <c r="X131" s="7"/>
+      <c r="Y131" s="7"/>
+      <c r="Z131" s="7"/>
+    </row>
+    <row r="132" ht="25.5" customHeight="1">
+      <c r="A132" s="7"/>
+      <c r="B132" s="32"/>
+      <c r="C132" s="43"/>
+      <c r="D132" s="32" t="s">
         <v>193</v>
       </c>
-      <c r="D132" s="40"/>
-      <c r="E132" s="41"/>
-      <c r="F132" s="41"/>
-      <c r="G132" s="41"/>
-      <c r="H132" s="41"/>
-      <c r="I132" s="42"/>
+      <c r="E132" s="62"/>
+      <c r="F132" s="62"/>
+      <c r="G132" s="62"/>
+      <c r="H132" s="62"/>
+      <c r="I132" s="39" t="s">
+        <v>42</v>
+      </c>
       <c r="J132" s="76"/>
       <c r="K132" s="76"/>
       <c r="L132" s="76"/>
@@ -8631,27 +8626,26 @@
       <c r="Y132" s="76"/>
       <c r="Z132" s="76"/>
     </row>
-    <row r="133" ht="21.75" customHeight="1">
-      <c r="A133" s="32"/>
-      <c r="B133" s="32"/>
-      <c r="C133" s="43"/>
+    <row r="133" ht="43.5" customHeight="1">
+      <c r="A133" s="7"/>
+      <c r="C133" s="32"/>
       <c r="D133" s="32" t="s">
         <v>194</v>
       </c>
-      <c r="E133" s="104">
-        <v>37.6</v>
-      </c>
-      <c r="F133" s="104">
-        <v>37.6</v>
-      </c>
-      <c r="G133" s="104">
-        <v>37.6</v>
-      </c>
-      <c r="H133" s="104">
-        <v>37.6</v>
-      </c>
-      <c r="I133" s="105">
-        <v>38.6</v>
+      <c r="E133" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F133" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G133" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H133" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I133" s="39" t="s">
+        <v>42</v>
       </c>
       <c r="J133" s="76"/>
       <c r="K133" s="76"/>
@@ -8672,27 +8666,16 @@
       <c r="Z133" s="76"/>
     </row>
     <row r="134" ht="21.75" customHeight="1">
-      <c r="A134" s="32"/>
-      <c r="B134" s="32"/>
-      <c r="C134" s="43"/>
-      <c r="D134" s="32" t="s">
+      <c r="A134" s="82"/>
+      <c r="C134" s="33" t="s">
         <v>195</v>
       </c>
-      <c r="E134" s="106">
-        <v>36.4</v>
-      </c>
-      <c r="F134" s="106">
-        <v>36.4</v>
-      </c>
-      <c r="G134" s="106">
-        <v>36.4</v>
-      </c>
-      <c r="H134" s="106">
-        <v>36.4</v>
-      </c>
-      <c r="I134" s="107">
-        <v>36.4</v>
-      </c>
+      <c r="D134" s="40"/>
+      <c r="E134" s="41"/>
+      <c r="F134" s="41"/>
+      <c r="G134" s="41"/>
+      <c r="H134" s="41"/>
+      <c r="I134" s="42"/>
       <c r="J134" s="76"/>
       <c r="K134" s="76"/>
       <c r="L134" s="76"/>
@@ -8712,16 +8695,27 @@
       <c r="Z134" s="76"/>
     </row>
     <row r="135" ht="21.75" customHeight="1">
-      <c r="A135" s="108"/>
-      <c r="C135" s="33" t="s">
+      <c r="A135" s="32"/>
+      <c r="B135" s="32"/>
+      <c r="C135" s="43"/>
+      <c r="D135" s="32" t="s">
         <v>196</v>
       </c>
-      <c r="D135" s="40"/>
-      <c r="E135" s="66"/>
-      <c r="F135" s="66"/>
-      <c r="G135" s="66"/>
-      <c r="H135" s="66"/>
-      <c r="I135" s="109"/>
+      <c r="E135" s="104">
+        <v>37.6</v>
+      </c>
+      <c r="F135" s="104">
+        <v>37.6</v>
+      </c>
+      <c r="G135" s="104">
+        <v>37.6</v>
+      </c>
+      <c r="H135" s="104">
+        <v>37.6</v>
+      </c>
+      <c r="I135" s="105">
+        <v>38.6</v>
+      </c>
       <c r="J135" s="76"/>
       <c r="K135" s="76"/>
       <c r="L135" s="76"/>
@@ -8745,22 +8739,22 @@
       <c r="B136" s="32"/>
       <c r="C136" s="43"/>
       <c r="D136" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="E136" s="104">
-        <v>42.3</v>
-      </c>
-      <c r="F136" s="104">
-        <v>42.3</v>
-      </c>
-      <c r="G136" s="104">
-        <v>42.3</v>
-      </c>
-      <c r="H136" s="104">
-        <v>42.3</v>
-      </c>
-      <c r="I136" s="105">
-        <v>42.3</v>
+        <v>197</v>
+      </c>
+      <c r="E136" s="106">
+        <v>36.4</v>
+      </c>
+      <c r="F136" s="106">
+        <v>36.4</v>
+      </c>
+      <c r="G136" s="106">
+        <v>36.4</v>
+      </c>
+      <c r="H136" s="106">
+        <v>36.4</v>
+      </c>
+      <c r="I136" s="107">
+        <v>36.4</v>
       </c>
       <c r="J136" s="76"/>
       <c r="K136" s="76"/>
@@ -8781,27 +8775,16 @@
       <c r="Z136" s="76"/>
     </row>
     <row r="137" ht="21.75" customHeight="1">
-      <c r="A137" s="32"/>
-      <c r="B137" s="32"/>
-      <c r="C137" s="43"/>
-      <c r="D137" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="E137" s="106">
-        <v>37.4</v>
-      </c>
-      <c r="F137" s="106">
-        <v>37.4</v>
-      </c>
-      <c r="G137" s="106">
-        <v>37.4</v>
-      </c>
-      <c r="H137" s="106">
-        <v>37.4</v>
-      </c>
-      <c r="I137" s="107">
-        <v>37.4</v>
-      </c>
+      <c r="A137" s="108"/>
+      <c r="C137" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="D137" s="40"/>
+      <c r="E137" s="66"/>
+      <c r="F137" s="66"/>
+      <c r="G137" s="66"/>
+      <c r="H137" s="66"/>
+      <c r="I137" s="109"/>
       <c r="J137" s="76"/>
       <c r="K137" s="76"/>
       <c r="L137" s="76"/>
@@ -8821,16 +8804,27 @@
       <c r="Z137" s="76"/>
     </row>
     <row r="138" ht="21.75" customHeight="1">
-      <c r="A138" s="108"/>
-      <c r="C138" s="33" t="s">
-        <v>197</v>
-      </c>
-      <c r="D138" s="40"/>
-      <c r="E138" s="66"/>
-      <c r="F138" s="66"/>
-      <c r="G138" s="66"/>
-      <c r="H138" s="66"/>
-      <c r="I138" s="109"/>
+      <c r="A138" s="32"/>
+      <c r="B138" s="32"/>
+      <c r="C138" s="43"/>
+      <c r="D138" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="E138" s="104">
+        <v>42.3</v>
+      </c>
+      <c r="F138" s="104">
+        <v>42.3</v>
+      </c>
+      <c r="G138" s="104">
+        <v>42.3</v>
+      </c>
+      <c r="H138" s="104">
+        <v>42.3</v>
+      </c>
+      <c r="I138" s="105">
+        <v>42.3</v>
+      </c>
       <c r="J138" s="76"/>
       <c r="K138" s="76"/>
       <c r="L138" s="76"/>
@@ -8854,22 +8848,22 @@
       <c r="B139" s="32"/>
       <c r="C139" s="43"/>
       <c r="D139" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="E139" s="104">
-        <v>57.0</v>
-      </c>
-      <c r="F139" s="104">
-        <v>57.0</v>
-      </c>
-      <c r="G139" s="104">
-        <v>57.0</v>
-      </c>
-      <c r="H139" s="104">
-        <v>57.0</v>
-      </c>
-      <c r="I139" s="105">
-        <v>57.0</v>
+        <v>197</v>
+      </c>
+      <c r="E139" s="106">
+        <v>37.4</v>
+      </c>
+      <c r="F139" s="106">
+        <v>37.4</v>
+      </c>
+      <c r="G139" s="106">
+        <v>37.4</v>
+      </c>
+      <c r="H139" s="106">
+        <v>37.4</v>
+      </c>
+      <c r="I139" s="107">
+        <v>37.4</v>
       </c>
       <c r="J139" s="76"/>
       <c r="K139" s="76"/>
@@ -8890,27 +8884,16 @@
       <c r="Z139" s="76"/>
     </row>
     <row r="140" ht="21.75" customHeight="1">
-      <c r="A140" s="32"/>
-      <c r="B140" s="32"/>
-      <c r="C140" s="43"/>
-      <c r="D140" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="E140" s="106">
-        <v>56.0</v>
-      </c>
-      <c r="F140" s="106">
-        <v>56.0</v>
-      </c>
-      <c r="G140" s="106">
-        <v>56.0</v>
-      </c>
-      <c r="H140" s="106">
-        <v>56.0</v>
-      </c>
-      <c r="I140" s="107">
-        <v>56.0</v>
-      </c>
+      <c r="A140" s="108"/>
+      <c r="C140" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="D140" s="40"/>
+      <c r="E140" s="66"/>
+      <c r="F140" s="66"/>
+      <c r="G140" s="66"/>
+      <c r="H140" s="66"/>
+      <c r="I140" s="109"/>
       <c r="J140" s="76"/>
       <c r="K140" s="76"/>
       <c r="L140" s="76"/>
@@ -8930,16 +8913,27 @@
       <c r="Z140" s="76"/>
     </row>
     <row r="141" ht="21.75" customHeight="1">
-      <c r="A141" s="82"/>
-      <c r="C141" s="33" t="s">
-        <v>198</v>
-      </c>
-      <c r="D141" s="40"/>
-      <c r="E141" s="66"/>
-      <c r="F141" s="66"/>
-      <c r="G141" s="66"/>
-      <c r="H141" s="66"/>
-      <c r="I141" s="109"/>
+      <c r="A141" s="32"/>
+      <c r="B141" s="32"/>
+      <c r="C141" s="43"/>
+      <c r="D141" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="E141" s="104">
+        <v>57.0</v>
+      </c>
+      <c r="F141" s="104">
+        <v>57.0</v>
+      </c>
+      <c r="G141" s="104">
+        <v>57.0</v>
+      </c>
+      <c r="H141" s="104">
+        <v>57.0</v>
+      </c>
+      <c r="I141" s="105">
+        <v>57.0</v>
+      </c>
       <c r="J141" s="76"/>
       <c r="K141" s="76"/>
       <c r="L141" s="76"/>
@@ -8963,22 +8957,22 @@
       <c r="B142" s="32"/>
       <c r="C142" s="43"/>
       <c r="D142" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="E142" s="104">
-        <v>54.3</v>
-      </c>
-      <c r="F142" s="104">
-        <v>54.3</v>
-      </c>
-      <c r="G142" s="104">
-        <v>54.3</v>
-      </c>
-      <c r="H142" s="104">
-        <v>54.3</v>
-      </c>
-      <c r="I142" s="105">
-        <v>54.3</v>
+        <v>197</v>
+      </c>
+      <c r="E142" s="106">
+        <v>56.0</v>
+      </c>
+      <c r="F142" s="106">
+        <v>56.0</v>
+      </c>
+      <c r="G142" s="106">
+        <v>56.0</v>
+      </c>
+      <c r="H142" s="106">
+        <v>56.0</v>
+      </c>
+      <c r="I142" s="107">
+        <v>56.0</v>
       </c>
       <c r="J142" s="76"/>
       <c r="K142" s="76"/>
@@ -8999,27 +8993,16 @@
       <c r="Z142" s="76"/>
     </row>
     <row r="143" ht="21.75" customHeight="1">
-      <c r="A143" s="32"/>
-      <c r="B143" s="32"/>
-      <c r="C143" s="43"/>
-      <c r="D143" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="E143" s="106">
-        <v>48.9</v>
-      </c>
-      <c r="F143" s="106">
-        <v>48.9</v>
-      </c>
-      <c r="G143" s="106">
-        <v>48.9</v>
-      </c>
-      <c r="H143" s="106">
-        <v>48.9</v>
-      </c>
-      <c r="I143" s="107">
-        <v>48.9</v>
-      </c>
+      <c r="A143" s="82"/>
+      <c r="C143" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="D143" s="40"/>
+      <c r="E143" s="66"/>
+      <c r="F143" s="66"/>
+      <c r="G143" s="66"/>
+      <c r="H143" s="66"/>
+      <c r="I143" s="109"/>
       <c r="J143" s="76"/>
       <c r="K143" s="76"/>
       <c r="L143" s="76"/>
@@ -9038,17 +9021,28 @@
       <c r="Y143" s="76"/>
       <c r="Z143" s="76"/>
     </row>
-    <row r="144" ht="27.75" customHeight="1">
-      <c r="A144" s="7"/>
-      <c r="C144" s="60" t="s">
-        <v>9</v>
-      </c>
-      <c r="D144" s="40"/>
-      <c r="E144" s="64"/>
-      <c r="F144" s="64"/>
-      <c r="G144" s="64"/>
-      <c r="H144" s="64"/>
-      <c r="I144" s="65"/>
+    <row r="144" ht="21.75" customHeight="1">
+      <c r="A144" s="32"/>
+      <c r="B144" s="32"/>
+      <c r="C144" s="43"/>
+      <c r="D144" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="E144" s="104">
+        <v>54.3</v>
+      </c>
+      <c r="F144" s="104">
+        <v>54.3</v>
+      </c>
+      <c r="G144" s="104">
+        <v>54.3</v>
+      </c>
+      <c r="H144" s="104">
+        <v>54.3</v>
+      </c>
+      <c r="I144" s="105">
+        <v>54.3</v>
+      </c>
       <c r="J144" s="76"/>
       <c r="K144" s="76"/>
       <c r="L144" s="76"/>
@@ -9067,26 +9061,27 @@
       <c r="Y144" s="76"/>
       <c r="Z144" s="76"/>
     </row>
-    <row r="145" ht="27.75" customHeight="1">
-      <c r="A145" s="7"/>
-      <c r="C145" s="40"/>
-      <c r="D145" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="E145" s="66">
-        <v>95.8</v>
-      </c>
-      <c r="F145" s="66">
-        <v>95.8</v>
-      </c>
-      <c r="G145" s="66">
-        <v>95.8</v>
-      </c>
-      <c r="H145" s="66">
-        <v>95.8</v>
-      </c>
-      <c r="I145" s="67">
-        <v>95.8</v>
+    <row r="145" ht="21.75" customHeight="1">
+      <c r="A145" s="32"/>
+      <c r="B145" s="32"/>
+      <c r="C145" s="43"/>
+      <c r="D145" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="E145" s="106">
+        <v>48.9</v>
+      </c>
+      <c r="F145" s="106">
+        <v>48.9</v>
+      </c>
+      <c r="G145" s="106">
+        <v>48.9</v>
+      </c>
+      <c r="H145" s="106">
+        <v>48.9</v>
+      </c>
+      <c r="I145" s="107">
+        <v>48.9</v>
       </c>
       <c r="J145" s="76"/>
       <c r="K145" s="76"/>
@@ -9106,27 +9101,17 @@
       <c r="Y145" s="76"/>
       <c r="Z145" s="76"/>
     </row>
-    <row r="146" ht="43.5" customHeight="1">
+    <row r="146" ht="27.75" customHeight="1">
       <c r="A146" s="7"/>
-      <c r="C146" s="33"/>
-      <c r="D146" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="E146" s="70">
-        <v>24.3</v>
-      </c>
-      <c r="F146" s="70">
-        <v>24.3</v>
-      </c>
-      <c r="G146" s="70">
-        <v>24.3</v>
-      </c>
-      <c r="H146" s="70">
-        <v>24.3</v>
-      </c>
-      <c r="I146" s="67">
-        <v>24.3</v>
-      </c>
+      <c r="C146" s="60" t="s">
+        <v>9</v>
+      </c>
+      <c r="D146" s="40"/>
+      <c r="E146" s="64"/>
+      <c r="F146" s="64"/>
+      <c r="G146" s="64"/>
+      <c r="H146" s="64"/>
+      <c r="I146" s="65"/>
       <c r="J146" s="76"/>
       <c r="K146" s="76"/>
       <c r="L146" s="76"/>
@@ -9145,57 +9130,66 @@
       <c r="Y146" s="76"/>
       <c r="Z146" s="76"/>
     </row>
-    <row r="147" ht="31.5" customHeight="1">
+    <row r="147" ht="27.75" customHeight="1">
       <c r="A147" s="7"/>
-      <c r="C147" s="32"/>
+      <c r="C147" s="40"/>
       <c r="D147" s="40" t="s">
         <v>201</v>
       </c>
-      <c r="E147" s="37">
-        <v>5.0</v>
-      </c>
-      <c r="F147" s="37">
-        <v>5.0</v>
-      </c>
-      <c r="G147" s="37">
-        <v>5.0</v>
-      </c>
-      <c r="H147" s="37">
-        <v>5.0</v>
-      </c>
-      <c r="I147" s="63">
-        <v>4.0</v>
-      </c>
-      <c r="J147" s="7"/>
-      <c r="K147" s="7"/>
-      <c r="L147" s="7"/>
-      <c r="M147" s="7"/>
-      <c r="N147" s="7"/>
-      <c r="O147" s="7"/>
-      <c r="P147" s="7"/>
-      <c r="Q147" s="7"/>
-      <c r="R147" s="7"/>
-      <c r="S147" s="7"/>
-      <c r="T147" s="7"/>
-      <c r="U147" s="7"/>
-      <c r="V147" s="7"/>
-      <c r="W147" s="7"/>
-      <c r="X147" s="7"/>
-      <c r="Y147" s="7"/>
-      <c r="Z147" s="7"/>
+      <c r="E147" s="66">
+        <v>95.8</v>
+      </c>
+      <c r="F147" s="66">
+        <v>95.8</v>
+      </c>
+      <c r="G147" s="66">
+        <v>95.8</v>
+      </c>
+      <c r="H147" s="66">
+        <v>95.8</v>
+      </c>
+      <c r="I147" s="67">
+        <v>95.8</v>
+      </c>
+      <c r="J147" s="76"/>
+      <c r="K147" s="76"/>
+      <c r="L147" s="76"/>
+      <c r="M147" s="76"/>
+      <c r="N147" s="76"/>
+      <c r="O147" s="76"/>
+      <c r="P147" s="76"/>
+      <c r="Q147" s="76"/>
+      <c r="R147" s="76"/>
+      <c r="S147" s="76"/>
+      <c r="T147" s="76"/>
+      <c r="U147" s="76"/>
+      <c r="V147" s="76"/>
+      <c r="W147" s="76"/>
+      <c r="X147" s="76"/>
+      <c r="Y147" s="76"/>
+      <c r="Z147" s="76"/>
     </row>
     <row r="148" ht="43.5" customHeight="1">
-      <c r="A148" s="75"/>
-      <c r="B148" s="110" t="s">
+      <c r="A148" s="7"/>
+      <c r="C148" s="33"/>
+      <c r="D148" s="40" t="s">
         <v>202</v>
       </c>
-      <c r="C148" s="100"/>
-      <c r="D148" s="8"/>
-      <c r="E148" s="10"/>
-      <c r="F148" s="10"/>
-      <c r="G148" s="10"/>
-      <c r="H148" s="10"/>
-      <c r="I148" s="11"/>
+      <c r="E148" s="70">
+        <v>24.3</v>
+      </c>
+      <c r="F148" s="70">
+        <v>24.3</v>
+      </c>
+      <c r="G148" s="70">
+        <v>24.3</v>
+      </c>
+      <c r="H148" s="70">
+        <v>24.3</v>
+      </c>
+      <c r="I148" s="67">
+        <v>24.3</v>
+      </c>
       <c r="J148" s="76"/>
       <c r="K148" s="76"/>
       <c r="L148" s="76"/>
@@ -9214,51 +9208,57 @@
       <c r="Y148" s="76"/>
       <c r="Z148" s="76"/>
     </row>
-    <row r="149" ht="43.5" customHeight="1">
-      <c r="A149" s="76"/>
-      <c r="B149" s="111"/>
-      <c r="C149" s="112" t="s">
+    <row r="149" ht="31.5" customHeight="1">
+      <c r="A149" s="7"/>
+      <c r="C149" s="32"/>
+      <c r="D149" s="40" t="s">
         <v>203</v>
       </c>
-      <c r="E149" s="113"/>
-      <c r="F149" s="113"/>
-      <c r="G149" s="113"/>
-      <c r="H149" s="113"/>
-      <c r="I149" s="114"/>
-      <c r="J149" s="76"/>
-      <c r="K149" s="76"/>
-      <c r="L149" s="76"/>
-      <c r="M149" s="76"/>
-      <c r="N149" s="76"/>
-      <c r="O149" s="76"/>
-      <c r="P149" s="76"/>
-      <c r="Q149" s="76"/>
-      <c r="R149" s="76"/>
-      <c r="S149" s="76"/>
-      <c r="T149" s="76"/>
-      <c r="U149" s="76"/>
-      <c r="V149" s="76"/>
-      <c r="W149" s="76"/>
-      <c r="X149" s="76"/>
-      <c r="Y149" s="76"/>
-      <c r="Z149" s="76"/>
-    </row>
-    <row r="150" ht="24.0" customHeight="1">
-      <c r="A150" s="76"/>
-      <c r="B150" s="7"/>
-      <c r="C150" s="43"/>
-      <c r="D150" s="32" t="s">
+      <c r="E149" s="37">
+        <v>5.0</v>
+      </c>
+      <c r="F149" s="37">
+        <v>5.0</v>
+      </c>
+      <c r="G149" s="37">
+        <v>5.0</v>
+      </c>
+      <c r="H149" s="37">
+        <v>5.0</v>
+      </c>
+      <c r="I149" s="63">
+        <v>4.0</v>
+      </c>
+      <c r="J149" s="7"/>
+      <c r="K149" s="7"/>
+      <c r="L149" s="7"/>
+      <c r="M149" s="7"/>
+      <c r="N149" s="7"/>
+      <c r="O149" s="7"/>
+      <c r="P149" s="7"/>
+      <c r="Q149" s="7"/>
+      <c r="R149" s="7"/>
+      <c r="S149" s="7"/>
+      <c r="T149" s="7"/>
+      <c r="U149" s="7"/>
+      <c r="V149" s="7"/>
+      <c r="W149" s="7"/>
+      <c r="X149" s="7"/>
+      <c r="Y149" s="7"/>
+      <c r="Z149" s="7"/>
+    </row>
+    <row r="150" ht="43.5" customHeight="1">
+      <c r="A150" s="75"/>
+      <c r="B150" s="110" t="s">
         <v>204</v>
       </c>
-      <c r="E150" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="F150" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G150" s="30"/>
-      <c r="H150" s="30"/>
-      <c r="I150" s="102"/>
+      <c r="C150" s="100"/>
+      <c r="D150" s="8"/>
+      <c r="E150" s="10"/>
+      <c r="F150" s="10"/>
+      <c r="G150" s="10"/>
+      <c r="H150" s="10"/>
+      <c r="I150" s="11"/>
       <c r="J150" s="76"/>
       <c r="K150" s="76"/>
       <c r="L150" s="76"/>
@@ -9277,24 +9277,17 @@
       <c r="Y150" s="76"/>
       <c r="Z150" s="76"/>
     </row>
-    <row r="151" ht="34.5" customHeight="1">
+    <row r="151" ht="43.5" customHeight="1">
       <c r="A151" s="76"/>
-      <c r="B151" s="7"/>
-      <c r="C151" s="85"/>
-      <c r="D151" s="86" t="s">
+      <c r="B151" s="111"/>
+      <c r="C151" s="112" t="s">
         <v>205</v>
       </c>
-      <c r="E151" s="30"/>
-      <c r="F151" s="47"/>
-      <c r="G151" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H151" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="I151" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="E151" s="113"/>
+      <c r="F151" s="113"/>
+      <c r="G151" s="113"/>
+      <c r="H151" s="113"/>
+      <c r="I151" s="114"/>
       <c r="J151" s="76"/>
       <c r="K151" s="76"/>
       <c r="L151" s="76"/>
@@ -9320,21 +9313,15 @@
       <c r="D152" s="32" t="s">
         <v>206</v>
       </c>
-      <c r="E152" s="30">
-        <v>8.0</v>
-      </c>
-      <c r="F152" s="30">
-        <v>8.0</v>
-      </c>
-      <c r="G152" s="30">
-        <v>16.0</v>
-      </c>
-      <c r="H152" s="30">
-        <v>16.0</v>
-      </c>
-      <c r="I152" s="48">
-        <v>16.0</v>
-      </c>
+      <c r="E152" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F152" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G152" s="30"/>
+      <c r="H152" s="30"/>
+      <c r="I152" s="102"/>
       <c r="J152" s="76"/>
       <c r="K152" s="76"/>
       <c r="L152" s="76"/>
@@ -9353,19 +9340,15 @@
       <c r="Y152" s="76"/>
       <c r="Z152" s="76"/>
     </row>
-    <row r="153" ht="36.0" customHeight="1">
-      <c r="A153" s="7"/>
+    <row r="153" ht="34.5" customHeight="1">
+      <c r="A153" s="76"/>
       <c r="B153" s="7"/>
-      <c r="C153" s="43"/>
-      <c r="D153" s="32" t="s">
+      <c r="C153" s="85"/>
+      <c r="D153" s="86" t="s">
         <v>207</v>
       </c>
-      <c r="E153" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="F153" s="55" t="s">
-        <v>42</v>
-      </c>
+      <c r="E153" s="30"/>
+      <c r="F153" s="47"/>
       <c r="G153" s="55" t="s">
         <v>42</v>
       </c>
@@ -9394,22 +9377,26 @@
       <c r="Z153" s="76"/>
     </row>
     <row r="154" ht="24.0" customHeight="1">
-      <c r="A154" s="7"/>
+      <c r="A154" s="76"/>
       <c r="B154" s="7"/>
       <c r="C154" s="43"/>
       <c r="D154" s="32" t="s">
         <v>208</v>
       </c>
-      <c r="E154" s="55"/>
-      <c r="F154" s="55"/>
-      <c r="G154" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H154" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="I154" s="68" t="s">
-        <v>42</v>
+      <c r="E154" s="30">
+        <v>8.0</v>
+      </c>
+      <c r="F154" s="30">
+        <v>8.0</v>
+      </c>
+      <c r="G154" s="30">
+        <v>16.0</v>
+      </c>
+      <c r="H154" s="30">
+        <v>16.0</v>
+      </c>
+      <c r="I154" s="48">
+        <v>16.0</v>
       </c>
       <c r="J154" s="76"/>
       <c r="K154" s="76"/>
@@ -9429,7 +9416,7 @@
       <c r="Y154" s="76"/>
       <c r="Z154" s="76"/>
     </row>
-    <row r="155" ht="24.0" customHeight="1">
+    <row r="155" ht="36.0" customHeight="1">
       <c r="A155" s="7"/>
       <c r="B155" s="7"/>
       <c r="C155" s="43"/>
@@ -9442,26 +9429,32 @@
       <c r="F155" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="G155" s="55"/>
-      <c r="H155" s="55"/>
-      <c r="I155" s="68"/>
-      <c r="J155" s="7"/>
-      <c r="K155" s="7"/>
-      <c r="L155" s="7"/>
-      <c r="M155" s="7"/>
-      <c r="N155" s="7"/>
-      <c r="O155" s="7"/>
-      <c r="P155" s="7"/>
-      <c r="Q155" s="7"/>
-      <c r="R155" s="7"/>
-      <c r="S155" s="7"/>
-      <c r="T155" s="7"/>
-      <c r="U155" s="7"/>
-      <c r="V155" s="7"/>
-      <c r="W155" s="7"/>
-      <c r="X155" s="7"/>
-      <c r="Y155" s="7"/>
-      <c r="Z155" s="7"/>
+      <c r="G155" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H155" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I155" s="68" t="s">
+        <v>42</v>
+      </c>
+      <c r="J155" s="76"/>
+      <c r="K155" s="76"/>
+      <c r="L155" s="76"/>
+      <c r="M155" s="76"/>
+      <c r="N155" s="76"/>
+      <c r="O155" s="76"/>
+      <c r="P155" s="76"/>
+      <c r="Q155" s="76"/>
+      <c r="R155" s="76"/>
+      <c r="S155" s="76"/>
+      <c r="T155" s="76"/>
+      <c r="U155" s="76"/>
+      <c r="V155" s="76"/>
+      <c r="W155" s="76"/>
+      <c r="X155" s="76"/>
+      <c r="Y155" s="76"/>
+      <c r="Z155" s="76"/>
     </row>
     <row r="156" ht="24.0" customHeight="1">
       <c r="A156" s="7"/>
@@ -9470,12 +9463,8 @@
       <c r="D156" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="E156" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="F156" s="55" t="s">
-        <v>42</v>
-      </c>
+      <c r="E156" s="55"/>
+      <c r="F156" s="55"/>
       <c r="G156" s="55" t="s">
         <v>42</v>
       </c>
@@ -9485,23 +9474,23 @@
       <c r="I156" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="J156" s="7"/>
-      <c r="K156" s="7"/>
-      <c r="L156" s="7"/>
-      <c r="M156" s="7"/>
-      <c r="N156" s="7"/>
-      <c r="O156" s="7"/>
-      <c r="P156" s="7"/>
-      <c r="Q156" s="7"/>
-      <c r="R156" s="7"/>
-      <c r="S156" s="7"/>
-      <c r="T156" s="7"/>
-      <c r="U156" s="7"/>
-      <c r="V156" s="7"/>
-      <c r="W156" s="7"/>
-      <c r="X156" s="7"/>
-      <c r="Y156" s="7"/>
-      <c r="Z156" s="7"/>
+      <c r="J156" s="76"/>
+      <c r="K156" s="76"/>
+      <c r="L156" s="76"/>
+      <c r="M156" s="76"/>
+      <c r="N156" s="76"/>
+      <c r="O156" s="76"/>
+      <c r="P156" s="76"/>
+      <c r="Q156" s="76"/>
+      <c r="R156" s="76"/>
+      <c r="S156" s="76"/>
+      <c r="T156" s="76"/>
+      <c r="U156" s="76"/>
+      <c r="V156" s="76"/>
+      <c r="W156" s="76"/>
+      <c r="X156" s="76"/>
+      <c r="Y156" s="76"/>
+      <c r="Z156" s="76"/>
     </row>
     <row r="157" ht="24.0" customHeight="1">
       <c r="A157" s="7"/>
@@ -9516,12 +9505,8 @@
       <c r="F157" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="G157" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H157" s="55" t="s">
-        <v>42</v>
-      </c>
+      <c r="G157" s="55"/>
+      <c r="H157" s="55"/>
       <c r="I157" s="68"/>
       <c r="J157" s="7"/>
       <c r="K157" s="7"/>
@@ -9541,7 +9526,7 @@
       <c r="Y157" s="7"/>
       <c r="Z157" s="7"/>
     </row>
-    <row r="158" ht="45.0" customHeight="1">
+    <row r="158" ht="24.0" customHeight="1">
       <c r="A158" s="7"/>
       <c r="B158" s="7"/>
       <c r="C158" s="43"/>
@@ -9581,24 +9566,26 @@
       <c r="Y158" s="7"/>
       <c r="Z158" s="7"/>
     </row>
-    <row r="159" ht="36.0" customHeight="1">
+    <row r="159" ht="24.0" customHeight="1">
       <c r="A159" s="7"/>
       <c r="B159" s="7"/>
       <c r="C159" s="43"/>
       <c r="D159" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="E159" s="55"/>
-      <c r="F159" s="55"/>
+      <c r="E159" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F159" s="55" t="s">
+        <v>42</v>
+      </c>
       <c r="G159" s="55" t="s">
         <v>42</v>
       </c>
       <c r="H159" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="I159" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="I159" s="68"/>
       <c r="J159" s="7"/>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -9617,22 +9604,26 @@
       <c r="Y159" s="7"/>
       <c r="Z159" s="7"/>
     </row>
-    <row r="160" ht="24.0" customHeight="1">
+    <row r="160" ht="45.0" customHeight="1">
       <c r="A160" s="7"/>
       <c r="B160" s="7"/>
-      <c r="C160" s="96"/>
-      <c r="D160" s="97" t="s">
+      <c r="C160" s="43"/>
+      <c r="D160" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="E160" s="55"/>
-      <c r="F160" s="55"/>
+      <c r="E160" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F160" s="55" t="s">
+        <v>42</v>
+      </c>
       <c r="G160" s="55" t="s">
         <v>42</v>
       </c>
       <c r="H160" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="I160" s="69" t="s">
+      <c r="I160" s="68" t="s">
         <v>42</v>
       </c>
       <c r="J160" s="7"/>
@@ -9653,24 +9644,22 @@
       <c r="Y160" s="7"/>
       <c r="Z160" s="7"/>
     </row>
-    <row r="161" ht="24.0" customHeight="1">
+    <row r="161" ht="36.0" customHeight="1">
       <c r="A161" s="7"/>
-      <c r="B161" s="32" t="s">
+      <c r="B161" s="7"/>
+      <c r="C161" s="43"/>
+      <c r="D161" s="32" t="s">
         <v>215</v>
       </c>
-      <c r="E161" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F161" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G161" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H161" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I161" s="39" t="s">
+      <c r="E161" s="55"/>
+      <c r="F161" s="55"/>
+      <c r="G161" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H161" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I161" s="68" t="s">
         <v>42</v>
       </c>
       <c r="J161" s="7"/>
@@ -9693,22 +9682,20 @@
     </row>
     <row r="162" ht="24.0" customHeight="1">
       <c r="A162" s="7"/>
-      <c r="B162" s="32" t="s">
+      <c r="B162" s="7"/>
+      <c r="C162" s="96"/>
+      <c r="D162" s="97" t="s">
         <v>216</v>
       </c>
-      <c r="E162" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F162" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G162" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H162" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I162" s="39" t="s">
+      <c r="E162" s="55"/>
+      <c r="F162" s="55"/>
+      <c r="G162" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H162" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I162" s="69" t="s">
         <v>42</v>
       </c>
       <c r="J162" s="7"/>
@@ -9734,8 +9721,12 @@
       <c r="B163" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="E163" s="62"/>
-      <c r="F163" s="62"/>
+      <c r="E163" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F163" s="62" t="s">
+        <v>42</v>
+      </c>
       <c r="G163" s="62" t="s">
         <v>42</v>
       </c>
@@ -9765,15 +9756,24 @@
     </row>
     <row r="164" ht="24.0" customHeight="1">
       <c r="A164" s="7"/>
-      <c r="C164" s="33" t="s">
+      <c r="B164" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="D164" s="40"/>
-      <c r="E164" s="41"/>
-      <c r="F164" s="41"/>
-      <c r="G164" s="41"/>
-      <c r="H164" s="41"/>
-      <c r="I164" s="42"/>
+      <c r="E164" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F164" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G164" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H164" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I164" s="39" t="s">
+        <v>42</v>
+      </c>
       <c r="J164" s="7"/>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
@@ -9792,26 +9792,20 @@
       <c r="Y164" s="7"/>
       <c r="Z164" s="7"/>
     </row>
-    <row r="165" ht="33.75" customHeight="1">
+    <row r="165" ht="24.0" customHeight="1">
       <c r="A165" s="7"/>
-      <c r="B165" s="27"/>
-      <c r="C165" s="85"/>
-      <c r="D165" s="86" t="s">
+      <c r="B165" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="E165" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="F165" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G165" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H165" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="I165" s="94" t="s">
+      <c r="E165" s="62"/>
+      <c r="F165" s="62"/>
+      <c r="G165" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H165" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I165" s="39" t="s">
         <v>42</v>
       </c>
       <c r="J165" s="7"/>
@@ -9832,28 +9826,17 @@
       <c r="Y165" s="7"/>
       <c r="Z165" s="7"/>
     </row>
-    <row r="166" ht="34.5" customHeight="1">
+    <row r="166" ht="24.0" customHeight="1">
       <c r="A166" s="7"/>
-      <c r="B166" s="27"/>
-      <c r="C166" s="85"/>
-      <c r="D166" s="86" t="s">
+      <c r="C166" s="33" t="s">
         <v>220</v>
       </c>
-      <c r="E166" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="F166" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G166" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H166" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="I166" s="94" t="s">
-        <v>42</v>
-      </c>
+      <c r="D166" s="40"/>
+      <c r="E166" s="41"/>
+      <c r="F166" s="41"/>
+      <c r="G166" s="41"/>
+      <c r="H166" s="41"/>
+      <c r="I166" s="42"/>
       <c r="J166" s="7"/>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -9872,26 +9855,26 @@
       <c r="Y166" s="7"/>
       <c r="Z166" s="7"/>
     </row>
-    <row r="167" ht="15.75" customHeight="1">
+    <row r="167" ht="33.75" customHeight="1">
       <c r="A167" s="7"/>
       <c r="B167" s="27"/>
-      <c r="C167" s="43"/>
-      <c r="D167" s="32" t="s">
+      <c r="C167" s="85"/>
+      <c r="D167" s="86" t="s">
         <v>221</v>
       </c>
-      <c r="E167" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="F167" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="G167" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H167" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="I167" s="69" t="s">
+      <c r="E167" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F167" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G167" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="H167" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I167" s="94" t="s">
         <v>42</v>
       </c>
       <c r="J167" s="7"/>
@@ -9914,19 +9897,26 @@
     </row>
     <row r="168" ht="34.5" customHeight="1">
       <c r="A168" s="7"/>
-      <c r="C168" s="32"/>
-      <c r="D168" s="32" t="s">
+      <c r="B168" s="27"/>
+      <c r="C168" s="85"/>
+      <c r="D168" s="86" t="s">
         <v>222</v>
       </c>
-      <c r="E168" s="62"/>
-      <c r="F168" s="62"/>
-      <c r="G168" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H168" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I168" s="39"/>
+      <c r="E168" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F168" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G168" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="H168" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I168" s="94" t="s">
+        <v>42</v>
+      </c>
       <c r="J168" s="7"/>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
@@ -9945,21 +9935,28 @@
       <c r="Y168" s="7"/>
       <c r="Z168" s="7"/>
     </row>
-    <row r="169" ht="36.0" customHeight="1">
+    <row r="169" ht="15.75" customHeight="1">
       <c r="A169" s="7"/>
-      <c r="C169" s="32"/>
+      <c r="B169" s="27"/>
+      <c r="C169" s="43"/>
       <c r="D169" s="32" t="s">
         <v>223</v>
       </c>
-      <c r="E169" s="62"/>
-      <c r="F169" s="37"/>
-      <c r="G169" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H169" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I169" s="39"/>
+      <c r="E169" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F169" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="G169" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H169" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I169" s="69" t="s">
+        <v>42</v>
+      </c>
       <c r="J169" s="7"/>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
@@ -9978,21 +9975,21 @@
       <c r="Y169" s="7"/>
       <c r="Z169" s="7"/>
     </row>
-    <row r="170" ht="52.5" customHeight="1">
+    <row r="170" ht="34.5" customHeight="1">
       <c r="A170" s="7"/>
       <c r="C170" s="32"/>
       <c r="D170" s="32" t="s">
         <v>224</v>
       </c>
       <c r="E170" s="62"/>
-      <c r="F170" s="37"/>
+      <c r="F170" s="62"/>
       <c r="G170" s="62" t="s">
         <v>42</v>
       </c>
       <c r="H170" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="I170" s="115"/>
+      <c r="I170" s="39"/>
       <c r="J170" s="7"/>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -10011,18 +10008,21 @@
       <c r="Y170" s="7"/>
       <c r="Z170" s="7"/>
     </row>
-    <row r="171" ht="43.5" customHeight="1">
+    <row r="171" ht="36.0" customHeight="1">
       <c r="A171" s="7"/>
-      <c r="B171" s="116" t="s">
+      <c r="C171" s="32"/>
+      <c r="D171" s="32" t="s">
         <v>225</v>
       </c>
-      <c r="C171" s="99"/>
-      <c r="D171" s="116"/>
-      <c r="E171" s="10"/>
-      <c r="F171" s="10"/>
-      <c r="G171" s="10"/>
-      <c r="H171" s="10"/>
-      <c r="I171" s="11"/>
+      <c r="E171" s="62"/>
+      <c r="F171" s="37"/>
+      <c r="G171" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H171" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I171" s="39"/>
       <c r="J171" s="7"/>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -10041,17 +10041,21 @@
       <c r="Y171" s="7"/>
       <c r="Z171" s="7"/>
     </row>
-    <row r="172" ht="25.5" customHeight="1">
+    <row r="172" ht="52.5" customHeight="1">
       <c r="A172" s="7"/>
-      <c r="B172" s="117"/>
-      <c r="C172" s="101" t="s">
+      <c r="C172" s="32"/>
+      <c r="D172" s="32" t="s">
         <v>226</v>
       </c>
-      <c r="E172" s="41"/>
-      <c r="F172" s="41"/>
-      <c r="G172" s="41"/>
-      <c r="H172" s="41"/>
-      <c r="I172" s="42"/>
+      <c r="E172" s="62"/>
+      <c r="F172" s="37"/>
+      <c r="G172" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H172" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I172" s="115"/>
       <c r="J172" s="7"/>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -10070,28 +10074,18 @@
       <c r="Y172" s="7"/>
       <c r="Z172" s="7"/>
     </row>
-    <row r="173" ht="51.75" customHeight="1">
+    <row r="173" ht="43.5" customHeight="1">
       <c r="A173" s="7"/>
-      <c r="B173" s="118"/>
-      <c r="C173" s="85"/>
-      <c r="D173" s="86" t="s">
+      <c r="B173" s="116" t="s">
         <v>227</v>
       </c>
-      <c r="E173" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="F173" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="G173" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="H173" s="93" t="s">
-        <v>42</v>
-      </c>
-      <c r="I173" s="94" t="s">
-        <v>42</v>
-      </c>
+      <c r="C173" s="99"/>
+      <c r="D173" s="116"/>
+      <c r="E173" s="10"/>
+      <c r="F173" s="10"/>
+      <c r="G173" s="10"/>
+      <c r="H173" s="10"/>
+      <c r="I173" s="11"/>
       <c r="J173" s="7"/>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -10110,27 +10104,17 @@
       <c r="Y173" s="7"/>
       <c r="Z173" s="7"/>
     </row>
-    <row r="174" ht="37.5" customHeight="1">
+    <row r="174" ht="25.5" customHeight="1">
       <c r="A174" s="7"/>
-      <c r="C174" s="86"/>
-      <c r="D174" s="86" t="s">
+      <c r="B174" s="117"/>
+      <c r="C174" s="101" t="s">
         <v>228</v>
       </c>
-      <c r="E174" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="F174" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="G174" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H174" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="I174" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="E174" s="41"/>
+      <c r="F174" s="41"/>
+      <c r="G174" s="41"/>
+      <c r="H174" s="41"/>
+      <c r="I174" s="42"/>
       <c r="J174" s="7"/>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
@@ -10149,23 +10133,28 @@
       <c r="Y174" s="7"/>
       <c r="Z174" s="7"/>
     </row>
-    <row r="175" ht="40.5" customHeight="1">
+    <row r="175" ht="51.75" customHeight="1">
       <c r="A175" s="7"/>
-      <c r="C175" s="32"/>
-      <c r="D175" s="32" t="s">
+      <c r="B175" s="118"/>
+      <c r="C175" s="85"/>
+      <c r="D175" s="86" t="s">
         <v>229</v>
       </c>
-      <c r="E175" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="F175" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="G175" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="H175" s="55"/>
-      <c r="I175" s="68"/>
+      <c r="E175" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="F175" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="G175" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="H175" s="93" t="s">
+        <v>42</v>
+      </c>
+      <c r="I175" s="94" t="s">
+        <v>42</v>
+      </c>
       <c r="J175" s="7"/>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -10184,7 +10173,7 @@
       <c r="Y175" s="7"/>
       <c r="Z175" s="7"/>
     </row>
-    <row r="176" ht="40.5" customHeight="1">
+    <row r="176" ht="37.5" customHeight="1">
       <c r="A176" s="7"/>
       <c r="C176" s="86"/>
       <c r="D176" s="86" t="s">
@@ -10223,10 +10212,10 @@
       <c r="Y176" s="7"/>
       <c r="Z176" s="7"/>
     </row>
-    <row r="177" ht="36.0" customHeight="1">
+    <row r="177" ht="40.5" customHeight="1">
       <c r="A177" s="7"/>
-      <c r="C177" s="86"/>
-      <c r="D177" s="86" t="s">
+      <c r="C177" s="32"/>
+      <c r="D177" s="32" t="s">
         <v>231</v>
       </c>
       <c r="E177" s="55" t="s">
@@ -10238,12 +10227,8 @@
       <c r="G177" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="H177" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="I177" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="H177" s="55"/>
+      <c r="I177" s="68"/>
       <c r="J177" s="7"/>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -10262,10 +10247,9 @@
       <c r="Y177" s="7"/>
       <c r="Z177" s="7"/>
     </row>
-    <row r="178" ht="39.0" customHeight="1">
+    <row r="178" ht="40.5" customHeight="1">
       <c r="A178" s="7"/>
-      <c r="B178" s="86"/>
-      <c r="C178" s="85"/>
+      <c r="C178" s="86"/>
       <c r="D178" s="86" t="s">
         <v>232</v>
       </c>
@@ -10278,8 +10262,12 @@
       <c r="G178" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="H178" s="55"/>
-      <c r="I178" s="68"/>
+      <c r="H178" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I178" s="68" t="s">
+        <v>42</v>
+      </c>
       <c r="J178" s="7"/>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -10298,10 +10286,9 @@
       <c r="Y178" s="7"/>
       <c r="Z178" s="7"/>
     </row>
-    <row r="179" ht="37.5" customHeight="1">
+    <row r="179" ht="36.0" customHeight="1">
       <c r="A179" s="7"/>
-      <c r="B179" s="86"/>
-      <c r="C179" s="85"/>
+      <c r="C179" s="86"/>
       <c r="D179" s="86" t="s">
         <v>233</v>
       </c>
@@ -10338,11 +10325,11 @@
       <c r="Y179" s="7"/>
       <c r="Z179" s="7"/>
     </row>
-    <row r="180" ht="25.5" customHeight="1">
+    <row r="180" ht="39.0" customHeight="1">
       <c r="A180" s="7"/>
-      <c r="B180" s="32"/>
-      <c r="C180" s="43"/>
-      <c r="D180" s="32" t="s">
+      <c r="B180" s="86"/>
+      <c r="C180" s="85"/>
+      <c r="D180" s="86" t="s">
         <v>234</v>
       </c>
       <c r="E180" s="55" t="s">
@@ -10354,12 +10341,8 @@
       <c r="G180" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="H180" s="55" t="s">
-        <v>42</v>
-      </c>
-      <c r="I180" s="68" t="s">
-        <v>42</v>
-      </c>
+      <c r="H180" s="55"/>
+      <c r="I180" s="68"/>
       <c r="J180" s="7"/>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
@@ -10378,11 +10361,11 @@
       <c r="Y180" s="7"/>
       <c r="Z180" s="7"/>
     </row>
-    <row r="181" ht="39.75" customHeight="1">
+    <row r="181" ht="37.5" customHeight="1">
       <c r="A181" s="7"/>
-      <c r="B181" s="32"/>
-      <c r="C181" s="43"/>
-      <c r="D181" s="32" t="s">
+      <c r="B181" s="86"/>
+      <c r="C181" s="85"/>
+      <c r="D181" s="86" t="s">
         <v>235</v>
       </c>
       <c r="E181" s="55" t="s">
@@ -10397,7 +10380,7 @@
       <c r="H181" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="I181" s="119" t="s">
+      <c r="I181" s="68" t="s">
         <v>42</v>
       </c>
       <c r="J181" s="7"/>
@@ -10418,7 +10401,7 @@
       <c r="Y181" s="7"/>
       <c r="Z181" s="7"/>
     </row>
-    <row r="182" ht="39.75" customHeight="1">
+    <row r="182" ht="25.5" customHeight="1">
       <c r="A182" s="7"/>
       <c r="B182" s="32"/>
       <c r="C182" s="43"/>
@@ -10437,7 +10420,7 @@
       <c r="H182" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="I182" s="119" t="s">
+      <c r="I182" s="68" t="s">
         <v>42</v>
       </c>
       <c r="J182" s="7"/>
@@ -10458,25 +10441,26 @@
       <c r="Y182" s="7"/>
       <c r="Z182" s="7"/>
     </row>
-    <row r="183" ht="31.5" customHeight="1">
+    <row r="183" ht="39.75" customHeight="1">
       <c r="A183" s="7"/>
-      <c r="C183" s="86"/>
-      <c r="D183" s="86" t="s">
+      <c r="B183" s="32"/>
+      <c r="C183" s="43"/>
+      <c r="D183" s="32" t="s">
         <v>237</v>
       </c>
-      <c r="E183" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="F183" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="G183" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="H183" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I183" s="89" t="s">
+      <c r="E183" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F183" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="G183" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H183" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I183" s="119" t="s">
         <v>42</v>
       </c>
       <c r="J183" s="7"/>
@@ -10497,25 +10481,26 @@
       <c r="Y183" s="7"/>
       <c r="Z183" s="7"/>
     </row>
-    <row r="184" ht="71.25" customHeight="1">
+    <row r="184" ht="39.75" customHeight="1">
       <c r="A184" s="7"/>
-      <c r="C184" s="86"/>
-      <c r="D184" s="86" t="s">
+      <c r="B184" s="32"/>
+      <c r="C184" s="43"/>
+      <c r="D184" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="E184" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="F184" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="G184" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="H184" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I184" s="89" t="s">
+      <c r="E184" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="F184" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="G184" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H184" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="I184" s="119" t="s">
         <v>42</v>
       </c>
       <c r="J184" s="7"/>
@@ -10536,11 +10521,10 @@
       <c r="Y184" s="7"/>
       <c r="Z184" s="7"/>
     </row>
-    <row r="185" ht="57.0" customHeight="1">
+    <row r="185" ht="31.5" customHeight="1">
       <c r="A185" s="7"/>
-      <c r="B185" s="86"/>
-      <c r="C185" s="120"/>
-      <c r="D185" s="121" t="s">
+      <c r="C185" s="86"/>
+      <c r="D185" s="86" t="s">
         <v>239</v>
       </c>
       <c r="E185" s="83" t="s">
@@ -10552,8 +10536,12 @@
       <c r="G185" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="H185" s="88"/>
-      <c r="I185" s="89"/>
+      <c r="H185" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I185" s="89" t="s">
+        <v>42</v>
+      </c>
       <c r="J185" s="7"/>
       <c r="K185" s="7"/>
       <c r="L185" s="7"/>
@@ -10572,12 +10560,13 @@
       <c r="Y185" s="7"/>
       <c r="Z185" s="7"/>
     </row>
-    <row r="186" ht="25.5" customHeight="1">
+    <row r="186" ht="71.25" customHeight="1">
       <c r="A186" s="7"/>
-      <c r="B186" s="32" t="s">
+      <c r="C186" s="86"/>
+      <c r="D186" s="86" t="s">
         <v>240</v>
       </c>
-      <c r="E186" s="88" t="s">
+      <c r="E186" s="83" t="s">
         <v>42</v>
       </c>
       <c r="F186" s="88" t="s">
@@ -10610,23 +10599,24 @@
       <c r="Y186" s="7"/>
       <c r="Z186" s="7"/>
     </row>
-    <row r="187" ht="25.5" customHeight="1">
+    <row r="187" ht="57.0" customHeight="1">
       <c r="A187" s="7"/>
-      <c r="C187" s="32"/>
-      <c r="D187" s="32" t="s">
+      <c r="B187" s="86"/>
+      <c r="C187" s="120"/>
+      <c r="D187" s="121" t="s">
         <v>241</v>
       </c>
-      <c r="E187" s="83"/>
-      <c r="F187" s="83"/>
-      <c r="G187" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="H187" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="I187" s="92" t="s">
-        <v>42</v>
-      </c>
+      <c r="E187" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="F187" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="G187" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="H187" s="88"/>
+      <c r="I187" s="89"/>
       <c r="J187" s="7"/>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -10647,15 +10637,24 @@
     </row>
     <row r="188" ht="25.5" customHeight="1">
       <c r="A188" s="7"/>
-      <c r="B188" s="32"/>
-      <c r="C188" s="40" t="s">
+      <c r="B188" s="32" t="s">
         <v>242</v>
       </c>
-      <c r="E188" s="41"/>
-      <c r="F188" s="41"/>
-      <c r="G188" s="41"/>
-      <c r="H188" s="41"/>
-      <c r="I188" s="42"/>
+      <c r="E188" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="F188" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="G188" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="H188" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I188" s="89" t="s">
+        <v>42</v>
+      </c>
       <c r="J188" s="7"/>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -10674,25 +10673,21 @@
       <c r="Y188" s="7"/>
       <c r="Z188" s="7"/>
     </row>
-    <row r="189" ht="33.0" customHeight="1">
+    <row r="189" ht="25.5" customHeight="1">
       <c r="A189" s="7"/>
       <c r="C189" s="32"/>
       <c r="D189" s="32" t="s">
         <v>243</v>
       </c>
-      <c r="E189" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="F189" s="83" t="s">
-        <v>42</v>
-      </c>
+      <c r="E189" s="83"/>
+      <c r="F189" s="83"/>
       <c r="G189" s="83" t="s">
         <v>42</v>
       </c>
       <c r="H189" s="83" t="s">
         <v>42</v>
       </c>
-      <c r="I189" s="87" t="s">
+      <c r="I189" s="92" t="s">
         <v>42</v>
       </c>
       <c r="J189" s="7"/>
@@ -10715,21 +10710,15 @@
     </row>
     <row r="190" ht="25.5" customHeight="1">
       <c r="A190" s="7"/>
-      <c r="C190" s="32"/>
-      <c r="D190" s="32" t="s">
+      <c r="B190" s="32"/>
+      <c r="C190" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="E190" s="38"/>
-      <c r="F190" s="91"/>
-      <c r="G190" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="H190" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="I190" s="92" t="s">
-        <v>42</v>
-      </c>
+      <c r="E190" s="41"/>
+      <c r="F190" s="41"/>
+      <c r="G190" s="41"/>
+      <c r="H190" s="41"/>
+      <c r="I190" s="42"/>
       <c r="J190" s="7"/>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -10748,17 +10737,27 @@
       <c r="Y190" s="7"/>
       <c r="Z190" s="7"/>
     </row>
-    <row r="191" ht="25.5" customHeight="1">
+    <row r="191" ht="33.0" customHeight="1">
       <c r="A191" s="7"/>
-      <c r="B191" s="86"/>
-      <c r="C191" s="40" t="s">
+      <c r="C191" s="32"/>
+      <c r="D191" s="32" t="s">
         <v>245</v>
       </c>
-      <c r="E191" s="41"/>
-      <c r="F191" s="41"/>
-      <c r="G191" s="41"/>
-      <c r="H191" s="41"/>
-      <c r="I191" s="122"/>
+      <c r="E191" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="F191" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="G191" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="H191" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="I191" s="87" t="s">
+        <v>42</v>
+      </c>
       <c r="J191" s="7"/>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -10779,20 +10778,19 @@
     </row>
     <row r="192" ht="25.5" customHeight="1">
       <c r="A192" s="7"/>
-      <c r="B192" s="32"/>
-      <c r="C192" s="96"/>
-      <c r="D192" s="97" t="s">
+      <c r="C192" s="32"/>
+      <c r="D192" s="32" t="s">
         <v>246</v>
       </c>
-      <c r="E192" s="88"/>
-      <c r="F192" s="88"/>
-      <c r="G192" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="H192" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I192" s="89" t="s">
+      <c r="E192" s="38"/>
+      <c r="F192" s="91"/>
+      <c r="G192" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="H192" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="I192" s="92" t="s">
         <v>42</v>
       </c>
       <c r="J192" s="7"/>
@@ -10815,25 +10813,15 @@
     </row>
     <row r="193" ht="25.5" customHeight="1">
       <c r="A193" s="7"/>
-      <c r="C193" s="32"/>
-      <c r="D193" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="E193" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="F193" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="G193" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="H193" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="I193" s="89" t="s">
-        <v>42</v>
-      </c>
+      <c r="B193" s="86"/>
+      <c r="C193" s="40" t="s">
+        <v>247</v>
+      </c>
+      <c r="E193" s="41"/>
+      <c r="F193" s="41"/>
+      <c r="G193" s="41"/>
+      <c r="H193" s="41"/>
+      <c r="I193" s="122"/>
       <c r="J193" s="7"/>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -10857,14 +10845,10 @@
       <c r="B194" s="32"/>
       <c r="C194" s="96"/>
       <c r="D194" s="97" t="s">
-        <v>247</v>
-      </c>
-      <c r="E194" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="F194" s="88" t="s">
-        <v>42</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="E194" s="88"/>
+      <c r="F194" s="88"/>
       <c r="G194" s="88" t="s">
         <v>42</v>
       </c>
@@ -10896,21 +10880,21 @@
       <c r="A195" s="7"/>
       <c r="C195" s="32"/>
       <c r="D195" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="E195" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="F195" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="G195" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="H195" s="91" t="s">
-        <v>42</v>
-      </c>
-      <c r="I195" s="92" t="s">
+        <v>136</v>
+      </c>
+      <c r="E195" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="F195" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="G195" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="H195" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="I195" s="89" t="s">
         <v>42</v>
       </c>
       <c r="J195" s="7"/>
@@ -10933,15 +10917,26 @@
     </row>
     <row r="196" ht="25.5" customHeight="1">
       <c r="A196" s="7"/>
-      <c r="C196" s="40" t="s">
+      <c r="B196" s="32"/>
+      <c r="C196" s="96"/>
+      <c r="D196" s="97" t="s">
         <v>249</v>
       </c>
-      <c r="D196" s="40"/>
-      <c r="E196" s="41"/>
-      <c r="F196" s="41"/>
-      <c r="G196" s="41"/>
-      <c r="H196" s="41"/>
-      <c r="I196" s="42"/>
+      <c r="E196" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="F196" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="G196" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="H196" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I196" s="89" t="s">
+        <v>42</v>
+      </c>
       <c r="J196" s="7"/>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -10960,25 +10955,25 @@
       <c r="Y196" s="7"/>
       <c r="Z196" s="7"/>
     </row>
-    <row r="197" ht="34.5" customHeight="1">
+    <row r="197" ht="25.5" customHeight="1">
       <c r="A197" s="7"/>
       <c r="C197" s="32"/>
       <c r="D197" s="32" t="s">
         <v>250</v>
       </c>
-      <c r="E197" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="F197" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="G197" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="H197" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="I197" s="87" t="s">
+      <c r="E197" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="F197" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="G197" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="H197" s="91" t="s">
+        <v>42</v>
+      </c>
+      <c r="I197" s="92" t="s">
         <v>42</v>
       </c>
       <c r="J197" s="7"/>
@@ -11001,26 +10996,15 @@
     </row>
     <row r="198" ht="25.5" customHeight="1">
       <c r="A198" s="7"/>
-      <c r="B198" s="118"/>
-      <c r="C198" s="96"/>
-      <c r="D198" s="97" t="s">
+      <c r="C198" s="40" t="s">
         <v>251</v>
       </c>
-      <c r="E198" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="F198" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="G198" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="H198" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I198" s="89" t="s">
-        <v>42</v>
-      </c>
+      <c r="D198" s="40"/>
+      <c r="E198" s="41"/>
+      <c r="F198" s="41"/>
+      <c r="G198" s="41"/>
+      <c r="H198" s="41"/>
+      <c r="I198" s="42"/>
       <c r="J198" s="7"/>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -11039,26 +11023,25 @@
       <c r="Y198" s="7"/>
       <c r="Z198" s="7"/>
     </row>
-    <row r="199" ht="25.5" customHeight="1">
+    <row r="199" ht="34.5" customHeight="1">
       <c r="A199" s="7"/>
-      <c r="B199" s="118"/>
-      <c r="C199" s="43"/>
+      <c r="C199" s="32"/>
       <c r="D199" s="32" t="s">
         <v>252</v>
       </c>
-      <c r="E199" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="F199" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="G199" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="H199" s="88" t="s">
-        <v>42</v>
-      </c>
-      <c r="I199" s="89" t="s">
+      <c r="E199" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="F199" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="G199" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="H199" s="83" t="s">
+        <v>42</v>
+      </c>
+      <c r="I199" s="87" t="s">
         <v>42</v>
       </c>
       <c r="J199" s="7"/>
@@ -11082,8 +11065,8 @@
     <row r="200" ht="25.5" customHeight="1">
       <c r="A200" s="7"/>
       <c r="B200" s="118"/>
-      <c r="C200" s="43"/>
-      <c r="D200" s="32" t="s">
+      <c r="C200" s="96"/>
+      <c r="D200" s="97" t="s">
         <v>253</v>
       </c>
       <c r="E200" s="88" t="s">
@@ -11239,9 +11222,10 @@
       <c r="Y203" s="7"/>
       <c r="Z203" s="7"/>
     </row>
-    <row r="204" ht="39.0" customHeight="1">
+    <row r="204" ht="25.5" customHeight="1">
       <c r="A204" s="7"/>
-      <c r="C204" s="32"/>
+      <c r="B204" s="118"/>
+      <c r="C204" s="43"/>
       <c r="D204" s="32" t="s">
         <v>257</v>
       </c>
@@ -11280,7 +11264,7 @@
     </row>
     <row r="205" ht="25.5" customHeight="1">
       <c r="A205" s="7"/>
-      <c r="B205" s="40"/>
+      <c r="B205" s="118"/>
       <c r="C205" s="43"/>
       <c r="D205" s="32" t="s">
         <v>258</v>
@@ -11318,10 +11302,9 @@
       <c r="Y205" s="7"/>
       <c r="Z205" s="7"/>
     </row>
-    <row r="206" ht="25.5" customHeight="1">
+    <row r="206" ht="39.0" customHeight="1">
       <c r="A206" s="7"/>
-      <c r="B206" s="40"/>
-      <c r="C206" s="43"/>
+      <c r="C206" s="32"/>
       <c r="D206" s="32" t="s">
         <v>259</v>
       </c>
@@ -11398,25 +11381,26 @@
       <c r="Y207" s="7"/>
       <c r="Z207" s="7"/>
     </row>
-    <row r="208" ht="43.5" customHeight="1">
+    <row r="208" ht="25.5" customHeight="1">
       <c r="A208" s="7"/>
-      <c r="C208" s="32"/>
+      <c r="B208" s="40"/>
+      <c r="C208" s="43"/>
       <c r="D208" s="32" t="s">
         <v>261</v>
       </c>
-      <c r="E208" s="90" t="s">
-        <v>42</v>
-      </c>
-      <c r="F208" s="90" t="s">
-        <v>42</v>
-      </c>
-      <c r="G208" s="90" t="s">
-        <v>42</v>
-      </c>
-      <c r="H208" s="90" t="s">
-        <v>42</v>
-      </c>
-      <c r="I208" s="123" t="s">
+      <c r="E208" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="F208" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="G208" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="H208" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I208" s="89" t="s">
         <v>42</v>
       </c>
       <c r="J208" s="7"/>
@@ -11437,18 +11421,28 @@
       <c r="Y208" s="7"/>
       <c r="Z208" s="7"/>
     </row>
-    <row r="209" ht="43.5" customHeight="1">
+    <row r="209" ht="25.5" customHeight="1">
       <c r="A209" s="7"/>
-      <c r="B209" s="124" t="s">
+      <c r="B209" s="40"/>
+      <c r="C209" s="43"/>
+      <c r="D209" s="32" t="s">
         <v>262</v>
       </c>
-      <c r="C209" s="124"/>
-      <c r="D209" s="124"/>
-      <c r="E209" s="124"/>
-      <c r="F209" s="124"/>
-      <c r="G209" s="124"/>
-      <c r="H209" s="124"/>
-      <c r="I209" s="11"/>
+      <c r="E209" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="F209" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="G209" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="H209" s="88" t="s">
+        <v>42</v>
+      </c>
+      <c r="I209" s="89" t="s">
+        <v>42</v>
+      </c>
       <c r="J209" s="7"/>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -11467,96 +11461,87 @@
       <c r="Y209" s="7"/>
       <c r="Z209" s="7"/>
     </row>
-    <row r="210" ht="51.75" customHeight="1">
-      <c r="A210" s="125"/>
-      <c r="B210" s="59"/>
-      <c r="C210" s="126" t="s">
+    <row r="210" ht="43.5" customHeight="1">
+      <c r="A210" s="7"/>
+      <c r="C210" s="32"/>
+      <c r="D210" s="32" t="s">
+        <v>263</v>
+      </c>
+      <c r="E210" s="90" t="s">
+        <v>42</v>
+      </c>
+      <c r="F210" s="90" t="s">
+        <v>42</v>
+      </c>
+      <c r="G210" s="90" t="s">
+        <v>42</v>
+      </c>
+      <c r="H210" s="90" t="s">
+        <v>42</v>
+      </c>
+      <c r="I210" s="123" t="s">
+        <v>42</v>
+      </c>
+      <c r="J210" s="7"/>
+      <c r="K210" s="7"/>
+      <c r="L210" s="7"/>
+      <c r="M210" s="7"/>
+      <c r="N210" s="7"/>
+      <c r="O210" s="7"/>
+      <c r="P210" s="7"/>
+      <c r="Q210" s="7"/>
+      <c r="R210" s="7"/>
+      <c r="S210" s="7"/>
+      <c r="T210" s="7"/>
+      <c r="U210" s="7"/>
+      <c r="V210" s="7"/>
+      <c r="W210" s="7"/>
+      <c r="X210" s="7"/>
+      <c r="Y210" s="7"/>
+      <c r="Z210" s="7"/>
+    </row>
+    <row r="211" ht="43.5" customHeight="1">
+      <c r="A211" s="7"/>
+      <c r="B211" s="124" t="s">
+        <v>264</v>
+      </c>
+      <c r="C211" s="124"/>
+      <c r="D211" s="124"/>
+      <c r="E211" s="124"/>
+      <c r="F211" s="124"/>
+      <c r="G211" s="124"/>
+      <c r="H211" s="124"/>
+      <c r="I211" s="11"/>
+      <c r="J211" s="7"/>
+      <c r="K211" s="7"/>
+      <c r="L211" s="7"/>
+      <c r="M211" s="7"/>
+      <c r="N211" s="7"/>
+      <c r="O211" s="7"/>
+      <c r="P211" s="7"/>
+      <c r="Q211" s="7"/>
+      <c r="R211" s="7"/>
+      <c r="S211" s="7"/>
+      <c r="T211" s="7"/>
+      <c r="U211" s="7"/>
+      <c r="V211" s="7"/>
+      <c r="W211" s="7"/>
+      <c r="X211" s="7"/>
+      <c r="Y211" s="7"/>
+      <c r="Z211" s="7"/>
+    </row>
+    <row r="212" ht="51.75" customHeight="1">
+      <c r="A212" s="125"/>
+      <c r="B212" s="59"/>
+      <c r="C212" s="126" t="s">
         <v>9</v>
       </c>
-      <c r="D210" s="32"/>
-      <c r="E210" s="38"/>
-      <c r="F210" s="38"/>
-      <c r="G210" s="38"/>
-      <c r="H210" s="38"/>
-      <c r="I210" s="44"/>
-      <c r="J210" s="125"/>
-      <c r="K210" s="125"/>
-      <c r="L210" s="125"/>
-      <c r="M210" s="125"/>
-      <c r="N210" s="125"/>
-      <c r="O210" s="125"/>
-      <c r="P210" s="125"/>
-      <c r="Q210" s="125"/>
-      <c r="R210" s="125"/>
-      <c r="S210" s="125"/>
-      <c r="T210" s="125"/>
-      <c r="U210" s="125"/>
-      <c r="V210" s="125"/>
-      <c r="W210" s="125"/>
-      <c r="X210" s="125"/>
-      <c r="Y210" s="125"/>
-      <c r="Z210" s="125"/>
-    </row>
-    <row r="211" ht="62.25" customHeight="1">
-      <c r="A211" s="125"/>
-      <c r="C211" s="32"/>
-      <c r="D211" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="E211" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F211" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G211" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H211" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I211" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="J211" s="125"/>
-      <c r="K211" s="125"/>
-      <c r="L211" s="125"/>
-      <c r="M211" s="125"/>
-      <c r="N211" s="125"/>
-      <c r="O211" s="125"/>
-      <c r="P211" s="125"/>
-      <c r="Q211" s="125"/>
-      <c r="R211" s="125"/>
-      <c r="S211" s="125"/>
-      <c r="T211" s="125"/>
-      <c r="U211" s="125"/>
-      <c r="V211" s="125"/>
-      <c r="W211" s="125"/>
-      <c r="X211" s="125"/>
-      <c r="Y211" s="125"/>
-      <c r="Z211" s="125"/>
-    </row>
-    <row r="212" ht="69.75" customHeight="1">
-      <c r="A212" s="125"/>
-      <c r="C212" s="32"/>
-      <c r="D212" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="E212" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="F212" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="G212" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="H212" s="62" t="s">
-        <v>42</v>
-      </c>
-      <c r="I212" s="39" t="s">
-        <v>42</v>
-      </c>
+      <c r="D212" s="32"/>
+      <c r="E212" s="38"/>
+      <c r="F212" s="38"/>
+      <c r="G212" s="38"/>
+      <c r="H212" s="38"/>
+      <c r="I212" s="44"/>
       <c r="J212" s="125"/>
       <c r="K212" s="125"/>
       <c r="L212" s="125"/>
@@ -11575,7 +11560,7 @@
       <c r="Y212" s="125"/>
       <c r="Z212" s="125"/>
     </row>
-    <row r="213" ht="63.0" customHeight="1">
+    <row r="213" ht="62.25" customHeight="1">
       <c r="A213" s="125"/>
       <c r="C213" s="32"/>
       <c r="D213" s="32" t="s">
@@ -11614,7 +11599,7 @@
       <c r="Y213" s="125"/>
       <c r="Z213" s="125"/>
     </row>
-    <row r="214" ht="72.75" customHeight="1">
+    <row r="214" ht="69.75" customHeight="1">
       <c r="A214" s="125"/>
       <c r="C214" s="32"/>
       <c r="D214" s="32" t="s">
@@ -11653,7 +11638,7 @@
       <c r="Y214" s="125"/>
       <c r="Z214" s="125"/>
     </row>
-    <row r="215" ht="87.0" customHeight="1">
+    <row r="215" ht="63.0" customHeight="1">
       <c r="A215" s="125"/>
       <c r="C215" s="32"/>
       <c r="D215" s="32" t="s">
@@ -11692,7 +11677,7 @@
       <c r="Y215" s="125"/>
       <c r="Z215" s="125"/>
     </row>
-    <row r="216" ht="68.25" customHeight="1">
+    <row r="216" ht="72.75" customHeight="1">
       <c r="A216" s="125"/>
       <c r="C216" s="32"/>
       <c r="D216" s="32" t="s">
@@ -11731,17 +11716,27 @@
       <c r="Y216" s="125"/>
       <c r="Z216" s="125"/>
     </row>
-    <row r="217" ht="126.75" customHeight="1">
+    <row r="217" ht="87.0" customHeight="1">
       <c r="A217" s="125"/>
-      <c r="C217" s="127"/>
-      <c r="D217" s="127" t="s">
+      <c r="C217" s="32"/>
+      <c r="D217" s="32" t="s">
         <v>269</v>
       </c>
-      <c r="E217" s="62"/>
-      <c r="F217" s="62"/>
-      <c r="G217" s="62"/>
-      <c r="H217" s="62"/>
-      <c r="I217" s="39"/>
+      <c r="E217" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F217" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G217" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H217" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I217" s="39" t="s">
+        <v>42</v>
+      </c>
       <c r="J217" s="125"/>
       <c r="K217" s="125"/>
       <c r="L217" s="125"/>
@@ -11760,72 +11755,84 @@
       <c r="Y217" s="125"/>
       <c r="Z217" s="125"/>
     </row>
-    <row r="218" ht="11.25" customHeight="1">
-      <c r="A218" s="75"/>
-      <c r="B218" s="128"/>
-      <c r="C218" s="128"/>
-      <c r="D218" s="128"/>
-      <c r="E218" s="129"/>
-      <c r="F218" s="129"/>
-      <c r="G218" s="129"/>
-      <c r="H218" s="129"/>
-      <c r="I218" s="34"/>
-      <c r="J218" s="76"/>
-      <c r="K218" s="76"/>
-      <c r="L218" s="76"/>
-      <c r="M218" s="76"/>
-      <c r="N218" s="76"/>
-      <c r="O218" s="76"/>
-      <c r="P218" s="76"/>
-      <c r="Q218" s="76"/>
-      <c r="R218" s="76"/>
-      <c r="S218" s="76"/>
-      <c r="T218" s="76"/>
-      <c r="U218" s="76"/>
-      <c r="V218" s="76"/>
-      <c r="W218" s="76"/>
-      <c r="X218" s="76"/>
-      <c r="Y218" s="76"/>
-      <c r="Z218" s="76"/>
-    </row>
-    <row r="219" ht="11.25" customHeight="1">
-      <c r="A219" s="75"/>
-      <c r="B219" s="128"/>
-      <c r="C219" s="128"/>
-      <c r="D219" s="128"/>
-      <c r="E219" s="130"/>
-      <c r="F219" s="130"/>
-      <c r="G219" s="130"/>
-      <c r="H219" s="130"/>
-      <c r="I219" s="53"/>
-      <c r="J219" s="76"/>
-      <c r="K219" s="76"/>
-      <c r="L219" s="76"/>
-      <c r="M219" s="76"/>
-      <c r="N219" s="76"/>
-      <c r="O219" s="76"/>
-      <c r="P219" s="76"/>
-      <c r="Q219" s="76"/>
-      <c r="R219" s="76"/>
-      <c r="S219" s="76"/>
-      <c r="T219" s="76"/>
-      <c r="U219" s="76"/>
-      <c r="V219" s="76"/>
-      <c r="W219" s="76"/>
-      <c r="X219" s="76"/>
-      <c r="Y219" s="76"/>
-      <c r="Z219" s="76"/>
+    <row r="218" ht="68.25" customHeight="1">
+      <c r="A218" s="125"/>
+      <c r="C218" s="32"/>
+      <c r="D218" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="E218" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="F218" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="G218" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="H218" s="62" t="s">
+        <v>42</v>
+      </c>
+      <c r="I218" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="J218" s="125"/>
+      <c r="K218" s="125"/>
+      <c r="L218" s="125"/>
+      <c r="M218" s="125"/>
+      <c r="N218" s="125"/>
+      <c r="O218" s="125"/>
+      <c r="P218" s="125"/>
+      <c r="Q218" s="125"/>
+      <c r="R218" s="125"/>
+      <c r="S218" s="125"/>
+      <c r="T218" s="125"/>
+      <c r="U218" s="125"/>
+      <c r="V218" s="125"/>
+      <c r="W218" s="125"/>
+      <c r="X218" s="125"/>
+      <c r="Y218" s="125"/>
+      <c r="Z218" s="125"/>
+    </row>
+    <row r="219" ht="126.75" customHeight="1">
+      <c r="A219" s="125"/>
+      <c r="C219" s="127"/>
+      <c r="D219" s="127" t="s">
+        <v>271</v>
+      </c>
+      <c r="E219" s="62"/>
+      <c r="F219" s="62"/>
+      <c r="G219" s="62"/>
+      <c r="H219" s="62"/>
+      <c r="I219" s="39"/>
+      <c r="J219" s="125"/>
+      <c r="K219" s="125"/>
+      <c r="L219" s="125"/>
+      <c r="M219" s="125"/>
+      <c r="N219" s="125"/>
+      <c r="O219" s="125"/>
+      <c r="P219" s="125"/>
+      <c r="Q219" s="125"/>
+      <c r="R219" s="125"/>
+      <c r="S219" s="125"/>
+      <c r="T219" s="125"/>
+      <c r="U219" s="125"/>
+      <c r="V219" s="125"/>
+      <c r="W219" s="125"/>
+      <c r="X219" s="125"/>
+      <c r="Y219" s="125"/>
+      <c r="Z219" s="125"/>
     </row>
     <row r="220" ht="11.25" customHeight="1">
       <c r="A220" s="75"/>
       <c r="B220" s="128"/>
       <c r="C220" s="128"/>
       <c r="D220" s="128"/>
-      <c r="E220" s="130"/>
-      <c r="F220" s="130"/>
-      <c r="G220" s="130"/>
-      <c r="H220" s="130"/>
-      <c r="I220" s="53"/>
+      <c r="E220" s="129"/>
+      <c r="F220" s="129"/>
+      <c r="G220" s="129"/>
+      <c r="H220" s="129"/>
+      <c r="I220" s="34"/>
       <c r="J220" s="76"/>
       <c r="K220" s="76"/>
       <c r="L220" s="76"/>
@@ -12657,10 +12664,10 @@
       <c r="Z249" s="76"/>
     </row>
     <row r="250" ht="11.25" customHeight="1">
-      <c r="A250" s="76"/>
-      <c r="B250" s="131"/>
-      <c r="C250" s="132"/>
-      <c r="D250" s="82"/>
+      <c r="A250" s="75"/>
+      <c r="B250" s="128"/>
+      <c r="C250" s="128"/>
+      <c r="D250" s="128"/>
       <c r="E250" s="130"/>
       <c r="F250" s="130"/>
       <c r="G250" s="130"/>
@@ -12685,10 +12692,10 @@
       <c r="Z250" s="76"/>
     </row>
     <row r="251" ht="11.25" customHeight="1">
-      <c r="A251" s="76"/>
-      <c r="B251" s="131"/>
-      <c r="C251" s="132"/>
-      <c r="D251" s="82"/>
+      <c r="A251" s="75"/>
+      <c r="B251" s="128"/>
+      <c r="C251" s="128"/>
+      <c r="D251" s="128"/>
       <c r="E251" s="130"/>
       <c r="F251" s="130"/>
       <c r="G251" s="130"/>
@@ -12880,7 +12887,7 @@
       <c r="Y257" s="76"/>
       <c r="Z257" s="76"/>
     </row>
-    <row r="258" ht="15.75" customHeight="1">
+    <row r="258" ht="11.25" customHeight="1">
       <c r="A258" s="76"/>
       <c r="B258" s="131"/>
       <c r="C258" s="132"/>
@@ -12908,7 +12915,7 @@
       <c r="Y258" s="76"/>
       <c r="Z258" s="76"/>
     </row>
-    <row r="259" ht="15.75" customHeight="1">
+    <row r="259" ht="11.25" customHeight="1">
       <c r="A259" s="76"/>
       <c r="B259" s="131"/>
       <c r="C259" s="132"/>
@@ -33824,14 +33831,68 @@
       <c r="Y1005" s="76"/>
       <c r="Z1005" s="76"/>
     </row>
+    <row r="1006" ht="15.75" customHeight="1">
+      <c r="A1006" s="76"/>
+      <c r="B1006" s="131"/>
+      <c r="C1006" s="132"/>
+      <c r="D1006" s="82"/>
+      <c r="E1006" s="130"/>
+      <c r="F1006" s="130"/>
+      <c r="G1006" s="130"/>
+      <c r="H1006" s="130"/>
+      <c r="I1006" s="53"/>
+      <c r="J1006" s="76"/>
+      <c r="K1006" s="76"/>
+      <c r="L1006" s="76"/>
+      <c r="M1006" s="76"/>
+      <c r="N1006" s="76"/>
+      <c r="O1006" s="76"/>
+      <c r="P1006" s="76"/>
+      <c r="Q1006" s="76"/>
+      <c r="R1006" s="76"/>
+      <c r="S1006" s="76"/>
+      <c r="T1006" s="76"/>
+      <c r="U1006" s="76"/>
+      <c r="V1006" s="76"/>
+      <c r="W1006" s="76"/>
+      <c r="X1006" s="76"/>
+      <c r="Y1006" s="76"/>
+      <c r="Z1006" s="76"/>
+    </row>
+    <row r="1007" ht="15.75" customHeight="1">
+      <c r="A1007" s="76"/>
+      <c r="B1007" s="131"/>
+      <c r="C1007" s="132"/>
+      <c r="D1007" s="82"/>
+      <c r="E1007" s="130"/>
+      <c r="F1007" s="130"/>
+      <c r="G1007" s="130"/>
+      <c r="H1007" s="130"/>
+      <c r="I1007" s="53"/>
+      <c r="J1007" s="76"/>
+      <c r="K1007" s="76"/>
+      <c r="L1007" s="76"/>
+      <c r="M1007" s="76"/>
+      <c r="N1007" s="76"/>
+      <c r="O1007" s="76"/>
+      <c r="P1007" s="76"/>
+      <c r="Q1007" s="76"/>
+      <c r="R1007" s="76"/>
+      <c r="S1007" s="76"/>
+      <c r="T1007" s="76"/>
+      <c r="U1007" s="76"/>
+      <c r="V1007" s="76"/>
+      <c r="W1007" s="76"/>
+      <c r="X1007" s="76"/>
+      <c r="Y1007" s="76"/>
+      <c r="Z1007" s="76"/>
+    </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="B161:D161"/>
-    <mergeCell ref="B162:D162"/>
     <mergeCell ref="B163:D163"/>
-    <mergeCell ref="B186:D186"/>
-    <mergeCell ref="A218:D218"/>
-    <mergeCell ref="A219:D219"/>
+    <mergeCell ref="B164:D164"/>
+    <mergeCell ref="B165:D165"/>
+    <mergeCell ref="B188:D188"/>
     <mergeCell ref="A220:D220"/>
     <mergeCell ref="A221:D221"/>
     <mergeCell ref="A222:D222"/>
@@ -33847,21 +33908,23 @@
     <mergeCell ref="A232:D232"/>
     <mergeCell ref="A233:D233"/>
     <mergeCell ref="A234:D234"/>
-    <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A243:D243"/>
+    <mergeCell ref="A235:D235"/>
+    <mergeCell ref="A236:D236"/>
     <mergeCell ref="A244:D244"/>
     <mergeCell ref="A245:D245"/>
     <mergeCell ref="A246:D246"/>
     <mergeCell ref="A247:D247"/>
     <mergeCell ref="A248:D248"/>
     <mergeCell ref="A249:D249"/>
-    <mergeCell ref="A235:D235"/>
-    <mergeCell ref="A236:D236"/>
+    <mergeCell ref="A250:D250"/>
+    <mergeCell ref="A251:D251"/>
     <mergeCell ref="A237:D237"/>
     <mergeCell ref="A238:D238"/>
     <mergeCell ref="A239:D239"/>
     <mergeCell ref="A240:D240"/>
     <mergeCell ref="A241:D241"/>
+    <mergeCell ref="A242:D242"/>
+    <mergeCell ref="A243:D243"/>
   </mergeCells>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -33891,121 +33954,121 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="133" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B1" s="134" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C1" s="134" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D1" s="134" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E1" s="134" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F1" s="134" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G1" s="134" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H1" s="134" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="2" ht="94.5" customHeight="1">
       <c r="A2" s="135" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B2" s="136">
         <v>168.0</v>
       </c>
       <c r="C2" s="137" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="D2" s="136" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E2" s="136" t="s">
         <v>7</v>
       </c>
       <c r="F2" s="138" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="G2" s="139" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H2" s="140" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="141" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B3" s="142" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C3" s="143" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D3" s="142" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E3" s="142" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F3" s="143" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G3" s="142" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H3" s="144" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="145" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B4" s="145">
         <v>39.0</v>
       </c>
       <c r="C4" s="146" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D4" s="145" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E4" s="147" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F4" s="145" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="G4" s="148" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="H4" s="145" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="149"/>
       <c r="B5" s="149"/>
       <c r="C5" s="150" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D5" s="149"/>
       <c r="E5" s="151" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F5" s="149"/>
       <c r="G5" s="140" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" s="149"/>
     </row>
@@ -34019,31 +34082,31 @@
       </c>
       <c r="F6" s="152"/>
       <c r="G6" s="140" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="H6" s="152"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="153" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B7" s="154">
         <v>44.0</v>
       </c>
       <c r="C7" s="154" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D7" s="154" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E7" s="154" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="154" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G7" s="155" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="H7" s="156"/>
     </row>
@@ -34053,16 +34116,16 @@
         <v>23.0</v>
       </c>
       <c r="C8" s="159" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D8" s="153" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E8" s="153" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="F8" s="159" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="G8" s="159" t="s">
         <v>52</v>
@@ -34077,16 +34140,16 @@
         <v>0</v>
       </c>
       <c r="D9" s="153" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E9" s="160" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F9" s="161" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="G9" s="159" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
@@ -34096,10 +34159,10 @@
       <c r="D10" s="157"/>
       <c r="E10" s="157"/>
       <c r="F10" s="161" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="G10" s="159" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11" ht="43.5" customHeight="1">
@@ -34109,56 +34172,56 @@
       <c r="D11" s="163"/>
       <c r="E11" s="163"/>
       <c r="F11" s="165" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="G11" s="166" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="141" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B12" s="142" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C12" s="143" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D12" s="142" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E12" s="142" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F12" s="143" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G12" s="142" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H12" s="144" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="13" ht="54.0" customHeight="1">
       <c r="A13" s="167" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B13" s="167">
         <v>181.0</v>
       </c>
       <c r="C13" s="168" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D13" s="167" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E13" s="167" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F13" s="169" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="G13" s="170"/>
       <c r="H13" s="171"/>
@@ -37163,107 +37226,107 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="176" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C1" s="176" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D1" s="176" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E1" s="176" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F1" s="176" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="59" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C2" s="59" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F2" s="59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C3" s="59" t="s">
+        <v>321</v>
+      </c>
+      <c r="E3" s="59" t="s">
         <v>319</v>
-      </c>
-      <c r="E3" s="59" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="59" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C4" s="59" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D4" s="59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E4" s="59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F4" s="59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D5" s="59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="59" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -37280,83 +37343,83 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="176" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C1" s="176" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D1" s="177" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="59" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C2" s="59" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C3" s="59" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D3" s="59" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="59" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="D4" s="59" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D5" s="59" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="59" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -37376,35 +37439,35 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="176" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B1" s="176" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C1" s="176" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="59" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C2" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="59" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C3" s="59" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4">
@@ -37414,35 +37477,35 @@
     </row>
     <row r="5">
       <c r="A5" s="59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="59" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C7" s="59" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="8">
@@ -37452,43 +37515,43 @@
     </row>
     <row r="9">
       <c r="A9" s="59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C10" s="59" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="59" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
   </sheetData>

--- a/mock/input.xlsx
+++ b/mock/input.xlsx
@@ -105,7 +105,7 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mjkEGs4wlMrP7e0jAKxhVmqQ+xi8w=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgIFNLNAtSDoTOLK/R9vlI0o51tEg=="/>
     </ext>
   </extLst>
 </comments>

--- a/mock/input.xlsx
+++ b/mock/input.xlsx
@@ -88,7 +88,10 @@
 Alexander Wong    (2026-03-17 15:29:52)
 Headline: Engine Type: 1.5L VTEC® Turbo Inline-4
 Description: The turbocharged Integra is engineered for true driving enthusiasts. With a 1.5L VTEC® Turbo engine that pumps out 200-HP* and an early and flat torque curve that offers smooth power delivery, the Integra is a powerful and agile tour de force.
-Image:  /-/media/Acura-Platform/Vehicle-Pages/INTEGRA/2025/pricing-and-specs/Specs-Cards-Powertrain/In-Line-4-Cylinder/Acura-Integra-Pricing-and-Specs-powertrain-s.jpg</t>
+ImageSmall: Acura-Integra-Pricing-and-Specs-powertrain-s
+ImageMedium: Acura-Integra-Pricing-and-Specs-powertrain-m
+ImageLarge: Acura-Integra-Pricing-and-Specs-powertrain-l
+ImageXlarge: Acura-Integra-Pricing-and-Specs-powertrain-xl</t>
       </text>
     </comment>
     <comment authorId="0" ref="I172">
@@ -105,7 +108,7 @@
   </commentList>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mgIFNLNAtSDoTOLK/R9vlI0o51tEg=="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId1" roundtripDataSignature="AMtx7mi6nL3Qe+xcKX0PuirLAKQmu8OMFA=="/>
     </ext>
   </extLst>
 </comments>
